--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="60">
   <si>
     <t>Month</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Olive Oil</t>
+  </si>
+  <si>
+    <t>Café</t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1554,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1577,7 +1580,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1603,7 +1606,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1629,7 +1632,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1655,7 +1658,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1681,7 +1684,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1707,7 +1710,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1733,7 +1736,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1759,7 +1762,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1785,7 +1788,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1811,7 +1814,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1837,7 +1840,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1863,7 +1866,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1889,7 +1892,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1915,7 +1918,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1941,7 +1944,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1967,7 +1970,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -1993,7 +1996,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2019,7 +2022,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2045,7 +2048,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2071,7 +2074,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2097,7 +2100,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2123,7 +2126,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2149,7 +2152,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2175,7 +2178,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2201,7 +2204,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2227,7 +2230,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2253,7 +2256,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2279,7 +2282,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2331,7 +2334,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="59">
   <si>
     <t>Month</t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>Canned Beans</t>
-  </si>
-  <si>
-    <t>Coffee</t>
   </si>
   <si>
     <t>Oats</t>
@@ -1554,7 +1551,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1580,7 +1577,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1606,7 +1603,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1632,7 +1629,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1658,7 +1655,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1684,7 +1681,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1710,7 +1707,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1736,7 +1733,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1762,7 +1759,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1788,7 +1785,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1814,7 +1811,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1840,7 +1837,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1866,7 +1863,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1892,7 +1889,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1918,7 +1915,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1944,7 +1941,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1970,7 +1967,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -1996,7 +1993,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2022,7 +2019,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2048,7 +2045,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2074,7 +2071,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2100,7 +2097,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2126,7 +2123,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2152,7 +2149,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2178,7 +2175,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2204,7 +2201,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2230,7 +2227,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2256,7 +2253,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2282,7 +2279,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2308,7 +2305,7 @@
         <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D67" s="2">
         <v>259</v>
@@ -2334,7 +2331,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>
@@ -2360,7 +2357,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D69" s="2">
         <v>173</v>
@@ -2386,7 +2383,7 @@
         <v>102</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D70" s="2">
         <v>186</v>
@@ -2412,7 +2409,7 @@
         <v>102</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D71" s="2">
         <v>274</v>
@@ -2438,7 +2435,7 @@
         <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D72" s="2">
         <v>238</v>
@@ -2464,7 +2461,7 @@
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D73" s="2">
         <v>109</v>
@@ -2490,7 +2487,7 @@
         <v>103</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D74" s="2">
         <v>380</v>
@@ -2516,7 +2513,7 @@
         <v>103</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D75" s="2">
         <v>383</v>
@@ -2542,7 +2539,7 @@
         <v>103</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D76" s="2">
         <v>168</v>
@@ -2568,7 +2565,7 @@
         <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D77" s="2">
         <v>73</v>
@@ -2594,7 +2591,7 @@
         <v>103</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D78" s="2">
         <v>282</v>
@@ -2620,7 +2617,7 @@
         <v>103</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D79" s="2">
         <v>362</v>
@@ -2646,7 +2643,7 @@
         <v>103</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D80" s="2">
         <v>386</v>
@@ -2672,7 +2669,7 @@
         <v>103</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D81" s="2">
         <v>323</v>
@@ -2698,7 +2695,7 @@
         <v>103</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D82" s="2">
         <v>51</v>
@@ -2724,7 +2721,7 @@
         <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D83" s="2">
         <v>452</v>
@@ -2750,7 +2747,7 @@
         <v>103</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D84" s="2">
         <v>55</v>
@@ -2776,7 +2773,7 @@
         <v>103</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D85" s="2">
         <v>341</v>
@@ -2802,7 +2799,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D86" s="2">
         <v>155</v>
@@ -2828,7 +2825,7 @@
         <v>103</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D87" s="2">
         <v>496</v>
@@ -2854,7 +2851,7 @@
         <v>103</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D88" s="2">
         <v>462</v>
@@ -2880,7 +2877,7 @@
         <v>103</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D89" s="2">
         <v>394</v>
@@ -2906,7 +2903,7 @@
         <v>103</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D90" s="2">
         <v>207</v>
@@ -2932,7 +2929,7 @@
         <v>103</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D91" s="2">
         <v>336</v>
@@ -2958,7 +2955,7 @@
         <v>103</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D92" s="2">
         <v>481</v>
@@ -2984,7 +2981,7 @@
         <v>103</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D93" s="2">
         <v>180</v>
@@ -3010,7 +3007,7 @@
         <v>103</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D94" s="2">
         <v>337</v>
@@ -3036,7 +3033,7 @@
         <v>103</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D95" s="2">
         <v>88</v>
@@ -3062,7 +3059,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D96" s="2">
         <v>221</v>
@@ -3088,7 +3085,7 @@
         <v>103</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D97" s="2">
         <v>442</v>
@@ -3114,7 +3111,7 @@
         <v>103</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D98" s="2">
         <v>216</v>
@@ -3140,7 +3137,7 @@
         <v>103</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D99" s="2">
         <v>237</v>
@@ -3166,7 +3163,7 @@
         <v>103</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D100" s="2">
         <v>336</v>
@@ -3192,7 +3189,7 @@
         <v>103</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D101" s="2">
         <v>281</v>
@@ -3218,7 +3215,7 @@
         <v>103</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D102" s="2">
         <v>216</v>
@@ -3244,7 +3241,7 @@
         <v>103</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D103" s="2">
         <v>214</v>
@@ -3270,7 +3267,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D104" s="2">
         <v>323</v>
@@ -3296,7 +3293,7 @@
         <v>103</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D105" s="2">
         <v>305</v>
@@ -3322,7 +3319,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D106" s="2">
         <v>258</v>
@@ -3348,7 +3345,7 @@
         <v>103</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D107" s="2">
         <v>235</v>
@@ -3374,7 +3371,7 @@
         <v>103</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D108" s="2">
         <v>250</v>
@@ -3400,7 +3397,7 @@
         <v>103</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D109" s="2">
         <v>225</v>
@@ -3426,7 +3423,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3452,7 +3449,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3478,7 +3475,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3504,7 +3501,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3530,7 +3527,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3556,7 +3553,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3582,7 +3579,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3608,7 +3605,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3634,7 +3631,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3660,7 +3657,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3686,7 +3683,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>
@@ -3712,7 +3709,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3738,7 +3735,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3764,7 +3761,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3790,7 +3787,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3816,7 +3813,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3842,7 +3839,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -3868,7 +3865,7 @@
         <v>104</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D127" s="2">
         <v>141</v>
@@ -3894,7 +3891,7 @@
         <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D128" s="2">
         <v>303</v>
@@ -3920,7 +3917,7 @@
         <v>104</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D129" s="2">
         <v>281</v>
@@ -3946,7 +3943,7 @@
         <v>104</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D130" s="2">
         <v>453</v>
@@ -3972,7 +3969,7 @@
         <v>104</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D131" s="2">
         <v>310</v>
@@ -3998,7 +3995,7 @@
         <v>104</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D132" s="2">
         <v>243</v>
@@ -4024,7 +4021,7 @@
         <v>104</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D133" s="2">
         <v>248</v>
@@ -4050,7 +4047,7 @@
         <v>104</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D134" s="2">
         <v>253</v>
@@ -4076,7 +4073,7 @@
         <v>104</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D135" s="2">
         <v>197</v>
@@ -4102,7 +4099,7 @@
         <v>104</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D136" s="2">
         <v>184</v>
@@ -4128,7 +4125,7 @@
         <v>104</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D137" s="2">
         <v>119</v>
@@ -4154,7 +4151,7 @@
         <v>104</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D138" s="2">
         <v>192</v>
@@ -4180,7 +4177,7 @@
         <v>104</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D139" s="2">
         <v>237</v>
@@ -4206,7 +4203,7 @@
         <v>104</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D140" s="2">
         <v>71</v>
@@ -4232,7 +4229,7 @@
         <v>104</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D141" s="2">
         <v>170</v>
@@ -4258,7 +4255,7 @@
         <v>104</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D142" s="2">
         <v>201</v>
@@ -4284,7 +4281,7 @@
         <v>104</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D143" s="2">
         <v>226</v>
@@ -4310,7 +4307,7 @@
         <v>104</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D144" s="2">
         <v>251</v>
@@ -4336,7 +4333,7 @@
         <v>104</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D145" s="2">
         <v>281</v>
@@ -4362,7 +4359,7 @@
         <v>105</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D146" s="2">
         <v>494</v>
@@ -4388,7 +4385,7 @@
         <v>105</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D147" s="2">
         <v>383</v>
@@ -4414,7 +4411,7 @@
         <v>105</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D148" s="2">
         <v>243</v>
@@ -4440,7 +4437,7 @@
         <v>105</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D149" s="2">
         <v>384</v>
@@ -4466,7 +4463,7 @@
         <v>105</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D150" s="2">
         <v>316</v>
@@ -4492,7 +4489,7 @@
         <v>105</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D151" s="2">
         <v>362</v>
@@ -4518,7 +4515,7 @@
         <v>105</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D152" s="2">
         <v>479</v>
@@ -4544,7 +4541,7 @@
         <v>105</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D153" s="2">
         <v>317</v>
@@ -4570,7 +4567,7 @@
         <v>105</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D154" s="2">
         <v>240</v>
@@ -4596,7 +4593,7 @@
         <v>105</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D155" s="2">
         <v>290</v>
@@ -4622,7 +4619,7 @@
         <v>105</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D156" s="2">
         <v>477</v>
@@ -4648,7 +4645,7 @@
         <v>105</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D157" s="2">
         <v>362</v>
@@ -4674,7 +4671,7 @@
         <v>105</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D158" s="2">
         <v>54</v>
@@ -4700,7 +4697,7 @@
         <v>105</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D159" s="2">
         <v>281</v>
@@ -4726,7 +4723,7 @@
         <v>105</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D160" s="2">
         <v>381</v>
@@ -4752,7 +4749,7 @@
         <v>105</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D161" s="2">
         <v>351</v>
@@ -4778,7 +4775,7 @@
         <v>105</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D162" s="2">
         <v>309</v>
@@ -4804,7 +4801,7 @@
         <v>105</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D163" s="2">
         <v>383</v>
@@ -4830,7 +4827,7 @@
         <v>105</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D164" s="2">
         <v>407</v>
@@ -4856,7 +4853,7 @@
         <v>105</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D165" s="2">
         <v>171</v>
@@ -4882,7 +4879,7 @@
         <v>105</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D166" s="2">
         <v>274</v>
@@ -4908,7 +4905,7 @@
         <v>105</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D167" s="2">
         <v>295</v>
@@ -4934,7 +4931,7 @@
         <v>105</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D168" s="2">
         <v>418</v>
@@ -4960,7 +4957,7 @@
         <v>105</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D169" s="2">
         <v>84</v>
@@ -4986,7 +4983,7 @@
         <v>105</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D170" s="2">
         <v>247</v>
@@ -5012,7 +5009,7 @@
         <v>105</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D171" s="2">
         <v>179</v>
@@ -5038,7 +5035,7 @@
         <v>105</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D172" s="2">
         <v>322</v>
@@ -5064,7 +5061,7 @@
         <v>105</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D173" s="2">
         <v>271</v>
@@ -5090,7 +5087,7 @@
         <v>105</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D174" s="2">
         <v>281</v>
@@ -5116,7 +5113,7 @@
         <v>105</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D175" s="2">
         <v>174</v>
@@ -5142,7 +5139,7 @@
         <v>105</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D176" s="2">
         <v>305</v>
@@ -5168,7 +5165,7 @@
         <v>105</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D177" s="2">
         <v>254</v>
@@ -5194,7 +5191,7 @@
         <v>105</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D178" s="2">
         <v>312</v>
@@ -5220,7 +5217,7 @@
         <v>105</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D179" s="2">
         <v>115</v>
@@ -5246,7 +5243,7 @@
         <v>105</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D180" s="2">
         <v>161</v>
@@ -5272,7 +5269,7 @@
         <v>105</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D181" s="2">
         <v>240</v>
@@ -5298,7 +5295,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -5324,7 +5321,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5350,7 +5347,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5376,7 +5373,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5402,7 +5399,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -5428,7 +5425,7 @@
         <v>106</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D187" s="2">
         <v>342</v>
@@ -5454,7 +5451,7 @@
         <v>106</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D188" s="2">
         <v>285</v>
@@ -5480,7 +5477,7 @@
         <v>106</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D189" s="2">
         <v>453</v>
@@ -5506,7 +5503,7 @@
         <v>106</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D190" s="2">
         <v>69</v>
@@ -5532,7 +5529,7 @@
         <v>106</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D191" s="2">
         <v>154</v>
@@ -5558,7 +5555,7 @@
         <v>106</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D192" s="2">
         <v>246</v>
@@ -5584,7 +5581,7 @@
         <v>106</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D193" s="2">
         <v>446</v>
@@ -5610,7 +5607,7 @@
         <v>106</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D194" s="2">
         <v>467</v>
@@ -5636,7 +5633,7 @@
         <v>106</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D195" s="2">
         <v>374</v>
@@ -5662,7 +5659,7 @@
         <v>106</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D196" s="2">
         <v>266</v>
@@ -5688,7 +5685,7 @@
         <v>106</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D197" s="2">
         <v>281</v>
@@ -5714,7 +5711,7 @@
         <v>106</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D198" s="2">
         <v>277</v>
@@ -5740,7 +5737,7 @@
         <v>106</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D199" s="2">
         <v>153</v>
@@ -5766,7 +5763,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D200" s="2">
         <v>176</v>
@@ -5792,7 +5789,7 @@
         <v>106</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D201" s="2">
         <v>281</v>
@@ -5818,7 +5815,7 @@
         <v>106</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D202" s="2">
         <v>52</v>
@@ -5844,7 +5841,7 @@
         <v>106</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D203" s="2">
         <v>94</v>
@@ -5870,7 +5867,7 @@
         <v>106</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D204" s="2">
         <v>181</v>
@@ -5896,7 +5893,7 @@
         <v>106</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D205" s="2">
         <v>336</v>
@@ -5922,7 +5919,7 @@
         <v>106</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D206" s="2">
         <v>349</v>
@@ -5948,7 +5945,7 @@
         <v>106</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D207" s="2">
         <v>127</v>
@@ -5974,7 +5971,7 @@
         <v>106</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D208" s="2">
         <v>376</v>
@@ -6000,7 +5997,7 @@
         <v>106</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D209" s="2">
         <v>98</v>
@@ -6026,7 +6023,7 @@
         <v>106</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D210" s="2">
         <v>152</v>
@@ -6052,7 +6049,7 @@
         <v>106</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D211" s="2">
         <v>235</v>
@@ -6078,7 +6075,7 @@
         <v>106</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D212" s="2">
         <v>105</v>
@@ -6104,7 +6101,7 @@
         <v>106</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D213" s="2">
         <v>150</v>
@@ -6130,7 +6127,7 @@
         <v>106</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D214" s="2">
         <v>215</v>
@@ -6156,7 +6153,7 @@
         <v>106</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D215" s="2">
         <v>216</v>
@@ -6182,7 +6179,7 @@
         <v>106</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D216" s="2">
         <v>214</v>
@@ -6208,7 +6205,7 @@
         <v>106</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D217" s="2">
         <v>194</v>
@@ -6234,7 +6231,7 @@
         <v>107</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D218" s="2">
         <v>184</v>
@@ -6260,7 +6257,7 @@
         <v>107</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D219" s="2">
         <v>379</v>
@@ -6286,7 +6283,7 @@
         <v>107</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D220" s="2">
         <v>424</v>
@@ -6312,7 +6309,7 @@
         <v>107</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D221" s="2">
         <v>93</v>
@@ -6338,7 +6335,7 @@
         <v>107</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D222" s="2">
         <v>219</v>
@@ -6364,7 +6361,7 @@
         <v>107</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D223" s="2">
         <v>165</v>
@@ -6390,7 +6387,7 @@
         <v>107</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D224" s="2">
         <v>462</v>
@@ -6416,7 +6413,7 @@
         <v>107</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D225" s="2">
         <v>332</v>
@@ -6442,7 +6439,7 @@
         <v>107</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D226" s="2">
         <v>162</v>
@@ -6468,7 +6465,7 @@
         <v>107</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D227" s="2">
         <v>305</v>
@@ -6494,7 +6491,7 @@
         <v>107</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D228" s="2">
         <v>446</v>
@@ -6520,7 +6517,7 @@
         <v>107</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D229" s="2">
         <v>196</v>
@@ -6546,7 +6543,7 @@
         <v>107</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D230" s="2">
         <v>443</v>
@@ -6572,7 +6569,7 @@
         <v>107</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D231" s="2">
         <v>158</v>
@@ -6598,7 +6595,7 @@
         <v>107</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D232" s="2">
         <v>191</v>
@@ -6624,7 +6621,7 @@
         <v>107</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D233" s="2">
         <v>321</v>
@@ -6650,7 +6647,7 @@
         <v>107</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D234" s="2">
         <v>316</v>
@@ -6676,7 +6673,7 @@
         <v>107</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D235" s="2">
         <v>71</v>
@@ -6702,7 +6699,7 @@
         <v>107</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D236" s="2">
         <v>171</v>
@@ -6728,7 +6725,7 @@
         <v>107</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D237" s="2">
         <v>450</v>
@@ -6754,7 +6751,7 @@
         <v>107</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D238" s="2">
         <v>354</v>
@@ -6780,7 +6777,7 @@
         <v>107</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D239" s="2">
         <v>475</v>
@@ -6806,7 +6803,7 @@
         <v>107</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D240" s="2">
         <v>130</v>
@@ -6832,7 +6829,7 @@
         <v>107</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D241" s="2">
         <v>140</v>
@@ -6858,7 +6855,7 @@
         <v>107</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D242" s="2">
         <v>253</v>
@@ -6884,7 +6881,7 @@
         <v>107</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D243" s="2">
         <v>246</v>
@@ -6910,7 +6907,7 @@
         <v>107</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D244" s="2">
         <v>297</v>
@@ -6936,7 +6933,7 @@
         <v>107</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D245" s="2">
         <v>201</v>
@@ -6962,7 +6959,7 @@
         <v>107</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D246" s="2">
         <v>339</v>
@@ -6988,7 +6985,7 @@
         <v>107</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D247" s="2">
         <v>132</v>
@@ -7014,7 +7011,7 @@
         <v>107</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D248" s="2">
         <v>239</v>
@@ -7040,7 +7037,7 @@
         <v>107</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D249" s="2">
         <v>169</v>
@@ -7066,7 +7063,7 @@
         <v>107</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D250" s="2">
         <v>217</v>
@@ -7092,7 +7089,7 @@
         <v>107</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D251" s="2">
         <v>340</v>
@@ -7118,7 +7115,7 @@
         <v>107</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D252" s="2">
         <v>192</v>
@@ -7144,7 +7141,7 @@
         <v>107</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D253" s="2">
         <v>243</v>
@@ -7170,7 +7167,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -7196,7 +7193,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7222,7 +7219,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -7248,7 +7245,7 @@
         <v>108</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D257" s="2">
         <v>451</v>
@@ -7274,7 +7271,7 @@
         <v>108</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D258" s="2">
         <v>183</v>
@@ -7300,7 +7297,7 @@
         <v>108</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D259" s="2">
         <v>311</v>
@@ -7326,7 +7323,7 @@
         <v>108</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D260" s="2">
         <v>365</v>
@@ -7352,7 +7349,7 @@
         <v>108</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D261" s="2">
         <v>411</v>
@@ -7378,7 +7375,7 @@
         <v>108</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D262" s="2">
         <v>130</v>
@@ -7404,7 +7401,7 @@
         <v>108</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D263" s="2">
         <v>69</v>
@@ -7430,7 +7427,7 @@
         <v>108</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D264" s="2">
         <v>391</v>
@@ -7456,7 +7453,7 @@
         <v>108</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D265" s="2">
         <v>475</v>
@@ -7482,7 +7479,7 @@
         <v>108</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D266" s="2">
         <v>386</v>
@@ -7508,7 +7505,7 @@
         <v>108</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D267" s="2">
         <v>345</v>
@@ -7534,7 +7531,7 @@
         <v>108</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D268" s="2">
         <v>57</v>
@@ -7560,7 +7557,7 @@
         <v>108</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D269" s="2">
         <v>489</v>
@@ -7586,7 +7583,7 @@
         <v>108</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D270" s="2">
         <v>88</v>
@@ -7612,7 +7609,7 @@
         <v>108</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D271" s="2">
         <v>417</v>
@@ -7638,7 +7635,7 @@
         <v>108</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D272" s="2">
         <v>437</v>
@@ -7664,7 +7661,7 @@
         <v>108</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D273" s="2">
         <v>249</v>
@@ -7690,7 +7687,7 @@
         <v>108</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D274" s="2">
         <v>86</v>
@@ -7716,7 +7713,7 @@
         <v>108</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D275" s="2">
         <v>191</v>
@@ -7742,7 +7739,7 @@
         <v>108</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D276" s="2">
         <v>298</v>
@@ -7768,7 +7765,7 @@
         <v>108</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D277" s="2">
         <v>235</v>
@@ -7794,7 +7791,7 @@
         <v>108</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D278" s="2">
         <v>201</v>
@@ -7820,7 +7817,7 @@
         <v>108</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D279" s="2">
         <v>158</v>
@@ -7846,7 +7843,7 @@
         <v>108</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D280" s="2">
         <v>135</v>
@@ -7872,7 +7869,7 @@
         <v>108</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D281" s="2">
         <v>333</v>
@@ -7898,7 +7895,7 @@
         <v>108</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D282" s="2">
         <v>352</v>
@@ -7924,7 +7921,7 @@
         <v>108</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D283" s="2">
         <v>66</v>
@@ -7950,7 +7947,7 @@
         <v>108</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D284" s="2">
         <v>116</v>
@@ -7976,7 +7973,7 @@
         <v>108</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D285" s="2">
         <v>214</v>
@@ -8002,7 +7999,7 @@
         <v>108</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D286" s="2">
         <v>210</v>
@@ -8028,7 +8025,7 @@
         <v>108</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D287" s="2">
         <v>295</v>
@@ -8054,7 +8051,7 @@
         <v>108</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D288" s="2">
         <v>112</v>
@@ -8080,7 +8077,7 @@
         <v>108</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D289" s="2">
         <v>222</v>
@@ -8106,7 +8103,7 @@
         <v>109</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D290" s="2">
         <v>212</v>
@@ -8132,7 +8129,7 @@
         <v>109</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D291" s="2">
         <v>457</v>
@@ -8158,7 +8155,7 @@
         <v>109</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D292" s="2">
         <v>203</v>
@@ -8184,7 +8181,7 @@
         <v>109</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D293" s="2">
         <v>247</v>
@@ -8210,7 +8207,7 @@
         <v>109</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D294" s="2">
         <v>113</v>
@@ -8236,7 +8233,7 @@
         <v>109</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D295" s="2">
         <v>107</v>
@@ -8262,7 +8259,7 @@
         <v>109</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D296" s="2">
         <v>338</v>
@@ -8288,7 +8285,7 @@
         <v>109</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D297" s="2">
         <v>259</v>
@@ -8314,7 +8311,7 @@
         <v>109</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D298" s="2">
         <v>430</v>
@@ -8340,7 +8337,7 @@
         <v>109</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D299" s="2">
         <v>329</v>
@@ -8366,7 +8363,7 @@
         <v>109</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D300" s="2">
         <v>369</v>
@@ -8392,7 +8389,7 @@
         <v>109</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D301" s="2">
         <v>262</v>
@@ -8418,7 +8415,7 @@
         <v>109</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D302" s="2">
         <v>253</v>
@@ -8444,7 +8441,7 @@
         <v>109</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D303" s="2">
         <v>257</v>
@@ -8470,7 +8467,7 @@
         <v>109</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D304" s="2">
         <v>446</v>
@@ -8496,7 +8493,7 @@
         <v>109</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D305" s="2">
         <v>270</v>
@@ -8522,7 +8519,7 @@
         <v>109</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D306" s="2">
         <v>486</v>
@@ -8548,7 +8545,7 @@
         <v>109</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D307" s="2">
         <v>484</v>
@@ -8574,7 +8571,7 @@
         <v>109</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D308" s="2">
         <v>277</v>
@@ -8600,7 +8597,7 @@
         <v>109</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D309" s="2">
         <v>298</v>
@@ -8626,7 +8623,7 @@
         <v>109</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D310" s="2">
         <v>148</v>
@@ -8652,7 +8649,7 @@
         <v>109</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D311" s="2">
         <v>218</v>
@@ -8678,7 +8675,7 @@
         <v>109</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D312" s="2">
         <v>253</v>
@@ -8704,7 +8701,7 @@
         <v>109</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D313" s="2">
         <v>266</v>
@@ -8730,7 +8727,7 @@
         <v>109</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D314" s="2">
         <v>290</v>
@@ -8756,7 +8753,7 @@
         <v>109</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D315" s="2">
         <v>197</v>
@@ -8782,7 +8779,7 @@
         <v>109</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D316" s="2">
         <v>160</v>
@@ -8808,7 +8805,7 @@
         <v>109</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D317" s="2">
         <v>272</v>
@@ -8834,7 +8831,7 @@
         <v>109</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D318" s="2">
         <v>254</v>
@@ -8860,7 +8857,7 @@
         <v>109</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D319" s="2">
         <v>160</v>
@@ -8886,7 +8883,7 @@
         <v>109</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D320" s="2">
         <v>150</v>
@@ -8912,7 +8909,7 @@
         <v>109</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D321" s="2">
         <v>247</v>
@@ -8938,7 +8935,7 @@
         <v>109</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D322" s="2">
         <v>263</v>
@@ -8964,7 +8961,7 @@
         <v>109</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D323" s="2">
         <v>267</v>
@@ -8990,7 +8987,7 @@
         <v>109</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D324" s="2">
         <v>223</v>
@@ -9016,7 +9013,7 @@
         <v>109</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D325" s="2">
         <v>170</v>
@@ -9042,7 +9039,7 @@
         <v>110</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D326" s="2">
         <v>175</v>
@@ -9068,7 +9065,7 @@
         <v>110</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D327" s="2">
         <v>333</v>
@@ -9094,7 +9091,7 @@
         <v>110</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D328" s="2">
         <v>442</v>
@@ -9120,7 +9117,7 @@
         <v>110</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D329" s="2">
         <v>131</v>
@@ -9146,7 +9143,7 @@
         <v>110</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D330" s="2">
         <v>275</v>
@@ -9172,7 +9169,7 @@
         <v>110</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D331" s="2">
         <v>170</v>
@@ -9198,7 +9195,7 @@
         <v>110</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D332" s="2">
         <v>94</v>
@@ -9224,7 +9221,7 @@
         <v>110</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D333" s="2">
         <v>56</v>
@@ -9250,7 +9247,7 @@
         <v>110</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D334" s="2">
         <v>297</v>
@@ -9276,7 +9273,7 @@
         <v>110</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D335" s="2">
         <v>389</v>
@@ -9302,7 +9299,7 @@
         <v>110</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D336" s="2">
         <v>88</v>
@@ -9328,7 +9325,7 @@
         <v>110</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D337" s="2">
         <v>101</v>
@@ -9354,7 +9351,7 @@
         <v>110</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D338" s="2">
         <v>237</v>
@@ -9380,7 +9377,7 @@
         <v>110</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D339" s="2">
         <v>251</v>
@@ -9406,7 +9403,7 @@
         <v>110</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D340" s="2">
         <v>62</v>
@@ -9432,7 +9429,7 @@
         <v>110</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D341" s="2">
         <v>144</v>
@@ -9458,7 +9455,7 @@
         <v>110</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D342" s="2">
         <v>180</v>
@@ -9484,7 +9481,7 @@
         <v>110</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D343" s="2">
         <v>358</v>
@@ -9510,7 +9507,7 @@
         <v>110</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D344" s="2">
         <v>452</v>
@@ -9536,7 +9533,7 @@
         <v>110</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D345" s="2">
         <v>121</v>
@@ -9562,7 +9559,7 @@
         <v>110</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D346" s="2">
         <v>354</v>
@@ -9588,7 +9585,7 @@
         <v>110</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D347" s="2">
         <v>151</v>
@@ -9614,7 +9611,7 @@
         <v>110</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D348" s="2">
         <v>270</v>
@@ -9640,7 +9637,7 @@
         <v>110</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D349" s="2">
         <v>361</v>
@@ -9666,7 +9663,7 @@
         <v>110</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D350" s="2">
         <v>148</v>
@@ -9692,7 +9689,7 @@
         <v>110</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D351" s="2">
         <v>223</v>
@@ -9718,7 +9715,7 @@
         <v>110</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D352" s="2">
         <v>79</v>
@@ -9744,7 +9741,7 @@
         <v>110</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D353" s="2">
         <v>104</v>
@@ -9770,7 +9767,7 @@
         <v>110</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D354" s="2">
         <v>294</v>
@@ -9796,7 +9793,7 @@
         <v>110</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D355" s="2">
         <v>248</v>
@@ -9822,7 +9819,7 @@
         <v>110</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D356" s="2">
         <v>215</v>
@@ -9848,7 +9845,7 @@
         <v>110</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D357" s="2">
         <v>258</v>
@@ -9874,7 +9871,7 @@
         <v>110</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D358" s="2">
         <v>201</v>
@@ -9900,7 +9897,7 @@
         <v>110</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D359" s="2">
         <v>238</v>
@@ -9926,7 +9923,7 @@
         <v>110</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D360" s="2">
         <v>286</v>
@@ -9952,7 +9949,7 @@
         <v>110</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D361" s="2">
         <v>386</v>
@@ -9978,7 +9975,7 @@
         <v>111</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D362" s="2">
         <v>497</v>
@@ -10004,7 +10001,7 @@
         <v>111</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D363" s="2">
         <v>372</v>
@@ -10030,7 +10027,7 @@
         <v>111</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D364" s="2">
         <v>377</v>
@@ -10056,7 +10053,7 @@
         <v>111</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D365" s="2">
         <v>450</v>
@@ -10082,7 +10079,7 @@
         <v>111</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D366" s="2">
         <v>381</v>
@@ -10108,7 +10105,7 @@
         <v>111</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D367" s="2">
         <v>132</v>
@@ -10134,7 +10131,7 @@
         <v>111</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D368" s="2">
         <v>160</v>
@@ -10160,7 +10157,7 @@
         <v>111</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D369" s="2">
         <v>80</v>
@@ -10186,7 +10183,7 @@
         <v>111</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D370" s="2">
         <v>124</v>
@@ -10212,7 +10209,7 @@
         <v>111</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D371" s="2">
         <v>468</v>
@@ -10238,7 +10235,7 @@
         <v>111</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D372" s="2">
         <v>131</v>
@@ -10264,7 +10261,7 @@
         <v>111</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D373" s="2">
         <v>171</v>
@@ -10290,7 +10287,7 @@
         <v>111</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D374" s="2">
         <v>470</v>
@@ -10316,7 +10313,7 @@
         <v>111</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D375" s="2">
         <v>423</v>
@@ -10342,7 +10339,7 @@
         <v>111</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D376" s="2">
         <v>392</v>
@@ -10368,7 +10365,7 @@
         <v>111</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D377" s="2">
         <v>330</v>
@@ -10394,7 +10391,7 @@
         <v>111</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D378" s="2">
         <v>287</v>
@@ -10420,7 +10417,7 @@
         <v>111</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D379" s="2">
         <v>171</v>
@@ -10446,7 +10443,7 @@
         <v>111</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D380" s="2">
         <v>470</v>
@@ -10472,7 +10469,7 @@
         <v>111</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D381" s="2">
         <v>345</v>
@@ -10498,7 +10495,7 @@
         <v>111</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D382" s="2">
         <v>78</v>
@@ -10524,7 +10521,7 @@
         <v>111</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D383" s="2">
         <v>389</v>
@@ -10550,7 +10547,7 @@
         <v>111</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D384" s="2">
         <v>129</v>
@@ -10576,7 +10573,7 @@
         <v>111</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D385" s="2">
         <v>449</v>
@@ -10602,7 +10599,7 @@
         <v>111</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D386" s="2">
         <v>224</v>
@@ -10628,7 +10625,7 @@
         <v>111</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D387" s="2">
         <v>99</v>
@@ -10654,7 +10651,7 @@
         <v>111</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D388" s="2">
         <v>84</v>
@@ -10680,7 +10677,7 @@
         <v>111</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D389" s="2">
         <v>206</v>
@@ -10706,7 +10703,7 @@
         <v>111</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D390" s="2">
         <v>356</v>
@@ -10732,7 +10729,7 @@
         <v>111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D391" s="2">
         <v>370</v>
@@ -10758,7 +10755,7 @@
         <v>111</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D392" s="2">
         <v>211</v>
@@ -10784,7 +10781,7 @@
         <v>111</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D393" s="2">
         <v>198</v>
@@ -10810,7 +10807,7 @@
         <v>111</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D394" s="2">
         <v>246</v>
@@ -10836,7 +10833,7 @@
         <v>111</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D395" s="2">
         <v>119</v>
@@ -10862,7 +10859,7 @@
         <v>111</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D396" s="2">
         <v>228</v>
@@ -10888,7 +10885,7 @@
         <v>111</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D397" s="2">
         <v>166</v>
@@ -10914,7 +10911,7 @@
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D398" s="2">
         <v>421</v>
@@ -10940,7 +10937,7 @@
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D399" s="2">
         <v>99</v>
@@ -10966,7 +10963,7 @@
         <v>112</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D400" s="2">
         <v>474</v>
@@ -10992,7 +10989,7 @@
         <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D401" s="2">
         <v>398</v>
@@ -11018,7 +11015,7 @@
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D402" s="2">
         <v>147</v>
@@ -11044,7 +11041,7 @@
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D403" s="2">
         <v>443</v>
@@ -11070,7 +11067,7 @@
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D404" s="2">
         <v>259</v>
@@ -11096,7 +11093,7 @@
         <v>112</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D405" s="2">
         <v>264</v>
@@ -11122,7 +11119,7 @@
         <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D406" s="2">
         <v>450</v>
@@ -11148,7 +11145,7 @@
         <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D407" s="2">
         <v>490</v>
@@ -11174,7 +11171,7 @@
         <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D408" s="2">
         <v>457</v>
@@ -11200,7 +11197,7 @@
         <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D409" s="2">
         <v>481</v>
@@ -11226,7 +11223,7 @@
         <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D410" s="2">
         <v>452</v>
@@ -11252,7 +11249,7 @@
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D411" s="2">
         <v>194</v>
@@ -11278,7 +11275,7 @@
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D412" s="2">
         <v>399</v>
@@ -11304,7 +11301,7 @@
         <v>112</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D413" s="2">
         <v>264</v>
@@ -11330,7 +11327,7 @@
         <v>112</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D414" s="2">
         <v>109</v>
@@ -11356,7 +11353,7 @@
         <v>112</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D415" s="2">
         <v>437</v>
@@ -11382,7 +11379,7 @@
         <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D416" s="2">
         <v>447</v>
@@ -11408,7 +11405,7 @@
         <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D417" s="2">
         <v>421</v>
@@ -11434,7 +11431,7 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D418" s="2">
         <v>80</v>
@@ -11460,7 +11457,7 @@
         <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D419" s="2">
         <v>493</v>
@@ -11486,7 +11483,7 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D420" s="2">
         <v>105</v>
@@ -11512,7 +11509,7 @@
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D421" s="2">
         <v>432</v>
@@ -11538,7 +11535,7 @@
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D422" s="2">
         <v>332</v>
@@ -11564,7 +11561,7 @@
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D423" s="2">
         <v>238</v>
@@ -11590,7 +11587,7 @@
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D424" s="2">
         <v>300</v>
@@ -11616,7 +11613,7 @@
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D425" s="2">
         <v>249</v>
@@ -11642,7 +11639,7 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D426" s="2">
         <v>336</v>
@@ -11668,7 +11665,7 @@
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D427" s="2">
         <v>114</v>
@@ -11694,7 +11691,7 @@
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D428" s="2">
         <v>175</v>
@@ -11720,7 +11717,7 @@
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D429" s="2">
         <v>473</v>
@@ -11746,7 +11743,7 @@
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D430" s="2">
         <v>202</v>
@@ -11772,7 +11769,7 @@
         <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D431" s="2">
         <v>215</v>
@@ -11798,7 +11795,7 @@
         <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D432" s="2">
         <v>252</v>
@@ -11824,7 +11821,7 @@
         <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D433" s="2">
         <v>223</v>
@@ -11850,7 +11847,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>
@@ -11876,7 +11873,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11902,7 +11899,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11928,7 +11925,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>
@@ -11954,7 +11951,7 @@
         <v>113</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D438" s="2">
         <v>219</v>
@@ -11980,7 +11977,7 @@
         <v>113</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D439" s="2">
         <v>99</v>
@@ -12006,7 +12003,7 @@
         <v>113</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D440" s="2">
         <v>177</v>
@@ -12032,7 +12029,7 @@
         <v>113</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D441" s="2">
         <v>380</v>
@@ -12058,7 +12055,7 @@
         <v>113</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D442" s="2">
         <v>464</v>
@@ -12084,7 +12081,7 @@
         <v>113</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D443" s="2">
         <v>460</v>
@@ -12110,7 +12107,7 @@
         <v>113</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D444" s="2">
         <v>299</v>
@@ -12136,7 +12133,7 @@
         <v>113</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D445" s="2">
         <v>243</v>
@@ -12162,7 +12159,7 @@
         <v>113</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D446" s="2">
         <v>154</v>
@@ -12188,7 +12185,7 @@
         <v>113</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D447" s="2">
         <v>239</v>
@@ -12214,7 +12211,7 @@
         <v>113</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D448" s="2">
         <v>410</v>
@@ -12240,7 +12237,7 @@
         <v>113</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D449" s="2">
         <v>273</v>
@@ -12266,7 +12263,7 @@
         <v>113</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D450" s="2">
         <v>90</v>
@@ -12292,7 +12289,7 @@
         <v>113</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D451" s="2">
         <v>407</v>
@@ -12318,7 +12315,7 @@
         <v>113</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D452" s="2">
         <v>301</v>
@@ -12344,7 +12341,7 @@
         <v>113</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D453" s="2">
         <v>181</v>
@@ -12370,7 +12367,7 @@
         <v>113</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D454" s="2">
         <v>186</v>
@@ -12396,7 +12393,7 @@
         <v>113</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D455" s="2">
         <v>424</v>
@@ -12422,7 +12419,7 @@
         <v>113</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D456" s="2">
         <v>268</v>
@@ -12448,7 +12445,7 @@
         <v>113</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D457" s="2">
         <v>277</v>
@@ -12474,7 +12471,7 @@
         <v>113</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D458" s="2">
         <v>89</v>
@@ -12500,7 +12497,7 @@
         <v>113</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D459" s="2">
         <v>219</v>
@@ -12526,7 +12523,7 @@
         <v>113</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D460" s="2">
         <v>273</v>
@@ -12552,7 +12549,7 @@
         <v>113</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D461" s="2">
         <v>254</v>
@@ -12578,7 +12575,7 @@
         <v>113</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D462" s="2">
         <v>243</v>
@@ -12604,7 +12601,7 @@
         <v>113</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D463" s="2">
         <v>349</v>
@@ -12630,7 +12627,7 @@
         <v>113</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D464" s="2">
         <v>245</v>
@@ -12656,7 +12653,7 @@
         <v>113</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D465" s="2">
         <v>174</v>
@@ -12682,7 +12679,7 @@
         <v>113</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D466" s="2">
         <v>80</v>
@@ -12708,7 +12705,7 @@
         <v>113</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D467" s="2">
         <v>210</v>
@@ -12734,7 +12731,7 @@
         <v>113</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D468" s="2">
         <v>281</v>
@@ -12760,7 +12757,7 @@
         <v>113</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D469" s="2">
         <v>80</v>
@@ -12786,7 +12783,7 @@
         <v>114</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D470" s="2">
         <v>106</v>
@@ -12812,7 +12809,7 @@
         <v>114</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D471" s="2">
         <v>53</v>
@@ -12838,7 +12835,7 @@
         <v>114</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D472" s="2">
         <v>80</v>
@@ -12864,7 +12861,7 @@
         <v>114</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D473" s="2">
         <v>92</v>
@@ -12890,7 +12887,7 @@
         <v>114</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D474" s="2">
         <v>146</v>
@@ -12916,7 +12913,7 @@
         <v>114</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D475" s="2">
         <v>465</v>
@@ -12942,7 +12939,7 @@
         <v>114</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D476" s="2">
         <v>361</v>
@@ -12968,7 +12965,7 @@
         <v>114</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D477" s="2">
         <v>420</v>
@@ -12994,7 +12991,7 @@
         <v>114</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D478" s="2">
         <v>471</v>
@@ -13020,7 +13017,7 @@
         <v>114</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D479" s="2">
         <v>174</v>
@@ -13046,7 +13043,7 @@
         <v>114</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D480" s="2">
         <v>95</v>
@@ -13072,7 +13069,7 @@
         <v>114</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D481" s="2">
         <v>305</v>
@@ -13098,7 +13095,7 @@
         <v>114</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D482" s="2">
         <v>465</v>
@@ -13124,7 +13121,7 @@
         <v>114</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D483" s="2">
         <v>418</v>
@@ -13150,7 +13147,7 @@
         <v>114</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D484" s="2">
         <v>478</v>
@@ -13176,7 +13173,7 @@
         <v>114</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D485" s="2">
         <v>434</v>
@@ -13202,7 +13199,7 @@
         <v>114</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D486" s="2">
         <v>459</v>
@@ -13228,7 +13225,7 @@
         <v>114</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D487" s="2">
         <v>99</v>
@@ -13254,7 +13251,7 @@
         <v>114</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D488" s="2">
         <v>104</v>
@@ -13280,7 +13277,7 @@
         <v>114</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D489" s="2">
         <v>166</v>
@@ -13306,7 +13303,7 @@
         <v>114</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D490" s="2">
         <v>277</v>
@@ -13332,7 +13329,7 @@
         <v>114</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D491" s="2">
         <v>329</v>
@@ -13358,7 +13355,7 @@
         <v>114</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D492" s="2">
         <v>193</v>
@@ -13384,7 +13381,7 @@
         <v>114</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D493" s="2">
         <v>70</v>
@@ -13410,7 +13407,7 @@
         <v>114</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D494" s="2">
         <v>174</v>
@@ -13436,7 +13433,7 @@
         <v>114</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D495" s="2">
         <v>305</v>
@@ -13462,7 +13459,7 @@
         <v>114</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D496" s="2">
         <v>274</v>
@@ -13488,7 +13485,7 @@
         <v>114</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D497" s="2">
         <v>185</v>
@@ -13514,7 +13511,7 @@
         <v>114</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D498" s="2">
         <v>249</v>
@@ -13540,7 +13537,7 @@
         <v>114</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D499" s="2">
         <v>203</v>
@@ -13566,7 +13563,7 @@
         <v>114</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D500" s="2">
         <v>315</v>
@@ -13592,7 +13589,7 @@
         <v>114</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D501" s="2">
         <v>211</v>
@@ -13618,7 +13615,7 @@
         <v>114</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D502" s="2">
         <v>262</v>
@@ -13644,7 +13641,7 @@
         <v>114</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D503" s="2">
         <v>346</v>
@@ -13670,7 +13667,7 @@
         <v>114</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D504" s="2">
         <v>232</v>
@@ -13696,7 +13693,7 @@
         <v>114</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D505" s="2">
         <v>142</v>
@@ -13722,7 +13719,7 @@
         <v>115</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D506" s="2">
         <v>316</v>
@@ -13748,7 +13745,7 @@
         <v>115</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D507" s="2">
         <v>221</v>
@@ -13774,7 +13771,7 @@
         <v>115</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D508" s="2">
         <v>318</v>
@@ -13800,7 +13797,7 @@
         <v>115</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D509" s="2">
         <v>147</v>
@@ -13826,7 +13823,7 @@
         <v>115</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D510" s="2">
         <v>396</v>
@@ -13852,7 +13849,7 @@
         <v>115</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D511" s="2">
         <v>409</v>
@@ -13878,7 +13875,7 @@
         <v>115</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D512" s="2">
         <v>278</v>
@@ -13904,7 +13901,7 @@
         <v>115</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D513" s="2">
         <v>103</v>
@@ -13930,7 +13927,7 @@
         <v>115</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D514" s="2">
         <v>419</v>
@@ -13956,7 +13953,7 @@
         <v>115</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D515" s="2">
         <v>243</v>
@@ -13982,7 +13979,7 @@
         <v>115</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D516" s="2">
         <v>280</v>
@@ -14008,7 +14005,7 @@
         <v>115</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D517" s="2">
         <v>206</v>
@@ -14034,7 +14031,7 @@
         <v>115</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D518" s="2">
         <v>114</v>
@@ -14060,7 +14057,7 @@
         <v>115</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D519" s="2">
         <v>58</v>
@@ -14086,7 +14083,7 @@
         <v>115</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D520" s="2">
         <v>198</v>
@@ -14112,7 +14109,7 @@
         <v>115</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D521" s="2">
         <v>138</v>
@@ -14138,7 +14135,7 @@
         <v>115</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D522" s="2">
         <v>417</v>
@@ -14164,7 +14161,7 @@
         <v>115</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D523" s="2">
         <v>141</v>
@@ -14190,7 +14187,7 @@
         <v>115</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D524" s="2">
         <v>456</v>
@@ -14216,7 +14213,7 @@
         <v>115</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D525" s="2">
         <v>316</v>
@@ -14242,7 +14239,7 @@
         <v>115</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D526" s="2">
         <v>357</v>
@@ -14268,7 +14265,7 @@
         <v>115</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D527" s="2">
         <v>143</v>
@@ -14294,7 +14291,7 @@
         <v>115</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D528" s="2">
         <v>177</v>
@@ -14320,7 +14317,7 @@
         <v>115</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D529" s="2">
         <v>226</v>
@@ -14346,7 +14343,7 @@
         <v>115</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D530" s="2">
         <v>344</v>
@@ -14372,7 +14369,7 @@
         <v>115</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D531" s="2">
         <v>143</v>
@@ -14398,7 +14395,7 @@
         <v>115</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D532" s="2">
         <v>97</v>
@@ -14424,7 +14421,7 @@
         <v>115</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D533" s="2">
         <v>193</v>
@@ -14450,7 +14447,7 @@
         <v>115</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D534" s="2">
         <v>56</v>
@@ -14476,7 +14473,7 @@
         <v>115</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D535" s="2">
         <v>121</v>
@@ -14502,7 +14499,7 @@
         <v>115</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D536" s="2">
         <v>150</v>
@@ -14528,7 +14525,7 @@
         <v>115</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D537" s="2">
         <v>344</v>
@@ -14554,7 +14551,7 @@
         <v>115</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D538" s="2">
         <v>188</v>
@@ -14580,7 +14577,7 @@
         <v>115</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D539" s="2">
         <v>342</v>
@@ -14606,7 +14603,7 @@
         <v>115</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D540" s="2">
         <v>234</v>
@@ -14632,7 +14629,7 @@
         <v>115</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D541" s="2">
         <v>239</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="60">
   <si>
     <t>Month</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Café</t>
+  </si>
+  <si>
+    <t>Danone</t>
   </si>
 </sst>
 </file>
@@ -3423,7 +3426,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3449,7 +3452,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3475,7 +3478,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3501,7 +3504,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3527,7 +3530,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3553,7 +3556,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3579,7 +3582,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3605,7 +3608,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3631,7 +3634,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3657,7 +3660,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3683,7 +3686,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="64">
   <si>
     <t>Month</t>
   </si>
@@ -202,6 +202,18 @@
   </si>
   <si>
     <t>Danone</t>
+  </si>
+  <si>
+    <t>Lait</t>
+  </si>
+  <si>
+    <t>Fromage</t>
+  </si>
+  <si>
+    <t>Beurre</t>
+  </si>
+  <si>
+    <t>Pain</t>
   </si>
 </sst>
 </file>
@@ -618,7 +630,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2">
         <v>373</v>
@@ -3712,7 +3724,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3738,7 +3750,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3764,7 +3776,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3790,7 +3802,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3816,7 +3828,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3842,7 +3854,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -5298,7 +5310,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -7170,7 +7182,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -11850,7 +11862,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -656,7 +656,7 @@
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D3" s="2">
         <v>423</v>
@@ -682,7 +682,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2">
         <v>147</v>
@@ -708,7 +708,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2">
         <v>431</v>
@@ -5336,7 +5336,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5362,7 +5362,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5388,7 +5388,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5414,7 +5414,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -7208,7 +7208,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7234,7 +7234,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -11888,7 +11888,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11914,7 +11914,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11940,7 +11940,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -156,9 +156,6 @@
     <t>2023-12</t>
   </si>
   <si>
-    <t>Canned Beans</t>
-  </si>
-  <si>
     <t>Oats</t>
   </si>
   <si>
@@ -214,6 +211,9 @@
   </si>
   <si>
     <t>Pain</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lait</t>
   </si>
 </sst>
 </file>
@@ -630,7 +630,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" s="2">
         <v>373</v>
@@ -656,7 +656,7 @@
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2">
         <v>423</v>
@@ -682,7 +682,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2">
         <v>147</v>
@@ -708,7 +708,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2">
         <v>431</v>
@@ -734,7 +734,7 @@
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2">
         <v>305</v>
@@ -760,7 +760,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2">
         <v>167</v>
@@ -786,7 +786,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2">
         <v>101</v>
@@ -812,7 +812,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2">
         <v>73</v>
@@ -838,7 +838,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2">
         <v>445</v>
@@ -864,7 +864,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2">
         <v>180</v>
@@ -890,7 +890,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2">
         <v>221</v>
@@ -916,7 +916,7 @@
         <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D13" s="2">
         <v>153</v>
@@ -942,7 +942,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2">
         <v>283</v>
@@ -968,7 +968,7 @@
         <v>101</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D15" s="2">
         <v>220</v>
@@ -994,7 +994,7 @@
         <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2">
         <v>338</v>
@@ -1020,7 +1020,7 @@
         <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2">
         <v>209</v>
@@ -1046,7 +1046,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2">
         <v>186</v>
@@ -1072,7 +1072,7 @@
         <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2">
         <v>383</v>
@@ -1098,7 +1098,7 @@
         <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D20" s="2">
         <v>253</v>
@@ -1124,7 +1124,7 @@
         <v>101</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D21" s="2">
         <v>159</v>
@@ -1150,7 +1150,7 @@
         <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2">
         <v>212</v>
@@ -1176,7 +1176,7 @@
         <v>101</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2">
         <v>377</v>
@@ -1202,7 +1202,7 @@
         <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2">
         <v>126</v>
@@ -1228,7 +1228,7 @@
         <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D25" s="2">
         <v>283</v>
@@ -1254,7 +1254,7 @@
         <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D26" s="2">
         <v>235</v>
@@ -1280,7 +1280,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D27" s="2">
         <v>170</v>
@@ -1306,7 +1306,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D28" s="2">
         <v>321</v>
@@ -1332,7 +1332,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2">
         <v>127</v>
@@ -1358,7 +1358,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2">
         <v>162</v>
@@ -1384,7 +1384,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D31" s="2">
         <v>265</v>
@@ -1410,7 +1410,7 @@
         <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2">
         <v>193</v>
@@ -1436,7 +1436,7 @@
         <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D33" s="2">
         <v>211</v>
@@ -1462,7 +1462,7 @@
         <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D34" s="2">
         <v>328</v>
@@ -1488,7 +1488,7 @@
         <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D35" s="2">
         <v>127</v>
@@ -1514,7 +1514,7 @@
         <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D36" s="2">
         <v>176</v>
@@ -1540,7 +1540,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D37" s="2">
         <v>278</v>
@@ -1566,7 +1566,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1592,7 +1592,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1618,7 +1618,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1644,7 +1644,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1670,7 +1670,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1696,7 +1696,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1722,7 +1722,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1748,7 +1748,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1774,7 +1774,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1800,7 +1800,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1826,7 +1826,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1852,7 +1852,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1878,7 +1878,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1904,7 +1904,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1930,7 +1930,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1956,7 +1956,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1982,7 +1982,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -2008,7 +2008,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2034,7 +2034,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2060,7 +2060,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2086,7 +2086,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2112,7 +2112,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2138,7 +2138,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2164,7 +2164,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2190,7 +2190,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2216,7 +2216,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2242,7 +2242,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2268,7 +2268,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2294,7 +2294,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2320,7 +2320,7 @@
         <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D67" s="2">
         <v>259</v>
@@ -2346,7 +2346,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>
@@ -2372,7 +2372,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D69" s="2">
         <v>173</v>
@@ -2398,7 +2398,7 @@
         <v>102</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D70" s="2">
         <v>186</v>
@@ -2424,7 +2424,7 @@
         <v>102</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D71" s="2">
         <v>274</v>
@@ -2450,7 +2450,7 @@
         <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D72" s="2">
         <v>238</v>
@@ -2476,7 +2476,7 @@
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D73" s="2">
         <v>109</v>
@@ -2502,7 +2502,7 @@
         <v>103</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D74" s="2">
         <v>380</v>
@@ -2528,7 +2528,7 @@
         <v>103</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D75" s="2">
         <v>383</v>
@@ -2554,7 +2554,7 @@
         <v>103</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D76" s="2">
         <v>168</v>
@@ -2580,7 +2580,7 @@
         <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D77" s="2">
         <v>73</v>
@@ -2606,7 +2606,7 @@
         <v>103</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D78" s="2">
         <v>282</v>
@@ -2632,7 +2632,7 @@
         <v>103</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D79" s="2">
         <v>362</v>
@@ -2658,7 +2658,7 @@
         <v>103</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D80" s="2">
         <v>386</v>
@@ -2684,7 +2684,7 @@
         <v>103</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D81" s="2">
         <v>323</v>
@@ -2710,7 +2710,7 @@
         <v>103</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D82" s="2">
         <v>51</v>
@@ -2736,7 +2736,7 @@
         <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D83" s="2">
         <v>452</v>
@@ -2762,7 +2762,7 @@
         <v>103</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D84" s="2">
         <v>55</v>
@@ -2788,7 +2788,7 @@
         <v>103</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D85" s="2">
         <v>341</v>
@@ -2814,7 +2814,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D86" s="2">
         <v>155</v>
@@ -2840,7 +2840,7 @@
         <v>103</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D87" s="2">
         <v>496</v>
@@ -2866,7 +2866,7 @@
         <v>103</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D88" s="2">
         <v>462</v>
@@ -2892,7 +2892,7 @@
         <v>103</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D89" s="2">
         <v>394</v>
@@ -2918,7 +2918,7 @@
         <v>103</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D90" s="2">
         <v>207</v>
@@ -2944,7 +2944,7 @@
         <v>103</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D91" s="2">
         <v>336</v>
@@ -2970,7 +2970,7 @@
         <v>103</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D92" s="2">
         <v>481</v>
@@ -2996,7 +2996,7 @@
         <v>103</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D93" s="2">
         <v>180</v>
@@ -3022,7 +3022,7 @@
         <v>103</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D94" s="2">
         <v>337</v>
@@ -3048,7 +3048,7 @@
         <v>103</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D95" s="2">
         <v>88</v>
@@ -3074,7 +3074,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D96" s="2">
         <v>221</v>
@@ -3100,7 +3100,7 @@
         <v>103</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D97" s="2">
         <v>442</v>
@@ -3126,7 +3126,7 @@
         <v>103</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D98" s="2">
         <v>216</v>
@@ -3152,7 +3152,7 @@
         <v>103</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D99" s="2">
         <v>237</v>
@@ -3178,7 +3178,7 @@
         <v>103</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D100" s="2">
         <v>336</v>
@@ -3204,7 +3204,7 @@
         <v>103</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D101" s="2">
         <v>281</v>
@@ -3230,7 +3230,7 @@
         <v>103</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D102" s="2">
         <v>216</v>
@@ -3256,7 +3256,7 @@
         <v>103</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D103" s="2">
         <v>214</v>
@@ -3282,7 +3282,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D104" s="2">
         <v>323</v>
@@ -3308,7 +3308,7 @@
         <v>103</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D105" s="2">
         <v>305</v>
@@ -3334,7 +3334,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D106" s="2">
         <v>258</v>
@@ -3360,7 +3360,7 @@
         <v>103</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D107" s="2">
         <v>235</v>
@@ -3386,7 +3386,7 @@
         <v>103</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D108" s="2">
         <v>250</v>
@@ -3412,7 +3412,7 @@
         <v>103</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D109" s="2">
         <v>225</v>
@@ -3438,7 +3438,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3464,7 +3464,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3490,7 +3490,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3516,7 +3516,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3542,7 +3542,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3568,7 +3568,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3594,7 +3594,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3620,7 +3620,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3646,7 +3646,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3672,7 +3672,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3698,7 +3698,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>
@@ -3724,7 +3724,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3750,7 +3750,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3776,7 +3776,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3802,7 +3802,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3828,7 +3828,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3854,7 +3854,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -3880,7 +3880,7 @@
         <v>104</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D127" s="2">
         <v>141</v>
@@ -3906,7 +3906,7 @@
         <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D128" s="2">
         <v>303</v>
@@ -3932,7 +3932,7 @@
         <v>104</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D129" s="2">
         <v>281</v>
@@ -3958,7 +3958,7 @@
         <v>104</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D130" s="2">
         <v>453</v>
@@ -3984,7 +3984,7 @@
         <v>104</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D131" s="2">
         <v>310</v>
@@ -4010,7 +4010,7 @@
         <v>104</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D132" s="2">
         <v>243</v>
@@ -4036,7 +4036,7 @@
         <v>104</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D133" s="2">
         <v>248</v>
@@ -4062,7 +4062,7 @@
         <v>104</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D134" s="2">
         <v>253</v>
@@ -4088,7 +4088,7 @@
         <v>104</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D135" s="2">
         <v>197</v>
@@ -4114,7 +4114,7 @@
         <v>104</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D136" s="2">
         <v>184</v>
@@ -4140,7 +4140,7 @@
         <v>104</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D137" s="2">
         <v>119</v>
@@ -4166,7 +4166,7 @@
         <v>104</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D138" s="2">
         <v>192</v>
@@ -4192,7 +4192,7 @@
         <v>104</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D139" s="2">
         <v>237</v>
@@ -4218,7 +4218,7 @@
         <v>104</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D140" s="2">
         <v>71</v>
@@ -4244,7 +4244,7 @@
         <v>104</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D141" s="2">
         <v>170</v>
@@ -4270,7 +4270,7 @@
         <v>104</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D142" s="2">
         <v>201</v>
@@ -4296,7 +4296,7 @@
         <v>104</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D143" s="2">
         <v>226</v>
@@ -4322,7 +4322,7 @@
         <v>104</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D144" s="2">
         <v>251</v>
@@ -4348,7 +4348,7 @@
         <v>104</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D145" s="2">
         <v>281</v>
@@ -4374,7 +4374,7 @@
         <v>105</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D146" s="2">
         <v>494</v>
@@ -4400,7 +4400,7 @@
         <v>105</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D147" s="2">
         <v>383</v>
@@ -4426,7 +4426,7 @@
         <v>105</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D148" s="2">
         <v>243</v>
@@ -4452,7 +4452,7 @@
         <v>105</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D149" s="2">
         <v>384</v>
@@ -4478,7 +4478,7 @@
         <v>105</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D150" s="2">
         <v>316</v>
@@ -4504,7 +4504,7 @@
         <v>105</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D151" s="2">
         <v>362</v>
@@ -4530,7 +4530,7 @@
         <v>105</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D152" s="2">
         <v>479</v>
@@ -4556,7 +4556,7 @@
         <v>105</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D153" s="2">
         <v>317</v>
@@ -4582,7 +4582,7 @@
         <v>105</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D154" s="2">
         <v>240</v>
@@ -4608,7 +4608,7 @@
         <v>105</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D155" s="2">
         <v>290</v>
@@ -4634,7 +4634,7 @@
         <v>105</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D156" s="2">
         <v>477</v>
@@ -4660,7 +4660,7 @@
         <v>105</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D157" s="2">
         <v>362</v>
@@ -4686,7 +4686,7 @@
         <v>105</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D158" s="2">
         <v>54</v>
@@ -4712,7 +4712,7 @@
         <v>105</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D159" s="2">
         <v>281</v>
@@ -4738,7 +4738,7 @@
         <v>105</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D160" s="2">
         <v>381</v>
@@ -4764,7 +4764,7 @@
         <v>105</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D161" s="2">
         <v>351</v>
@@ -4790,7 +4790,7 @@
         <v>105</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D162" s="2">
         <v>309</v>
@@ -4816,7 +4816,7 @@
         <v>105</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D163" s="2">
         <v>383</v>
@@ -4842,7 +4842,7 @@
         <v>105</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D164" s="2">
         <v>407</v>
@@ -4868,7 +4868,7 @@
         <v>105</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D165" s="2">
         <v>171</v>
@@ -4894,7 +4894,7 @@
         <v>105</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D166" s="2">
         <v>274</v>
@@ -4920,7 +4920,7 @@
         <v>105</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D167" s="2">
         <v>295</v>
@@ -4946,7 +4946,7 @@
         <v>105</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D168" s="2">
         <v>418</v>
@@ -4972,7 +4972,7 @@
         <v>105</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D169" s="2">
         <v>84</v>
@@ -4998,7 +4998,7 @@
         <v>105</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D170" s="2">
         <v>247</v>
@@ -5024,7 +5024,7 @@
         <v>105</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D171" s="2">
         <v>179</v>
@@ -5050,7 +5050,7 @@
         <v>105</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D172" s="2">
         <v>322</v>
@@ -5076,7 +5076,7 @@
         <v>105</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D173" s="2">
         <v>271</v>
@@ -5102,7 +5102,7 @@
         <v>105</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D174" s="2">
         <v>281</v>
@@ -5128,7 +5128,7 @@
         <v>105</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D175" s="2">
         <v>174</v>
@@ -5154,7 +5154,7 @@
         <v>105</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D176" s="2">
         <v>305</v>
@@ -5180,7 +5180,7 @@
         <v>105</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D177" s="2">
         <v>254</v>
@@ -5206,7 +5206,7 @@
         <v>105</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D178" s="2">
         <v>312</v>
@@ -5232,7 +5232,7 @@
         <v>105</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D179" s="2">
         <v>115</v>
@@ -5258,7 +5258,7 @@
         <v>105</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D180" s="2">
         <v>161</v>
@@ -5284,7 +5284,7 @@
         <v>105</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D181" s="2">
         <v>240</v>
@@ -5310,7 +5310,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -5336,7 +5336,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5362,7 +5362,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5388,7 +5388,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5414,7 +5414,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -5440,7 +5440,7 @@
         <v>106</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D187" s="2">
         <v>342</v>
@@ -5466,7 +5466,7 @@
         <v>106</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D188" s="2">
         <v>285</v>
@@ -5492,7 +5492,7 @@
         <v>106</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D189" s="2">
         <v>453</v>
@@ -5518,7 +5518,7 @@
         <v>106</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D190" s="2">
         <v>69</v>
@@ -5544,7 +5544,7 @@
         <v>106</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D191" s="2">
         <v>154</v>
@@ -5570,7 +5570,7 @@
         <v>106</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D192" s="2">
         <v>246</v>
@@ -5596,7 +5596,7 @@
         <v>106</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D193" s="2">
         <v>446</v>
@@ -5622,7 +5622,7 @@
         <v>106</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D194" s="2">
         <v>467</v>
@@ -5648,7 +5648,7 @@
         <v>106</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D195" s="2">
         <v>374</v>
@@ -5674,7 +5674,7 @@
         <v>106</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D196" s="2">
         <v>266</v>
@@ -5700,7 +5700,7 @@
         <v>106</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D197" s="2">
         <v>281</v>
@@ -5726,7 +5726,7 @@
         <v>106</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D198" s="2">
         <v>277</v>
@@ -5752,7 +5752,7 @@
         <v>106</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D199" s="2">
         <v>153</v>
@@ -5778,7 +5778,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D200" s="2">
         <v>176</v>
@@ -5804,7 +5804,7 @@
         <v>106</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D201" s="2">
         <v>281</v>
@@ -5830,7 +5830,7 @@
         <v>106</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D202" s="2">
         <v>52</v>
@@ -5856,7 +5856,7 @@
         <v>106</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D203" s="2">
         <v>94</v>
@@ -5882,7 +5882,7 @@
         <v>106</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D204" s="2">
         <v>181</v>
@@ -5908,7 +5908,7 @@
         <v>106</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D205" s="2">
         <v>336</v>
@@ -5934,7 +5934,7 @@
         <v>106</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D206" s="2">
         <v>349</v>
@@ -5960,7 +5960,7 @@
         <v>106</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D207" s="2">
         <v>127</v>
@@ -5986,7 +5986,7 @@
         <v>106</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D208" s="2">
         <v>376</v>
@@ -6012,7 +6012,7 @@
         <v>106</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D209" s="2">
         <v>98</v>
@@ -6038,7 +6038,7 @@
         <v>106</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D210" s="2">
         <v>152</v>
@@ -6064,7 +6064,7 @@
         <v>106</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D211" s="2">
         <v>235</v>
@@ -6090,7 +6090,7 @@
         <v>106</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D212" s="2">
         <v>105</v>
@@ -6116,7 +6116,7 @@
         <v>106</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D213" s="2">
         <v>150</v>
@@ -6142,7 +6142,7 @@
         <v>106</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D214" s="2">
         <v>215</v>
@@ -6168,7 +6168,7 @@
         <v>106</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D215" s="2">
         <v>216</v>
@@ -6194,7 +6194,7 @@
         <v>106</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D216" s="2">
         <v>214</v>
@@ -6220,7 +6220,7 @@
         <v>106</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D217" s="2">
         <v>194</v>
@@ -6246,7 +6246,7 @@
         <v>107</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D218" s="2">
         <v>184</v>
@@ -6272,7 +6272,7 @@
         <v>107</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D219" s="2">
         <v>379</v>
@@ -6298,7 +6298,7 @@
         <v>107</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D220" s="2">
         <v>424</v>
@@ -6324,7 +6324,7 @@
         <v>107</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D221" s="2">
         <v>93</v>
@@ -6350,7 +6350,7 @@
         <v>107</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D222" s="2">
         <v>219</v>
@@ -6376,7 +6376,7 @@
         <v>107</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D223" s="2">
         <v>165</v>
@@ -6402,7 +6402,7 @@
         <v>107</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D224" s="2">
         <v>462</v>
@@ -6428,7 +6428,7 @@
         <v>107</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D225" s="2">
         <v>332</v>
@@ -6454,7 +6454,7 @@
         <v>107</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D226" s="2">
         <v>162</v>
@@ -6480,7 +6480,7 @@
         <v>107</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D227" s="2">
         <v>305</v>
@@ -6506,7 +6506,7 @@
         <v>107</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D228" s="2">
         <v>446</v>
@@ -6532,7 +6532,7 @@
         <v>107</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D229" s="2">
         <v>196</v>
@@ -6558,7 +6558,7 @@
         <v>107</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D230" s="2">
         <v>443</v>
@@ -6584,7 +6584,7 @@
         <v>107</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D231" s="2">
         <v>158</v>
@@ -6610,7 +6610,7 @@
         <v>107</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D232" s="2">
         <v>191</v>
@@ -6636,7 +6636,7 @@
         <v>107</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D233" s="2">
         <v>321</v>
@@ -6662,7 +6662,7 @@
         <v>107</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D234" s="2">
         <v>316</v>
@@ -6688,7 +6688,7 @@
         <v>107</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D235" s="2">
         <v>71</v>
@@ -6714,7 +6714,7 @@
         <v>107</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D236" s="2">
         <v>171</v>
@@ -6740,7 +6740,7 @@
         <v>107</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D237" s="2">
         <v>450</v>
@@ -6766,7 +6766,7 @@
         <v>107</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D238" s="2">
         <v>354</v>
@@ -6792,7 +6792,7 @@
         <v>107</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D239" s="2">
         <v>475</v>
@@ -6818,7 +6818,7 @@
         <v>107</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D240" s="2">
         <v>130</v>
@@ -6844,7 +6844,7 @@
         <v>107</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D241" s="2">
         <v>140</v>
@@ -6870,7 +6870,7 @@
         <v>107</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D242" s="2">
         <v>253</v>
@@ -6896,7 +6896,7 @@
         <v>107</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D243" s="2">
         <v>246</v>
@@ -6922,7 +6922,7 @@
         <v>107</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D244" s="2">
         <v>297</v>
@@ -6948,7 +6948,7 @@
         <v>107</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D245" s="2">
         <v>201</v>
@@ -6974,7 +6974,7 @@
         <v>107</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D246" s="2">
         <v>339</v>
@@ -7000,7 +7000,7 @@
         <v>107</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D247" s="2">
         <v>132</v>
@@ -7026,7 +7026,7 @@
         <v>107</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D248" s="2">
         <v>239</v>
@@ -7052,7 +7052,7 @@
         <v>107</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D249" s="2">
         <v>169</v>
@@ -7078,7 +7078,7 @@
         <v>107</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D250" s="2">
         <v>217</v>
@@ -7104,7 +7104,7 @@
         <v>107</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D251" s="2">
         <v>340</v>
@@ -7130,7 +7130,7 @@
         <v>107</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D252" s="2">
         <v>192</v>
@@ -7156,7 +7156,7 @@
         <v>107</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D253" s="2">
         <v>243</v>
@@ -7182,7 +7182,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -7208,7 +7208,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7234,7 +7234,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -7260,7 +7260,7 @@
         <v>108</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D257" s="2">
         <v>451</v>
@@ -7286,7 +7286,7 @@
         <v>108</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D258" s="2">
         <v>183</v>
@@ -7312,7 +7312,7 @@
         <v>108</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D259" s="2">
         <v>311</v>
@@ -7338,7 +7338,7 @@
         <v>108</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D260" s="2">
         <v>365</v>
@@ -7364,7 +7364,7 @@
         <v>108</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D261" s="2">
         <v>411</v>
@@ -7390,7 +7390,7 @@
         <v>108</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D262" s="2">
         <v>130</v>
@@ -7416,7 +7416,7 @@
         <v>108</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D263" s="2">
         <v>69</v>
@@ -7442,7 +7442,7 @@
         <v>108</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D264" s="2">
         <v>391</v>
@@ -7468,7 +7468,7 @@
         <v>108</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D265" s="2">
         <v>475</v>
@@ -7494,7 +7494,7 @@
         <v>108</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D266" s="2">
         <v>386</v>
@@ -7520,7 +7520,7 @@
         <v>108</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D267" s="2">
         <v>345</v>
@@ -7546,7 +7546,7 @@
         <v>108</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D268" s="2">
         <v>57</v>
@@ -7572,7 +7572,7 @@
         <v>108</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D269" s="2">
         <v>489</v>
@@ -7598,7 +7598,7 @@
         <v>108</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D270" s="2">
         <v>88</v>
@@ -7624,7 +7624,7 @@
         <v>108</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D271" s="2">
         <v>417</v>
@@ -7650,7 +7650,7 @@
         <v>108</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D272" s="2">
         <v>437</v>
@@ -7676,7 +7676,7 @@
         <v>108</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D273" s="2">
         <v>249</v>
@@ -7702,7 +7702,7 @@
         <v>108</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D274" s="2">
         <v>86</v>
@@ -7728,7 +7728,7 @@
         <v>108</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D275" s="2">
         <v>191</v>
@@ -7754,7 +7754,7 @@
         <v>108</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D276" s="2">
         <v>298</v>
@@ -7780,7 +7780,7 @@
         <v>108</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D277" s="2">
         <v>235</v>
@@ -7806,7 +7806,7 @@
         <v>108</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D278" s="2">
         <v>201</v>
@@ -7832,7 +7832,7 @@
         <v>108</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D279" s="2">
         <v>158</v>
@@ -7858,7 +7858,7 @@
         <v>108</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D280" s="2">
         <v>135</v>
@@ -7884,7 +7884,7 @@
         <v>108</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D281" s="2">
         <v>333</v>
@@ -7910,7 +7910,7 @@
         <v>108</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D282" s="2">
         <v>352</v>
@@ -7936,7 +7936,7 @@
         <v>108</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D283" s="2">
         <v>66</v>
@@ -7962,7 +7962,7 @@
         <v>108</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D284" s="2">
         <v>116</v>
@@ -7988,7 +7988,7 @@
         <v>108</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D285" s="2">
         <v>214</v>
@@ -8014,7 +8014,7 @@
         <v>108</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D286" s="2">
         <v>210</v>
@@ -8040,7 +8040,7 @@
         <v>108</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D287" s="2">
         <v>295</v>
@@ -8066,7 +8066,7 @@
         <v>108</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D288" s="2">
         <v>112</v>
@@ -8092,7 +8092,7 @@
         <v>108</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D289" s="2">
         <v>222</v>
@@ -8118,7 +8118,7 @@
         <v>109</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D290" s="2">
         <v>212</v>
@@ -8144,7 +8144,7 @@
         <v>109</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D291" s="2">
         <v>457</v>
@@ -8170,7 +8170,7 @@
         <v>109</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D292" s="2">
         <v>203</v>
@@ -8196,7 +8196,7 @@
         <v>109</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D293" s="2">
         <v>247</v>
@@ -8222,7 +8222,7 @@
         <v>109</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D294" s="2">
         <v>113</v>
@@ -8248,7 +8248,7 @@
         <v>109</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D295" s="2">
         <v>107</v>
@@ -8274,7 +8274,7 @@
         <v>109</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D296" s="2">
         <v>338</v>
@@ -8300,7 +8300,7 @@
         <v>109</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D297" s="2">
         <v>259</v>
@@ -8326,7 +8326,7 @@
         <v>109</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D298" s="2">
         <v>430</v>
@@ -8352,7 +8352,7 @@
         <v>109</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D299" s="2">
         <v>329</v>
@@ -8378,7 +8378,7 @@
         <v>109</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D300" s="2">
         <v>369</v>
@@ -8404,7 +8404,7 @@
         <v>109</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D301" s="2">
         <v>262</v>
@@ -8430,7 +8430,7 @@
         <v>109</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D302" s="2">
         <v>253</v>
@@ -8456,7 +8456,7 @@
         <v>109</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D303" s="2">
         <v>257</v>
@@ -8482,7 +8482,7 @@
         <v>109</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D304" s="2">
         <v>446</v>
@@ -8508,7 +8508,7 @@
         <v>109</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D305" s="2">
         <v>270</v>
@@ -8534,7 +8534,7 @@
         <v>109</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D306" s="2">
         <v>486</v>
@@ -8560,7 +8560,7 @@
         <v>109</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D307" s="2">
         <v>484</v>
@@ -8586,7 +8586,7 @@
         <v>109</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D308" s="2">
         <v>277</v>
@@ -8612,7 +8612,7 @@
         <v>109</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D309" s="2">
         <v>298</v>
@@ -8638,7 +8638,7 @@
         <v>109</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D310" s="2">
         <v>148</v>
@@ -8664,7 +8664,7 @@
         <v>109</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D311" s="2">
         <v>218</v>
@@ -8690,7 +8690,7 @@
         <v>109</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D312" s="2">
         <v>253</v>
@@ -8716,7 +8716,7 @@
         <v>109</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D313" s="2">
         <v>266</v>
@@ -8742,7 +8742,7 @@
         <v>109</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D314" s="2">
         <v>290</v>
@@ -8768,7 +8768,7 @@
         <v>109</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D315" s="2">
         <v>197</v>
@@ -8794,7 +8794,7 @@
         <v>109</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D316" s="2">
         <v>160</v>
@@ -8820,7 +8820,7 @@
         <v>109</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D317" s="2">
         <v>272</v>
@@ -8846,7 +8846,7 @@
         <v>109</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D318" s="2">
         <v>254</v>
@@ -8872,7 +8872,7 @@
         <v>109</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D319" s="2">
         <v>160</v>
@@ -8898,7 +8898,7 @@
         <v>109</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D320" s="2">
         <v>150</v>
@@ -8924,7 +8924,7 @@
         <v>109</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D321" s="2">
         <v>247</v>
@@ -8950,7 +8950,7 @@
         <v>109</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D322" s="2">
         <v>263</v>
@@ -8976,7 +8976,7 @@
         <v>109</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D323" s="2">
         <v>267</v>
@@ -9002,7 +9002,7 @@
         <v>109</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D324" s="2">
         <v>223</v>
@@ -9028,7 +9028,7 @@
         <v>109</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D325" s="2">
         <v>170</v>
@@ -9054,7 +9054,7 @@
         <v>110</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D326" s="2">
         <v>175</v>
@@ -9080,7 +9080,7 @@
         <v>110</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D327" s="2">
         <v>333</v>
@@ -9106,7 +9106,7 @@
         <v>110</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D328" s="2">
         <v>442</v>
@@ -9132,7 +9132,7 @@
         <v>110</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D329" s="2">
         <v>131</v>
@@ -9158,7 +9158,7 @@
         <v>110</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D330" s="2">
         <v>275</v>
@@ -9184,7 +9184,7 @@
         <v>110</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D331" s="2">
         <v>170</v>
@@ -9210,7 +9210,7 @@
         <v>110</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D332" s="2">
         <v>94</v>
@@ -9236,7 +9236,7 @@
         <v>110</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D333" s="2">
         <v>56</v>
@@ -9262,7 +9262,7 @@
         <v>110</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D334" s="2">
         <v>297</v>
@@ -9288,7 +9288,7 @@
         <v>110</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D335" s="2">
         <v>389</v>
@@ -9314,7 +9314,7 @@
         <v>110</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D336" s="2">
         <v>88</v>
@@ -9340,7 +9340,7 @@
         <v>110</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D337" s="2">
         <v>101</v>
@@ -9366,7 +9366,7 @@
         <v>110</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D338" s="2">
         <v>237</v>
@@ -9392,7 +9392,7 @@
         <v>110</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D339" s="2">
         <v>251</v>
@@ -9418,7 +9418,7 @@
         <v>110</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D340" s="2">
         <v>62</v>
@@ -9444,7 +9444,7 @@
         <v>110</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D341" s="2">
         <v>144</v>
@@ -9470,7 +9470,7 @@
         <v>110</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D342" s="2">
         <v>180</v>
@@ -9496,7 +9496,7 @@
         <v>110</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D343" s="2">
         <v>358</v>
@@ -9522,7 +9522,7 @@
         <v>110</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D344" s="2">
         <v>452</v>
@@ -9548,7 +9548,7 @@
         <v>110</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D345" s="2">
         <v>121</v>
@@ -9574,7 +9574,7 @@
         <v>110</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D346" s="2">
         <v>354</v>
@@ -9600,7 +9600,7 @@
         <v>110</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D347" s="2">
         <v>151</v>
@@ -9626,7 +9626,7 @@
         <v>110</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D348" s="2">
         <v>270</v>
@@ -9652,7 +9652,7 @@
         <v>110</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D349" s="2">
         <v>361</v>
@@ -9678,7 +9678,7 @@
         <v>110</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D350" s="2">
         <v>148</v>
@@ -9704,7 +9704,7 @@
         <v>110</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D351" s="2">
         <v>223</v>
@@ -9730,7 +9730,7 @@
         <v>110</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D352" s="2">
         <v>79</v>
@@ -9756,7 +9756,7 @@
         <v>110</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D353" s="2">
         <v>104</v>
@@ -9782,7 +9782,7 @@
         <v>110</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D354" s="2">
         <v>294</v>
@@ -9808,7 +9808,7 @@
         <v>110</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D355" s="2">
         <v>248</v>
@@ -9834,7 +9834,7 @@
         <v>110</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D356" s="2">
         <v>215</v>
@@ -9860,7 +9860,7 @@
         <v>110</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D357" s="2">
         <v>258</v>
@@ -9886,7 +9886,7 @@
         <v>110</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D358" s="2">
         <v>201</v>
@@ -9912,7 +9912,7 @@
         <v>110</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D359" s="2">
         <v>238</v>
@@ -9938,7 +9938,7 @@
         <v>110</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D360" s="2">
         <v>286</v>
@@ -9964,7 +9964,7 @@
         <v>110</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D361" s="2">
         <v>386</v>
@@ -9990,7 +9990,7 @@
         <v>111</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D362" s="2">
         <v>497</v>
@@ -10016,7 +10016,7 @@
         <v>111</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D363" s="2">
         <v>372</v>
@@ -10042,7 +10042,7 @@
         <v>111</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D364" s="2">
         <v>377</v>
@@ -10068,7 +10068,7 @@
         <v>111</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D365" s="2">
         <v>450</v>
@@ -10094,7 +10094,7 @@
         <v>111</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D366" s="2">
         <v>381</v>
@@ -10120,7 +10120,7 @@
         <v>111</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D367" s="2">
         <v>132</v>
@@ -10146,7 +10146,7 @@
         <v>111</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D368" s="2">
         <v>160</v>
@@ -10172,7 +10172,7 @@
         <v>111</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D369" s="2">
         <v>80</v>
@@ -10198,7 +10198,7 @@
         <v>111</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D370" s="2">
         <v>124</v>
@@ -10224,7 +10224,7 @@
         <v>111</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D371" s="2">
         <v>468</v>
@@ -10250,7 +10250,7 @@
         <v>111</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D372" s="2">
         <v>131</v>
@@ -10276,7 +10276,7 @@
         <v>111</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D373" s="2">
         <v>171</v>
@@ -10302,7 +10302,7 @@
         <v>111</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D374" s="2">
         <v>470</v>
@@ -10328,7 +10328,7 @@
         <v>111</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D375" s="2">
         <v>423</v>
@@ -10354,7 +10354,7 @@
         <v>111</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D376" s="2">
         <v>392</v>
@@ -10380,7 +10380,7 @@
         <v>111</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D377" s="2">
         <v>330</v>
@@ -10406,7 +10406,7 @@
         <v>111</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D378" s="2">
         <v>287</v>
@@ -10432,7 +10432,7 @@
         <v>111</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D379" s="2">
         <v>171</v>
@@ -10458,7 +10458,7 @@
         <v>111</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D380" s="2">
         <v>470</v>
@@ -10484,7 +10484,7 @@
         <v>111</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D381" s="2">
         <v>345</v>
@@ -10510,7 +10510,7 @@
         <v>111</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D382" s="2">
         <v>78</v>
@@ -10536,7 +10536,7 @@
         <v>111</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D383" s="2">
         <v>389</v>
@@ -10562,7 +10562,7 @@
         <v>111</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D384" s="2">
         <v>129</v>
@@ -10588,7 +10588,7 @@
         <v>111</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D385" s="2">
         <v>449</v>
@@ -10614,7 +10614,7 @@
         <v>111</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D386" s="2">
         <v>224</v>
@@ -10640,7 +10640,7 @@
         <v>111</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D387" s="2">
         <v>99</v>
@@ -10666,7 +10666,7 @@
         <v>111</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D388" s="2">
         <v>84</v>
@@ -10692,7 +10692,7 @@
         <v>111</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D389" s="2">
         <v>206</v>
@@ -10718,7 +10718,7 @@
         <v>111</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D390" s="2">
         <v>356</v>
@@ -10744,7 +10744,7 @@
         <v>111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D391" s="2">
         <v>370</v>
@@ -10770,7 +10770,7 @@
         <v>111</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D392" s="2">
         <v>211</v>
@@ -10796,7 +10796,7 @@
         <v>111</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D393" s="2">
         <v>198</v>
@@ -10822,7 +10822,7 @@
         <v>111</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D394" s="2">
         <v>246</v>
@@ -10848,7 +10848,7 @@
         <v>111</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D395" s="2">
         <v>119</v>
@@ -10874,7 +10874,7 @@
         <v>111</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D396" s="2">
         <v>228</v>
@@ -10900,7 +10900,7 @@
         <v>111</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D397" s="2">
         <v>166</v>
@@ -10926,7 +10926,7 @@
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D398" s="2">
         <v>421</v>
@@ -10952,7 +10952,7 @@
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D399" s="2">
         <v>99</v>
@@ -10978,7 +10978,7 @@
         <v>112</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D400" s="2">
         <v>474</v>
@@ -11004,7 +11004,7 @@
         <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D401" s="2">
         <v>398</v>
@@ -11030,7 +11030,7 @@
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D402" s="2">
         <v>147</v>
@@ -11056,7 +11056,7 @@
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D403" s="2">
         <v>443</v>
@@ -11082,7 +11082,7 @@
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D404" s="2">
         <v>259</v>
@@ -11108,7 +11108,7 @@
         <v>112</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D405" s="2">
         <v>264</v>
@@ -11134,7 +11134,7 @@
         <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D406" s="2">
         <v>450</v>
@@ -11160,7 +11160,7 @@
         <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D407" s="2">
         <v>490</v>
@@ -11186,7 +11186,7 @@
         <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D408" s="2">
         <v>457</v>
@@ -11212,7 +11212,7 @@
         <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D409" s="2">
         <v>481</v>
@@ -11238,7 +11238,7 @@
         <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D410" s="2">
         <v>452</v>
@@ -11264,7 +11264,7 @@
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D411" s="2">
         <v>194</v>
@@ -11290,7 +11290,7 @@
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D412" s="2">
         <v>399</v>
@@ -11316,7 +11316,7 @@
         <v>112</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D413" s="2">
         <v>264</v>
@@ -11342,7 +11342,7 @@
         <v>112</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D414" s="2">
         <v>109</v>
@@ -11368,7 +11368,7 @@
         <v>112</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D415" s="2">
         <v>437</v>
@@ -11394,7 +11394,7 @@
         <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D416" s="2">
         <v>447</v>
@@ -11420,7 +11420,7 @@
         <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D417" s="2">
         <v>421</v>
@@ -11446,7 +11446,7 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D418" s="2">
         <v>80</v>
@@ -11472,7 +11472,7 @@
         <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D419" s="2">
         <v>493</v>
@@ -11498,7 +11498,7 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D420" s="2">
         <v>105</v>
@@ -11524,7 +11524,7 @@
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D421" s="2">
         <v>432</v>
@@ -11550,7 +11550,7 @@
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D422" s="2">
         <v>332</v>
@@ -11576,7 +11576,7 @@
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D423" s="2">
         <v>238</v>
@@ -11602,7 +11602,7 @@
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D424" s="2">
         <v>300</v>
@@ -11628,7 +11628,7 @@
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D425" s="2">
         <v>249</v>
@@ -11654,7 +11654,7 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D426" s="2">
         <v>336</v>
@@ -11680,7 +11680,7 @@
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D427" s="2">
         <v>114</v>
@@ -11706,7 +11706,7 @@
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D428" s="2">
         <v>175</v>
@@ -11732,7 +11732,7 @@
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D429" s="2">
         <v>473</v>
@@ -11758,7 +11758,7 @@
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D430" s="2">
         <v>202</v>
@@ -11784,7 +11784,7 @@
         <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D431" s="2">
         <v>215</v>
@@ -11810,7 +11810,7 @@
         <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D432" s="2">
         <v>252</v>
@@ -11836,7 +11836,7 @@
         <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D433" s="2">
         <v>223</v>
@@ -11862,7 +11862,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>
@@ -11888,7 +11888,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11914,7 +11914,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11940,7 +11940,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>
@@ -11966,7 +11966,7 @@
         <v>113</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D438" s="2">
         <v>219</v>
@@ -11992,7 +11992,7 @@
         <v>113</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D439" s="2">
         <v>99</v>
@@ -12018,7 +12018,7 @@
         <v>113</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D440" s="2">
         <v>177</v>
@@ -12044,7 +12044,7 @@
         <v>113</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D441" s="2">
         <v>380</v>
@@ -12070,7 +12070,7 @@
         <v>113</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D442" s="2">
         <v>464</v>
@@ -12096,7 +12096,7 @@
         <v>113</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D443" s="2">
         <v>460</v>
@@ -12122,7 +12122,7 @@
         <v>113</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D444" s="2">
         <v>299</v>
@@ -12148,7 +12148,7 @@
         <v>113</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D445" s="2">
         <v>243</v>
@@ -12174,7 +12174,7 @@
         <v>113</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D446" s="2">
         <v>154</v>
@@ -12200,7 +12200,7 @@
         <v>113</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D447" s="2">
         <v>239</v>
@@ -12226,7 +12226,7 @@
         <v>113</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D448" s="2">
         <v>410</v>
@@ -12252,7 +12252,7 @@
         <v>113</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D449" s="2">
         <v>273</v>
@@ -12278,7 +12278,7 @@
         <v>113</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D450" s="2">
         <v>90</v>
@@ -12304,7 +12304,7 @@
         <v>113</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D451" s="2">
         <v>407</v>
@@ -12330,7 +12330,7 @@
         <v>113</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D452" s="2">
         <v>301</v>
@@ -12356,7 +12356,7 @@
         <v>113</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D453" s="2">
         <v>181</v>
@@ -12382,7 +12382,7 @@
         <v>113</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D454" s="2">
         <v>186</v>
@@ -12408,7 +12408,7 @@
         <v>113</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D455" s="2">
         <v>424</v>
@@ -12434,7 +12434,7 @@
         <v>113</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D456" s="2">
         <v>268</v>
@@ -12460,7 +12460,7 @@
         <v>113</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D457" s="2">
         <v>277</v>
@@ -12486,7 +12486,7 @@
         <v>113</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D458" s="2">
         <v>89</v>
@@ -12512,7 +12512,7 @@
         <v>113</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D459" s="2">
         <v>219</v>
@@ -12538,7 +12538,7 @@
         <v>113</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D460" s="2">
         <v>273</v>
@@ -12564,7 +12564,7 @@
         <v>113</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D461" s="2">
         <v>254</v>
@@ -12590,7 +12590,7 @@
         <v>113</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D462" s="2">
         <v>243</v>
@@ -12616,7 +12616,7 @@
         <v>113</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D463" s="2">
         <v>349</v>
@@ -12642,7 +12642,7 @@
         <v>113</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D464" s="2">
         <v>245</v>
@@ -12668,7 +12668,7 @@
         <v>113</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D465" s="2">
         <v>174</v>
@@ -12694,7 +12694,7 @@
         <v>113</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D466" s="2">
         <v>80</v>
@@ -12720,7 +12720,7 @@
         <v>113</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D467" s="2">
         <v>210</v>
@@ -12746,7 +12746,7 @@
         <v>113</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D468" s="2">
         <v>281</v>
@@ -12772,7 +12772,7 @@
         <v>113</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D469" s="2">
         <v>80</v>
@@ -12798,7 +12798,7 @@
         <v>114</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D470" s="2">
         <v>106</v>
@@ -12824,7 +12824,7 @@
         <v>114</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D471" s="2">
         <v>53</v>
@@ -12850,7 +12850,7 @@
         <v>114</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D472" s="2">
         <v>80</v>
@@ -12876,7 +12876,7 @@
         <v>114</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D473" s="2">
         <v>92</v>
@@ -12902,7 +12902,7 @@
         <v>114</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D474" s="2">
         <v>146</v>
@@ -12928,7 +12928,7 @@
         <v>114</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D475" s="2">
         <v>465</v>
@@ -12954,7 +12954,7 @@
         <v>114</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D476" s="2">
         <v>361</v>
@@ -12980,7 +12980,7 @@
         <v>114</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D477" s="2">
         <v>420</v>
@@ -13006,7 +13006,7 @@
         <v>114</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D478" s="2">
         <v>471</v>
@@ -13032,7 +13032,7 @@
         <v>114</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D479" s="2">
         <v>174</v>
@@ -13058,7 +13058,7 @@
         <v>114</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D480" s="2">
         <v>95</v>
@@ -13084,7 +13084,7 @@
         <v>114</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D481" s="2">
         <v>305</v>
@@ -13110,7 +13110,7 @@
         <v>114</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D482" s="2">
         <v>465</v>
@@ -13136,7 +13136,7 @@
         <v>114</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D483" s="2">
         <v>418</v>
@@ -13162,7 +13162,7 @@
         <v>114</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D484" s="2">
         <v>478</v>
@@ -13188,7 +13188,7 @@
         <v>114</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D485" s="2">
         <v>434</v>
@@ -13214,7 +13214,7 @@
         <v>114</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D486" s="2">
         <v>459</v>
@@ -13240,7 +13240,7 @@
         <v>114</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D487" s="2">
         <v>99</v>
@@ -13266,7 +13266,7 @@
         <v>114</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D488" s="2">
         <v>104</v>
@@ -13292,7 +13292,7 @@
         <v>114</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D489" s="2">
         <v>166</v>
@@ -13318,7 +13318,7 @@
         <v>114</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D490" s="2">
         <v>277</v>
@@ -13344,7 +13344,7 @@
         <v>114</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D491" s="2">
         <v>329</v>
@@ -13370,7 +13370,7 @@
         <v>114</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D492" s="2">
         <v>193</v>
@@ -13396,7 +13396,7 @@
         <v>114</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D493" s="2">
         <v>70</v>
@@ -13422,7 +13422,7 @@
         <v>114</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D494" s="2">
         <v>174</v>
@@ -13448,7 +13448,7 @@
         <v>114</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D495" s="2">
         <v>305</v>
@@ -13474,7 +13474,7 @@
         <v>114</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D496" s="2">
         <v>274</v>
@@ -13500,7 +13500,7 @@
         <v>114</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D497" s="2">
         <v>185</v>
@@ -13526,7 +13526,7 @@
         <v>114</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D498" s="2">
         <v>249</v>
@@ -13552,7 +13552,7 @@
         <v>114</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D499" s="2">
         <v>203</v>
@@ -13578,7 +13578,7 @@
         <v>114</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D500" s="2">
         <v>315</v>
@@ -13604,7 +13604,7 @@
         <v>114</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D501" s="2">
         <v>211</v>
@@ -13630,7 +13630,7 @@
         <v>114</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D502" s="2">
         <v>262</v>
@@ -13656,7 +13656,7 @@
         <v>114</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D503" s="2">
         <v>346</v>
@@ -13682,7 +13682,7 @@
         <v>114</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D504" s="2">
         <v>232</v>
@@ -13708,7 +13708,7 @@
         <v>114</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D505" s="2">
         <v>142</v>
@@ -13734,7 +13734,7 @@
         <v>115</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D506" s="2">
         <v>316</v>
@@ -13760,7 +13760,7 @@
         <v>115</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D507" s="2">
         <v>221</v>
@@ -13786,7 +13786,7 @@
         <v>115</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D508" s="2">
         <v>318</v>
@@ -13812,7 +13812,7 @@
         <v>115</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D509" s="2">
         <v>147</v>
@@ -13838,7 +13838,7 @@
         <v>115</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D510" s="2">
         <v>396</v>
@@ -13864,7 +13864,7 @@
         <v>115</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D511" s="2">
         <v>409</v>
@@ -13890,7 +13890,7 @@
         <v>115</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D512" s="2">
         <v>278</v>
@@ -13916,7 +13916,7 @@
         <v>115</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D513" s="2">
         <v>103</v>
@@ -13942,7 +13942,7 @@
         <v>115</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D514" s="2">
         <v>419</v>
@@ -13968,7 +13968,7 @@
         <v>115</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D515" s="2">
         <v>243</v>
@@ -13994,7 +13994,7 @@
         <v>115</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D516" s="2">
         <v>280</v>
@@ -14020,7 +14020,7 @@
         <v>115</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D517" s="2">
         <v>206</v>
@@ -14046,7 +14046,7 @@
         <v>115</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D518" s="2">
         <v>114</v>
@@ -14072,7 +14072,7 @@
         <v>115</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D519" s="2">
         <v>58</v>
@@ -14098,7 +14098,7 @@
         <v>115</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D520" s="2">
         <v>198</v>
@@ -14124,7 +14124,7 @@
         <v>115</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D521" s="2">
         <v>138</v>
@@ -14150,7 +14150,7 @@
         <v>115</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D522" s="2">
         <v>417</v>
@@ -14176,7 +14176,7 @@
         <v>115</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D523" s="2">
         <v>141</v>
@@ -14202,7 +14202,7 @@
         <v>115</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D524" s="2">
         <v>456</v>
@@ -14228,7 +14228,7 @@
         <v>115</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D525" s="2">
         <v>316</v>
@@ -14254,7 +14254,7 @@
         <v>115</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D526" s="2">
         <v>357</v>
@@ -14280,7 +14280,7 @@
         <v>115</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D527" s="2">
         <v>143</v>
@@ -14306,7 +14306,7 @@
         <v>115</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D528" s="2">
         <v>177</v>
@@ -14332,7 +14332,7 @@
         <v>115</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D529" s="2">
         <v>226</v>
@@ -14358,7 +14358,7 @@
         <v>115</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D530" s="2">
         <v>344</v>
@@ -14384,7 +14384,7 @@
         <v>115</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D531" s="2">
         <v>143</v>
@@ -14410,7 +14410,7 @@
         <v>115</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D532" s="2">
         <v>97</v>
@@ -14436,7 +14436,7 @@
         <v>115</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D533" s="2">
         <v>193</v>
@@ -14462,7 +14462,7 @@
         <v>115</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D534" s="2">
         <v>56</v>
@@ -14488,7 +14488,7 @@
         <v>115</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D535" s="2">
         <v>121</v>
@@ -14514,7 +14514,7 @@
         <v>115</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D536" s="2">
         <v>150</v>
@@ -14540,7 +14540,7 @@
         <v>115</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D537" s="2">
         <v>344</v>
@@ -14566,7 +14566,7 @@
         <v>115</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D538" s="2">
         <v>188</v>
@@ -14592,7 +14592,7 @@
         <v>115</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D539" s="2">
         <v>342</v>
@@ -14618,7 +14618,7 @@
         <v>115</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D540" s="2">
         <v>234</v>
@@ -14644,7 +14644,7 @@
         <v>115</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D541" s="2">
         <v>239</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="63">
   <si>
     <t>Month</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>Butter</t>
-  </si>
-  <si>
-    <t>Yogurt</t>
   </si>
   <si>
     <t>Juice</t>
@@ -630,7 +627,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2">
         <v>373</v>
@@ -656,7 +653,7 @@
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2">
         <v>423</v>
@@ -682,7 +679,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2">
         <v>147</v>
@@ -708,7 +705,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2">
         <v>431</v>
@@ -734,7 +731,7 @@
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2">
         <v>305</v>
@@ -760,7 +757,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="2">
         <v>167</v>
@@ -786,7 +783,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2">
         <v>101</v>
@@ -812,7 +809,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="2">
         <v>73</v>
@@ -838,7 +835,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="2">
         <v>445</v>
@@ -864,7 +861,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2">
         <v>180</v>
@@ -890,7 +887,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2">
         <v>221</v>
@@ -916,7 +913,7 @@
         <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" s="2">
         <v>153</v>
@@ -942,7 +939,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="2">
         <v>283</v>
@@ -968,7 +965,7 @@
         <v>101</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" s="2">
         <v>220</v>
@@ -994,7 +991,7 @@
         <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" s="2">
         <v>338</v>
@@ -1020,7 +1017,7 @@
         <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" s="2">
         <v>209</v>
@@ -1046,7 +1043,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="2">
         <v>186</v>
@@ -1072,7 +1069,7 @@
         <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="2">
         <v>383</v>
@@ -1098,7 +1095,7 @@
         <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2">
         <v>253</v>
@@ -1124,7 +1121,7 @@
         <v>101</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" s="2">
         <v>159</v>
@@ -1150,7 +1147,7 @@
         <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D22" s="2">
         <v>212</v>
@@ -1176,7 +1173,7 @@
         <v>101</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" s="2">
         <v>377</v>
@@ -1202,7 +1199,7 @@
         <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D24" s="2">
         <v>126</v>
@@ -1228,7 +1225,7 @@
         <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2">
         <v>283</v>
@@ -1254,7 +1251,7 @@
         <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="2">
         <v>235</v>
@@ -1280,7 +1277,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D27" s="2">
         <v>170</v>
@@ -1306,7 +1303,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D28" s="2">
         <v>321</v>
@@ -1332,7 +1329,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D29" s="2">
         <v>127</v>
@@ -1358,7 +1355,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D30" s="2">
         <v>162</v>
@@ -1384,7 +1381,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D31" s="2">
         <v>265</v>
@@ -1410,7 +1407,7 @@
         <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D32" s="2">
         <v>193</v>
@@ -1436,7 +1433,7 @@
         <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D33" s="2">
         <v>211</v>
@@ -1462,7 +1459,7 @@
         <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="2">
         <v>328</v>
@@ -1488,7 +1485,7 @@
         <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" s="2">
         <v>127</v>
@@ -1514,7 +1511,7 @@
         <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D36" s="2">
         <v>176</v>
@@ -1540,7 +1537,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D37" s="2">
         <v>278</v>
@@ -1566,7 +1563,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1592,7 +1589,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1618,7 +1615,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1644,7 +1641,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1670,7 +1667,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1696,7 +1693,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1722,7 +1719,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1748,7 +1745,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1774,7 +1771,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1800,7 +1797,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1826,7 +1823,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1852,7 +1849,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1878,7 +1875,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1904,7 +1901,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1930,7 +1927,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1956,7 +1953,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1982,7 +1979,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -2008,7 +2005,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2034,7 +2031,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2060,7 +2057,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2086,7 +2083,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2112,7 +2109,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2138,7 +2135,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2164,7 +2161,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2190,7 +2187,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2216,7 +2213,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2242,7 +2239,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2268,7 +2265,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2294,7 +2291,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2320,7 +2317,7 @@
         <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D67" s="2">
         <v>259</v>
@@ -2346,7 +2343,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>
@@ -2372,7 +2369,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D69" s="2">
         <v>173</v>
@@ -2398,7 +2395,7 @@
         <v>102</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D70" s="2">
         <v>186</v>
@@ -2424,7 +2421,7 @@
         <v>102</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D71" s="2">
         <v>274</v>
@@ -2450,7 +2447,7 @@
         <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D72" s="2">
         <v>238</v>
@@ -2476,7 +2473,7 @@
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D73" s="2">
         <v>109</v>
@@ -3438,7 +3435,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3464,7 +3461,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3490,7 +3487,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3516,7 +3513,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3542,7 +3539,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3568,7 +3565,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3594,7 +3591,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3620,7 +3617,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3646,7 +3643,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3672,7 +3669,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3698,7 +3695,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>
@@ -3724,7 +3721,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3750,7 +3747,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3776,7 +3773,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3802,7 +3799,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3828,7 +3825,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3854,7 +3851,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -3880,7 +3877,7 @@
         <v>104</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D127" s="2">
         <v>141</v>
@@ -3906,7 +3903,7 @@
         <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D128" s="2">
         <v>303</v>
@@ -3932,7 +3929,7 @@
         <v>104</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D129" s="2">
         <v>281</v>
@@ -3958,7 +3955,7 @@
         <v>104</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D130" s="2">
         <v>453</v>
@@ -3984,7 +3981,7 @@
         <v>104</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D131" s="2">
         <v>310</v>
@@ -4010,7 +4007,7 @@
         <v>104</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D132" s="2">
         <v>243</v>
@@ -4036,7 +4033,7 @@
         <v>104</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D133" s="2">
         <v>248</v>
@@ -4062,7 +4059,7 @@
         <v>104</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D134" s="2">
         <v>253</v>
@@ -4088,7 +4085,7 @@
         <v>104</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D135" s="2">
         <v>197</v>
@@ -4114,7 +4111,7 @@
         <v>104</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D136" s="2">
         <v>184</v>
@@ -4140,7 +4137,7 @@
         <v>104</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D137" s="2">
         <v>119</v>
@@ -4166,7 +4163,7 @@
         <v>104</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D138" s="2">
         <v>192</v>
@@ -4192,7 +4189,7 @@
         <v>104</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D139" s="2">
         <v>237</v>
@@ -4218,7 +4215,7 @@
         <v>104</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D140" s="2">
         <v>71</v>
@@ -4244,7 +4241,7 @@
         <v>104</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D141" s="2">
         <v>170</v>
@@ -4270,7 +4267,7 @@
         <v>104</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D142" s="2">
         <v>201</v>
@@ -4296,7 +4293,7 @@
         <v>104</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D143" s="2">
         <v>226</v>
@@ -4322,7 +4319,7 @@
         <v>104</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D144" s="2">
         <v>251</v>
@@ -4348,7 +4345,7 @@
         <v>104</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D145" s="2">
         <v>281</v>
@@ -5310,7 +5307,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -5336,7 +5333,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5362,7 +5359,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5388,7 +5385,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5414,7 +5411,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -7182,7 +7179,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -7208,7 +7205,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7234,7 +7231,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -9054,7 +9051,7 @@
         <v>110</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D326" s="2">
         <v>175</v>
@@ -9080,7 +9077,7 @@
         <v>110</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D327" s="2">
         <v>333</v>
@@ -9106,7 +9103,7 @@
         <v>110</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D328" s="2">
         <v>442</v>
@@ -9132,7 +9129,7 @@
         <v>110</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D329" s="2">
         <v>131</v>
@@ -9158,7 +9155,7 @@
         <v>110</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D330" s="2">
         <v>275</v>
@@ -9184,7 +9181,7 @@
         <v>110</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D331" s="2">
         <v>170</v>
@@ -9210,7 +9207,7 @@
         <v>110</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D332" s="2">
         <v>94</v>
@@ -9236,7 +9233,7 @@
         <v>110</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D333" s="2">
         <v>56</v>
@@ -9262,7 +9259,7 @@
         <v>110</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D334" s="2">
         <v>297</v>
@@ -9288,7 +9285,7 @@
         <v>110</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D335" s="2">
         <v>389</v>
@@ -9314,7 +9311,7 @@
         <v>110</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D336" s="2">
         <v>88</v>
@@ -9340,7 +9337,7 @@
         <v>110</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D337" s="2">
         <v>101</v>
@@ -9366,7 +9363,7 @@
         <v>110</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D338" s="2">
         <v>237</v>
@@ -9392,7 +9389,7 @@
         <v>110</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D339" s="2">
         <v>251</v>
@@ -9418,7 +9415,7 @@
         <v>110</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D340" s="2">
         <v>62</v>
@@ -9444,7 +9441,7 @@
         <v>110</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D341" s="2">
         <v>144</v>
@@ -9470,7 +9467,7 @@
         <v>110</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D342" s="2">
         <v>180</v>
@@ -9496,7 +9493,7 @@
         <v>110</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D343" s="2">
         <v>358</v>
@@ -9522,7 +9519,7 @@
         <v>110</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D344" s="2">
         <v>452</v>
@@ -9548,7 +9545,7 @@
         <v>110</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D345" s="2">
         <v>121</v>
@@ -9574,7 +9571,7 @@
         <v>110</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D346" s="2">
         <v>354</v>
@@ -9600,7 +9597,7 @@
         <v>110</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D347" s="2">
         <v>151</v>
@@ -9626,7 +9623,7 @@
         <v>110</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D348" s="2">
         <v>270</v>
@@ -9652,7 +9649,7 @@
         <v>110</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D349" s="2">
         <v>361</v>
@@ -9678,7 +9675,7 @@
         <v>110</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D350" s="2">
         <v>148</v>
@@ -9704,7 +9701,7 @@
         <v>110</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D351" s="2">
         <v>223</v>
@@ -9730,7 +9727,7 @@
         <v>110</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D352" s="2">
         <v>79</v>
@@ -9756,7 +9753,7 @@
         <v>110</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D353" s="2">
         <v>104</v>
@@ -9782,7 +9779,7 @@
         <v>110</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D354" s="2">
         <v>294</v>
@@ -9808,7 +9805,7 @@
         <v>110</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D355" s="2">
         <v>248</v>
@@ -9834,7 +9831,7 @@
         <v>110</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D356" s="2">
         <v>215</v>
@@ -9860,7 +9857,7 @@
         <v>110</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D357" s="2">
         <v>258</v>
@@ -9886,7 +9883,7 @@
         <v>110</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D358" s="2">
         <v>201</v>
@@ -9912,7 +9909,7 @@
         <v>110</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D359" s="2">
         <v>238</v>
@@ -9938,7 +9935,7 @@
         <v>110</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D360" s="2">
         <v>286</v>
@@ -9964,7 +9961,7 @@
         <v>110</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D361" s="2">
         <v>386</v>
@@ -9990,7 +9987,7 @@
         <v>111</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D362" s="2">
         <v>497</v>
@@ -10016,7 +10013,7 @@
         <v>111</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D363" s="2">
         <v>372</v>
@@ -10042,7 +10039,7 @@
         <v>111</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D364" s="2">
         <v>377</v>
@@ -10068,7 +10065,7 @@
         <v>111</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D365" s="2">
         <v>450</v>
@@ -10094,7 +10091,7 @@
         <v>111</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D366" s="2">
         <v>381</v>
@@ -10120,7 +10117,7 @@
         <v>111</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D367" s="2">
         <v>132</v>
@@ -10146,7 +10143,7 @@
         <v>111</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D368" s="2">
         <v>160</v>
@@ -10172,7 +10169,7 @@
         <v>111</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D369" s="2">
         <v>80</v>
@@ -10198,7 +10195,7 @@
         <v>111</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D370" s="2">
         <v>124</v>
@@ -10224,7 +10221,7 @@
         <v>111</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D371" s="2">
         <v>468</v>
@@ -10250,7 +10247,7 @@
         <v>111</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D372" s="2">
         <v>131</v>
@@ -10276,7 +10273,7 @@
         <v>111</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D373" s="2">
         <v>171</v>
@@ -10302,7 +10299,7 @@
         <v>111</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D374" s="2">
         <v>470</v>
@@ -10328,7 +10325,7 @@
         <v>111</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D375" s="2">
         <v>423</v>
@@ -10354,7 +10351,7 @@
         <v>111</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D376" s="2">
         <v>392</v>
@@ -10380,7 +10377,7 @@
         <v>111</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D377" s="2">
         <v>330</v>
@@ -10406,7 +10403,7 @@
         <v>111</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D378" s="2">
         <v>287</v>
@@ -10432,7 +10429,7 @@
         <v>111</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D379" s="2">
         <v>171</v>
@@ -10458,7 +10455,7 @@
         <v>111</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D380" s="2">
         <v>470</v>
@@ -10484,7 +10481,7 @@
         <v>111</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D381" s="2">
         <v>345</v>
@@ -10510,7 +10507,7 @@
         <v>111</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D382" s="2">
         <v>78</v>
@@ -10536,7 +10533,7 @@
         <v>111</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D383" s="2">
         <v>389</v>
@@ -10562,7 +10559,7 @@
         <v>111</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D384" s="2">
         <v>129</v>
@@ -10588,7 +10585,7 @@
         <v>111</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D385" s="2">
         <v>449</v>
@@ -10614,7 +10611,7 @@
         <v>111</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D386" s="2">
         <v>224</v>
@@ -10640,7 +10637,7 @@
         <v>111</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D387" s="2">
         <v>99</v>
@@ -10666,7 +10663,7 @@
         <v>111</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D388" s="2">
         <v>84</v>
@@ -10692,7 +10689,7 @@
         <v>111</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D389" s="2">
         <v>206</v>
@@ -10718,7 +10715,7 @@
         <v>111</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D390" s="2">
         <v>356</v>
@@ -10744,7 +10741,7 @@
         <v>111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D391" s="2">
         <v>370</v>
@@ -10770,7 +10767,7 @@
         <v>111</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D392" s="2">
         <v>211</v>
@@ -10796,7 +10793,7 @@
         <v>111</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D393" s="2">
         <v>198</v>
@@ -10822,7 +10819,7 @@
         <v>111</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D394" s="2">
         <v>246</v>
@@ -10848,7 +10845,7 @@
         <v>111</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D395" s="2">
         <v>119</v>
@@ -10874,7 +10871,7 @@
         <v>111</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D396" s="2">
         <v>228</v>
@@ -10900,7 +10897,7 @@
         <v>111</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D397" s="2">
         <v>166</v>
@@ -10926,7 +10923,7 @@
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D398" s="2">
         <v>421</v>
@@ -10952,7 +10949,7 @@
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D399" s="2">
         <v>99</v>
@@ -10978,7 +10975,7 @@
         <v>112</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D400" s="2">
         <v>474</v>
@@ -11004,7 +11001,7 @@
         <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D401" s="2">
         <v>398</v>
@@ -11030,7 +11027,7 @@
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D402" s="2">
         <v>147</v>
@@ -11056,7 +11053,7 @@
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D403" s="2">
         <v>443</v>
@@ -11082,7 +11079,7 @@
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D404" s="2">
         <v>259</v>
@@ -11108,7 +11105,7 @@
         <v>112</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D405" s="2">
         <v>264</v>
@@ -11134,7 +11131,7 @@
         <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D406" s="2">
         <v>450</v>
@@ -11160,7 +11157,7 @@
         <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D407" s="2">
         <v>490</v>
@@ -11186,7 +11183,7 @@
         <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D408" s="2">
         <v>457</v>
@@ -11212,7 +11209,7 @@
         <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D409" s="2">
         <v>481</v>
@@ -11238,7 +11235,7 @@
         <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D410" s="2">
         <v>452</v>
@@ -11264,7 +11261,7 @@
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D411" s="2">
         <v>194</v>
@@ -11290,7 +11287,7 @@
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D412" s="2">
         <v>399</v>
@@ -11316,7 +11313,7 @@
         <v>112</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D413" s="2">
         <v>264</v>
@@ -11342,7 +11339,7 @@
         <v>112</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D414" s="2">
         <v>109</v>
@@ -11368,7 +11365,7 @@
         <v>112</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D415" s="2">
         <v>437</v>
@@ -11394,7 +11391,7 @@
         <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D416" s="2">
         <v>447</v>
@@ -11420,7 +11417,7 @@
         <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D417" s="2">
         <v>421</v>
@@ -11446,7 +11443,7 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D418" s="2">
         <v>80</v>
@@ -11472,7 +11469,7 @@
         <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D419" s="2">
         <v>493</v>
@@ -11498,7 +11495,7 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D420" s="2">
         <v>105</v>
@@ -11524,7 +11521,7 @@
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D421" s="2">
         <v>432</v>
@@ -11550,7 +11547,7 @@
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D422" s="2">
         <v>332</v>
@@ -11576,7 +11573,7 @@
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D423" s="2">
         <v>238</v>
@@ -11602,7 +11599,7 @@
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D424" s="2">
         <v>300</v>
@@ -11628,7 +11625,7 @@
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D425" s="2">
         <v>249</v>
@@ -11654,7 +11651,7 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D426" s="2">
         <v>336</v>
@@ -11680,7 +11677,7 @@
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D427" s="2">
         <v>114</v>
@@ -11706,7 +11703,7 @@
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D428" s="2">
         <v>175</v>
@@ -11732,7 +11729,7 @@
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D429" s="2">
         <v>473</v>
@@ -11758,7 +11755,7 @@
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D430" s="2">
         <v>202</v>
@@ -11784,7 +11781,7 @@
         <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D431" s="2">
         <v>215</v>
@@ -11810,7 +11807,7 @@
         <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D432" s="2">
         <v>252</v>
@@ -11836,7 +11833,7 @@
         <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D433" s="2">
         <v>223</v>
@@ -11862,7 +11859,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>
@@ -11888,7 +11885,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11914,7 +11911,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11940,7 +11937,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="62">
   <si>
     <t>Month</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>Pasta</t>
-  </si>
-  <si>
-    <t>Cheese</t>
   </si>
   <si>
     <t>Tea</t>
@@ -627,7 +624,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="2">
         <v>373</v>
@@ -653,7 +650,7 @@
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" s="2">
         <v>423</v>
@@ -679,7 +676,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2">
         <v>147</v>
@@ -705,7 +702,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2">
         <v>431</v>
@@ -731,7 +728,7 @@
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" s="2">
         <v>305</v>
@@ -757,7 +754,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2">
         <v>167</v>
@@ -783,7 +780,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2">
         <v>101</v>
@@ -809,7 +806,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2">
         <v>73</v>
@@ -835,7 +832,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2">
         <v>445</v>
@@ -861,7 +858,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2">
         <v>180</v>
@@ -887,7 +884,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" s="2">
         <v>221</v>
@@ -913,7 +910,7 @@
         <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" s="2">
         <v>153</v>
@@ -939,7 +936,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" s="2">
         <v>283</v>
@@ -965,7 +962,7 @@
         <v>101</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" s="2">
         <v>220</v>
@@ -991,7 +988,7 @@
         <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="2">
         <v>338</v>
@@ -1017,7 +1014,7 @@
         <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="2">
         <v>209</v>
@@ -1043,7 +1040,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2">
         <v>186</v>
@@ -1069,7 +1066,7 @@
         <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2">
         <v>383</v>
@@ -1095,7 +1092,7 @@
         <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" s="2">
         <v>253</v>
@@ -1121,7 +1118,7 @@
         <v>101</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2">
         <v>159</v>
@@ -1147,7 +1144,7 @@
         <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="2">
         <v>212</v>
@@ -1173,7 +1170,7 @@
         <v>101</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D23" s="2">
         <v>377</v>
@@ -1199,7 +1196,7 @@
         <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="2">
         <v>126</v>
@@ -1225,7 +1222,7 @@
         <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" s="2">
         <v>283</v>
@@ -1251,7 +1248,7 @@
         <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D26" s="2">
         <v>235</v>
@@ -1277,7 +1274,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" s="2">
         <v>170</v>
@@ -1303,7 +1300,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2">
         <v>321</v>
@@ -1329,7 +1326,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D29" s="2">
         <v>127</v>
@@ -1355,7 +1352,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" s="2">
         <v>162</v>
@@ -1381,7 +1378,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D31" s="2">
         <v>265</v>
@@ -1407,7 +1404,7 @@
         <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2">
         <v>193</v>
@@ -1433,7 +1430,7 @@
         <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2">
         <v>211</v>
@@ -1459,7 +1456,7 @@
         <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D34" s="2">
         <v>328</v>
@@ -1485,7 +1482,7 @@
         <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D35" s="2">
         <v>127</v>
@@ -1511,7 +1508,7 @@
         <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D36" s="2">
         <v>176</v>
@@ -1537,7 +1534,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" s="2">
         <v>278</v>
@@ -1563,7 +1560,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1589,7 +1586,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1615,7 +1612,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1641,7 +1638,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1667,7 +1664,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1693,7 +1690,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1719,7 +1716,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1745,7 +1742,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1771,7 +1768,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1797,7 +1794,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1823,7 +1820,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1849,7 +1846,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1875,7 +1872,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1901,7 +1898,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1927,7 +1924,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1953,7 +1950,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1979,7 +1976,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -2005,7 +2002,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2031,7 +2028,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2057,7 +2054,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2083,7 +2080,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2109,7 +2106,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2135,7 +2132,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2161,7 +2158,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2187,7 +2184,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2213,7 +2210,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2239,7 +2236,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2265,7 +2262,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2291,7 +2288,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2317,7 +2314,7 @@
         <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D67" s="2">
         <v>259</v>
@@ -2343,7 +2340,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>
@@ -2369,7 +2366,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D69" s="2">
         <v>173</v>
@@ -2395,7 +2392,7 @@
         <v>102</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D70" s="2">
         <v>186</v>
@@ -2421,7 +2418,7 @@
         <v>102</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D71" s="2">
         <v>274</v>
@@ -2447,7 +2444,7 @@
         <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D72" s="2">
         <v>238</v>
@@ -2473,7 +2470,7 @@
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D73" s="2">
         <v>109</v>
@@ -3435,7 +3432,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3461,7 +3458,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3487,7 +3484,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3513,7 +3510,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3539,7 +3536,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3565,7 +3562,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3591,7 +3588,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3617,7 +3614,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3643,7 +3640,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3669,7 +3666,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3695,7 +3692,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>
@@ -3721,7 +3718,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3747,7 +3744,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3773,7 +3770,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3799,7 +3796,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3825,7 +3822,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3851,7 +3848,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -3877,7 +3874,7 @@
         <v>104</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D127" s="2">
         <v>141</v>
@@ -3903,7 +3900,7 @@
         <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D128" s="2">
         <v>303</v>
@@ -3929,7 +3926,7 @@
         <v>104</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D129" s="2">
         <v>281</v>
@@ -3955,7 +3952,7 @@
         <v>104</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D130" s="2">
         <v>453</v>
@@ -3981,7 +3978,7 @@
         <v>104</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D131" s="2">
         <v>310</v>
@@ -4007,7 +4004,7 @@
         <v>104</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D132" s="2">
         <v>243</v>
@@ -4033,7 +4030,7 @@
         <v>104</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D133" s="2">
         <v>248</v>
@@ -4059,7 +4056,7 @@
         <v>104</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D134" s="2">
         <v>253</v>
@@ -4085,7 +4082,7 @@
         <v>104</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D135" s="2">
         <v>197</v>
@@ -4111,7 +4108,7 @@
         <v>104</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D136" s="2">
         <v>184</v>
@@ -4137,7 +4134,7 @@
         <v>104</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D137" s="2">
         <v>119</v>
@@ -4163,7 +4160,7 @@
         <v>104</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D138" s="2">
         <v>192</v>
@@ -4189,7 +4186,7 @@
         <v>104</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D139" s="2">
         <v>237</v>
@@ -4215,7 +4212,7 @@
         <v>104</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D140" s="2">
         <v>71</v>
@@ -4241,7 +4238,7 @@
         <v>104</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D141" s="2">
         <v>170</v>
@@ -4267,7 +4264,7 @@
         <v>104</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D142" s="2">
         <v>201</v>
@@ -4293,7 +4290,7 @@
         <v>104</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D143" s="2">
         <v>226</v>
@@ -4319,7 +4316,7 @@
         <v>104</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D144" s="2">
         <v>251</v>
@@ -4345,7 +4342,7 @@
         <v>104</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D145" s="2">
         <v>281</v>
@@ -4371,7 +4368,7 @@
         <v>105</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D146" s="2">
         <v>494</v>
@@ -4397,7 +4394,7 @@
         <v>105</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D147" s="2">
         <v>383</v>
@@ -4423,7 +4420,7 @@
         <v>105</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D148" s="2">
         <v>243</v>
@@ -4449,7 +4446,7 @@
         <v>105</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D149" s="2">
         <v>384</v>
@@ -4475,7 +4472,7 @@
         <v>105</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D150" s="2">
         <v>316</v>
@@ -4501,7 +4498,7 @@
         <v>105</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D151" s="2">
         <v>362</v>
@@ -4527,7 +4524,7 @@
         <v>105</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D152" s="2">
         <v>479</v>
@@ -4553,7 +4550,7 @@
         <v>105</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D153" s="2">
         <v>317</v>
@@ -4579,7 +4576,7 @@
         <v>105</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D154" s="2">
         <v>240</v>
@@ -4605,7 +4602,7 @@
         <v>105</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D155" s="2">
         <v>290</v>
@@ -4631,7 +4628,7 @@
         <v>105</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D156" s="2">
         <v>477</v>
@@ -4657,7 +4654,7 @@
         <v>105</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D157" s="2">
         <v>362</v>
@@ -4683,7 +4680,7 @@
         <v>105</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D158" s="2">
         <v>54</v>
@@ -4709,7 +4706,7 @@
         <v>105</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D159" s="2">
         <v>281</v>
@@ -4735,7 +4732,7 @@
         <v>105</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D160" s="2">
         <v>381</v>
@@ -4761,7 +4758,7 @@
         <v>105</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D161" s="2">
         <v>351</v>
@@ -4787,7 +4784,7 @@
         <v>105</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D162" s="2">
         <v>309</v>
@@ -4813,7 +4810,7 @@
         <v>105</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D163" s="2">
         <v>383</v>
@@ -4839,7 +4836,7 @@
         <v>105</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D164" s="2">
         <v>407</v>
@@ -4865,7 +4862,7 @@
         <v>105</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D165" s="2">
         <v>171</v>
@@ -4891,7 +4888,7 @@
         <v>105</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D166" s="2">
         <v>274</v>
@@ -4917,7 +4914,7 @@
         <v>105</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D167" s="2">
         <v>295</v>
@@ -4943,7 +4940,7 @@
         <v>105</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D168" s="2">
         <v>418</v>
@@ -4969,7 +4966,7 @@
         <v>105</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D169" s="2">
         <v>84</v>
@@ -4995,7 +4992,7 @@
         <v>105</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D170" s="2">
         <v>247</v>
@@ -5021,7 +5018,7 @@
         <v>105</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D171" s="2">
         <v>179</v>
@@ -5047,7 +5044,7 @@
         <v>105</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D172" s="2">
         <v>322</v>
@@ -5073,7 +5070,7 @@
         <v>105</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D173" s="2">
         <v>271</v>
@@ -5099,7 +5096,7 @@
         <v>105</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D174" s="2">
         <v>281</v>
@@ -5125,7 +5122,7 @@
         <v>105</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D175" s="2">
         <v>174</v>
@@ -5151,7 +5148,7 @@
         <v>105</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D176" s="2">
         <v>305</v>
@@ -5177,7 +5174,7 @@
         <v>105</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D177" s="2">
         <v>254</v>
@@ -5203,7 +5200,7 @@
         <v>105</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D178" s="2">
         <v>312</v>
@@ -5229,7 +5226,7 @@
         <v>105</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D179" s="2">
         <v>115</v>
@@ -5255,7 +5252,7 @@
         <v>105</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D180" s="2">
         <v>161</v>
@@ -5281,7 +5278,7 @@
         <v>105</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D181" s="2">
         <v>240</v>
@@ -5307,7 +5304,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -5333,7 +5330,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5359,7 +5356,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5385,7 +5382,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5411,7 +5408,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -5437,7 +5434,7 @@
         <v>106</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D187" s="2">
         <v>342</v>
@@ -5463,7 +5460,7 @@
         <v>106</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D188" s="2">
         <v>285</v>
@@ -5489,7 +5486,7 @@
         <v>106</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D189" s="2">
         <v>453</v>
@@ -5515,7 +5512,7 @@
         <v>106</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D190" s="2">
         <v>69</v>
@@ -5541,7 +5538,7 @@
         <v>106</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D191" s="2">
         <v>154</v>
@@ -5567,7 +5564,7 @@
         <v>106</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D192" s="2">
         <v>246</v>
@@ -5593,7 +5590,7 @@
         <v>106</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D193" s="2">
         <v>446</v>
@@ -5619,7 +5616,7 @@
         <v>106</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D194" s="2">
         <v>467</v>
@@ -5645,7 +5642,7 @@
         <v>106</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D195" s="2">
         <v>374</v>
@@ -5671,7 +5668,7 @@
         <v>106</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D196" s="2">
         <v>266</v>
@@ -5697,7 +5694,7 @@
         <v>106</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D197" s="2">
         <v>281</v>
@@ -5723,7 +5720,7 @@
         <v>106</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D198" s="2">
         <v>277</v>
@@ -5749,7 +5746,7 @@
         <v>106</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D199" s="2">
         <v>153</v>
@@ -5775,7 +5772,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D200" s="2">
         <v>176</v>
@@ -5801,7 +5798,7 @@
         <v>106</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D201" s="2">
         <v>281</v>
@@ -5827,7 +5824,7 @@
         <v>106</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D202" s="2">
         <v>52</v>
@@ -5853,7 +5850,7 @@
         <v>106</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D203" s="2">
         <v>94</v>
@@ -5879,7 +5876,7 @@
         <v>106</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D204" s="2">
         <v>181</v>
@@ -5905,7 +5902,7 @@
         <v>106</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D205" s="2">
         <v>336</v>
@@ -5931,7 +5928,7 @@
         <v>106</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D206" s="2">
         <v>349</v>
@@ -5957,7 +5954,7 @@
         <v>106</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D207" s="2">
         <v>127</v>
@@ -5983,7 +5980,7 @@
         <v>106</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D208" s="2">
         <v>376</v>
@@ -6009,7 +6006,7 @@
         <v>106</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D209" s="2">
         <v>98</v>
@@ -6035,7 +6032,7 @@
         <v>106</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D210" s="2">
         <v>152</v>
@@ -6061,7 +6058,7 @@
         <v>106</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D211" s="2">
         <v>235</v>
@@ -6087,7 +6084,7 @@
         <v>106</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D212" s="2">
         <v>105</v>
@@ -6113,7 +6110,7 @@
         <v>106</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D213" s="2">
         <v>150</v>
@@ -6139,7 +6136,7 @@
         <v>106</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D214" s="2">
         <v>215</v>
@@ -6165,7 +6162,7 @@
         <v>106</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D215" s="2">
         <v>216</v>
@@ -6191,7 +6188,7 @@
         <v>106</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D216" s="2">
         <v>214</v>
@@ -6217,7 +6214,7 @@
         <v>106</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D217" s="2">
         <v>194</v>
@@ -7179,7 +7176,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -7205,7 +7202,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7231,7 +7228,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -8115,7 +8112,7 @@
         <v>109</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D290" s="2">
         <v>212</v>
@@ -8141,7 +8138,7 @@
         <v>109</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D291" s="2">
         <v>457</v>
@@ -8167,7 +8164,7 @@
         <v>109</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D292" s="2">
         <v>203</v>
@@ -8193,7 +8190,7 @@
         <v>109</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D293" s="2">
         <v>247</v>
@@ -8219,7 +8216,7 @@
         <v>109</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D294" s="2">
         <v>113</v>
@@ -8245,7 +8242,7 @@
         <v>109</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D295" s="2">
         <v>107</v>
@@ -8271,7 +8268,7 @@
         <v>109</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D296" s="2">
         <v>338</v>
@@ -8297,7 +8294,7 @@
         <v>109</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D297" s="2">
         <v>259</v>
@@ -8323,7 +8320,7 @@
         <v>109</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D298" s="2">
         <v>430</v>
@@ -8349,7 +8346,7 @@
         <v>109</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D299" s="2">
         <v>329</v>
@@ -8375,7 +8372,7 @@
         <v>109</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D300" s="2">
         <v>369</v>
@@ -8401,7 +8398,7 @@
         <v>109</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D301" s="2">
         <v>262</v>
@@ -8427,7 +8424,7 @@
         <v>109</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D302" s="2">
         <v>253</v>
@@ -8453,7 +8450,7 @@
         <v>109</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D303" s="2">
         <v>257</v>
@@ -8479,7 +8476,7 @@
         <v>109</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D304" s="2">
         <v>446</v>
@@ -8505,7 +8502,7 @@
         <v>109</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D305" s="2">
         <v>270</v>
@@ -8531,7 +8528,7 @@
         <v>109</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D306" s="2">
         <v>486</v>
@@ -8557,7 +8554,7 @@
         <v>109</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D307" s="2">
         <v>484</v>
@@ -8583,7 +8580,7 @@
         <v>109</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D308" s="2">
         <v>277</v>
@@ -8609,7 +8606,7 @@
         <v>109</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D309" s="2">
         <v>298</v>
@@ -8635,7 +8632,7 @@
         <v>109</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D310" s="2">
         <v>148</v>
@@ -8661,7 +8658,7 @@
         <v>109</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D311" s="2">
         <v>218</v>
@@ -8687,7 +8684,7 @@
         <v>109</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D312" s="2">
         <v>253</v>
@@ -8713,7 +8710,7 @@
         <v>109</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D313" s="2">
         <v>266</v>
@@ -8739,7 +8736,7 @@
         <v>109</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D314" s="2">
         <v>290</v>
@@ -8765,7 +8762,7 @@
         <v>109</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D315" s="2">
         <v>197</v>
@@ -8791,7 +8788,7 @@
         <v>109</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D316" s="2">
         <v>160</v>
@@ -8817,7 +8814,7 @@
         <v>109</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D317" s="2">
         <v>272</v>
@@ -8843,7 +8840,7 @@
         <v>109</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D318" s="2">
         <v>254</v>
@@ -8869,7 +8866,7 @@
         <v>109</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D319" s="2">
         <v>160</v>
@@ -8895,7 +8892,7 @@
         <v>109</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D320" s="2">
         <v>150</v>
@@ -8921,7 +8918,7 @@
         <v>109</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D321" s="2">
         <v>247</v>
@@ -8947,7 +8944,7 @@
         <v>109</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D322" s="2">
         <v>263</v>
@@ -8973,7 +8970,7 @@
         <v>109</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D323" s="2">
         <v>267</v>
@@ -8999,7 +8996,7 @@
         <v>109</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D324" s="2">
         <v>223</v>
@@ -9025,7 +9022,7 @@
         <v>109</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D325" s="2">
         <v>170</v>
@@ -9051,7 +9048,7 @@
         <v>110</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D326" s="2">
         <v>175</v>
@@ -9077,7 +9074,7 @@
         <v>110</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D327" s="2">
         <v>333</v>
@@ -9103,7 +9100,7 @@
         <v>110</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D328" s="2">
         <v>442</v>
@@ -9129,7 +9126,7 @@
         <v>110</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D329" s="2">
         <v>131</v>
@@ -9155,7 +9152,7 @@
         <v>110</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D330" s="2">
         <v>275</v>
@@ -9181,7 +9178,7 @@
         <v>110</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D331" s="2">
         <v>170</v>
@@ -9207,7 +9204,7 @@
         <v>110</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D332" s="2">
         <v>94</v>
@@ -9233,7 +9230,7 @@
         <v>110</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D333" s="2">
         <v>56</v>
@@ -9259,7 +9256,7 @@
         <v>110</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D334" s="2">
         <v>297</v>
@@ -9285,7 +9282,7 @@
         <v>110</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D335" s="2">
         <v>389</v>
@@ -9311,7 +9308,7 @@
         <v>110</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D336" s="2">
         <v>88</v>
@@ -9337,7 +9334,7 @@
         <v>110</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D337" s="2">
         <v>101</v>
@@ -9363,7 +9360,7 @@
         <v>110</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D338" s="2">
         <v>237</v>
@@ -9389,7 +9386,7 @@
         <v>110</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D339" s="2">
         <v>251</v>
@@ -9415,7 +9412,7 @@
         <v>110</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D340" s="2">
         <v>62</v>
@@ -9441,7 +9438,7 @@
         <v>110</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D341" s="2">
         <v>144</v>
@@ -9467,7 +9464,7 @@
         <v>110</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D342" s="2">
         <v>180</v>
@@ -9493,7 +9490,7 @@
         <v>110</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D343" s="2">
         <v>358</v>
@@ -9519,7 +9516,7 @@
         <v>110</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D344" s="2">
         <v>452</v>
@@ -9545,7 +9542,7 @@
         <v>110</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D345" s="2">
         <v>121</v>
@@ -9571,7 +9568,7 @@
         <v>110</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D346" s="2">
         <v>354</v>
@@ -9597,7 +9594,7 @@
         <v>110</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D347" s="2">
         <v>151</v>
@@ -9623,7 +9620,7 @@
         <v>110</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D348" s="2">
         <v>270</v>
@@ -9649,7 +9646,7 @@
         <v>110</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D349" s="2">
         <v>361</v>
@@ -9675,7 +9672,7 @@
         <v>110</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D350" s="2">
         <v>148</v>
@@ -9701,7 +9698,7 @@
         <v>110</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D351" s="2">
         <v>223</v>
@@ -9727,7 +9724,7 @@
         <v>110</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D352" s="2">
         <v>79</v>
@@ -9753,7 +9750,7 @@
         <v>110</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D353" s="2">
         <v>104</v>
@@ -9779,7 +9776,7 @@
         <v>110</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D354" s="2">
         <v>294</v>
@@ -9805,7 +9802,7 @@
         <v>110</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D355" s="2">
         <v>248</v>
@@ -9831,7 +9828,7 @@
         <v>110</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D356" s="2">
         <v>215</v>
@@ -9857,7 +9854,7 @@
         <v>110</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D357" s="2">
         <v>258</v>
@@ -9883,7 +9880,7 @@
         <v>110</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D358" s="2">
         <v>201</v>
@@ -9909,7 +9906,7 @@
         <v>110</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D359" s="2">
         <v>238</v>
@@ -9935,7 +9932,7 @@
         <v>110</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D360" s="2">
         <v>286</v>
@@ -9961,7 +9958,7 @@
         <v>110</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D361" s="2">
         <v>386</v>
@@ -9987,7 +9984,7 @@
         <v>111</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D362" s="2">
         <v>497</v>
@@ -10013,7 +10010,7 @@
         <v>111</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D363" s="2">
         <v>372</v>
@@ -10039,7 +10036,7 @@
         <v>111</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D364" s="2">
         <v>377</v>
@@ -10065,7 +10062,7 @@
         <v>111</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D365" s="2">
         <v>450</v>
@@ -10091,7 +10088,7 @@
         <v>111</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D366" s="2">
         <v>381</v>
@@ -10117,7 +10114,7 @@
         <v>111</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D367" s="2">
         <v>132</v>
@@ -10143,7 +10140,7 @@
         <v>111</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D368" s="2">
         <v>160</v>
@@ -10169,7 +10166,7 @@
         <v>111</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D369" s="2">
         <v>80</v>
@@ -10195,7 +10192,7 @@
         <v>111</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D370" s="2">
         <v>124</v>
@@ -10221,7 +10218,7 @@
         <v>111</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D371" s="2">
         <v>468</v>
@@ -10247,7 +10244,7 @@
         <v>111</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D372" s="2">
         <v>131</v>
@@ -10273,7 +10270,7 @@
         <v>111</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D373" s="2">
         <v>171</v>
@@ -10299,7 +10296,7 @@
         <v>111</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D374" s="2">
         <v>470</v>
@@ -10325,7 +10322,7 @@
         <v>111</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D375" s="2">
         <v>423</v>
@@ -10351,7 +10348,7 @@
         <v>111</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D376" s="2">
         <v>392</v>
@@ -10377,7 +10374,7 @@
         <v>111</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D377" s="2">
         <v>330</v>
@@ -10403,7 +10400,7 @@
         <v>111</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D378" s="2">
         <v>287</v>
@@ -10429,7 +10426,7 @@
         <v>111</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D379" s="2">
         <v>171</v>
@@ -10455,7 +10452,7 @@
         <v>111</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D380" s="2">
         <v>470</v>
@@ -10481,7 +10478,7 @@
         <v>111</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D381" s="2">
         <v>345</v>
@@ -10507,7 +10504,7 @@
         <v>111</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D382" s="2">
         <v>78</v>
@@ -10533,7 +10530,7 @@
         <v>111</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D383" s="2">
         <v>389</v>
@@ -10559,7 +10556,7 @@
         <v>111</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D384" s="2">
         <v>129</v>
@@ -10585,7 +10582,7 @@
         <v>111</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D385" s="2">
         <v>449</v>
@@ -10611,7 +10608,7 @@
         <v>111</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D386" s="2">
         <v>224</v>
@@ -10637,7 +10634,7 @@
         <v>111</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D387" s="2">
         <v>99</v>
@@ -10663,7 +10660,7 @@
         <v>111</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D388" s="2">
         <v>84</v>
@@ -10689,7 +10686,7 @@
         <v>111</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D389" s="2">
         <v>206</v>
@@ -10715,7 +10712,7 @@
         <v>111</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D390" s="2">
         <v>356</v>
@@ -10741,7 +10738,7 @@
         <v>111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D391" s="2">
         <v>370</v>
@@ -10767,7 +10764,7 @@
         <v>111</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D392" s="2">
         <v>211</v>
@@ -10793,7 +10790,7 @@
         <v>111</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D393" s="2">
         <v>198</v>
@@ -10819,7 +10816,7 @@
         <v>111</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D394" s="2">
         <v>246</v>
@@ -10845,7 +10842,7 @@
         <v>111</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D395" s="2">
         <v>119</v>
@@ -10871,7 +10868,7 @@
         <v>111</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D396" s="2">
         <v>228</v>
@@ -10897,7 +10894,7 @@
         <v>111</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D397" s="2">
         <v>166</v>
@@ -10923,7 +10920,7 @@
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D398" s="2">
         <v>421</v>
@@ -10949,7 +10946,7 @@
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D399" s="2">
         <v>99</v>
@@ -10975,7 +10972,7 @@
         <v>112</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D400" s="2">
         <v>474</v>
@@ -11001,7 +10998,7 @@
         <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D401" s="2">
         <v>398</v>
@@ -11027,7 +11024,7 @@
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D402" s="2">
         <v>147</v>
@@ -11053,7 +11050,7 @@
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D403" s="2">
         <v>443</v>
@@ -11079,7 +11076,7 @@
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D404" s="2">
         <v>259</v>
@@ -11105,7 +11102,7 @@
         <v>112</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D405" s="2">
         <v>264</v>
@@ -11131,7 +11128,7 @@
         <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D406" s="2">
         <v>450</v>
@@ -11157,7 +11154,7 @@
         <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D407" s="2">
         <v>490</v>
@@ -11183,7 +11180,7 @@
         <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D408" s="2">
         <v>457</v>
@@ -11209,7 +11206,7 @@
         <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D409" s="2">
         <v>481</v>
@@ -11235,7 +11232,7 @@
         <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D410" s="2">
         <v>452</v>
@@ -11261,7 +11258,7 @@
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D411" s="2">
         <v>194</v>
@@ -11287,7 +11284,7 @@
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D412" s="2">
         <v>399</v>
@@ -11313,7 +11310,7 @@
         <v>112</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D413" s="2">
         <v>264</v>
@@ -11339,7 +11336,7 @@
         <v>112</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D414" s="2">
         <v>109</v>
@@ -11365,7 +11362,7 @@
         <v>112</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D415" s="2">
         <v>437</v>
@@ -11391,7 +11388,7 @@
         <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D416" s="2">
         <v>447</v>
@@ -11417,7 +11414,7 @@
         <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D417" s="2">
         <v>421</v>
@@ -11443,7 +11440,7 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D418" s="2">
         <v>80</v>
@@ -11469,7 +11466,7 @@
         <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D419" s="2">
         <v>493</v>
@@ -11495,7 +11492,7 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D420" s="2">
         <v>105</v>
@@ -11521,7 +11518,7 @@
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D421" s="2">
         <v>432</v>
@@ -11547,7 +11544,7 @@
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D422" s="2">
         <v>332</v>
@@ -11573,7 +11570,7 @@
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D423" s="2">
         <v>238</v>
@@ -11599,7 +11596,7 @@
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D424" s="2">
         <v>300</v>
@@ -11625,7 +11622,7 @@
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D425" s="2">
         <v>249</v>
@@ -11651,7 +11648,7 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D426" s="2">
         <v>336</v>
@@ -11677,7 +11674,7 @@
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D427" s="2">
         <v>114</v>
@@ -11703,7 +11700,7 @@
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D428" s="2">
         <v>175</v>
@@ -11729,7 +11726,7 @@
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D429" s="2">
         <v>473</v>
@@ -11755,7 +11752,7 @@
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D430" s="2">
         <v>202</v>
@@ -11781,7 +11778,7 @@
         <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D431" s="2">
         <v>215</v>
@@ -11807,7 +11804,7 @@
         <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D432" s="2">
         <v>252</v>
@@ -11833,7 +11830,7 @@
         <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D433" s="2">
         <v>223</v>
@@ -11859,7 +11856,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>
@@ -11885,7 +11882,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11911,7 +11908,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11937,7 +11934,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>
@@ -11963,7 +11960,7 @@
         <v>113</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D438" s="2">
         <v>219</v>
@@ -11989,7 +11986,7 @@
         <v>113</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D439" s="2">
         <v>99</v>
@@ -12015,7 +12012,7 @@
         <v>113</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D440" s="2">
         <v>177</v>
@@ -12041,7 +12038,7 @@
         <v>113</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D441" s="2">
         <v>380</v>
@@ -12067,7 +12064,7 @@
         <v>113</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D442" s="2">
         <v>464</v>
@@ -12093,7 +12090,7 @@
         <v>113</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D443" s="2">
         <v>460</v>
@@ -12119,7 +12116,7 @@
         <v>113</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D444" s="2">
         <v>299</v>
@@ -12145,7 +12142,7 @@
         <v>113</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D445" s="2">
         <v>243</v>
@@ -12171,7 +12168,7 @@
         <v>113</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D446" s="2">
         <v>154</v>
@@ -12197,7 +12194,7 @@
         <v>113</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D447" s="2">
         <v>239</v>
@@ -12223,7 +12220,7 @@
         <v>113</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D448" s="2">
         <v>410</v>
@@ -12249,7 +12246,7 @@
         <v>113</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D449" s="2">
         <v>273</v>
@@ -12275,7 +12272,7 @@
         <v>113</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D450" s="2">
         <v>90</v>
@@ -12301,7 +12298,7 @@
         <v>113</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D451" s="2">
         <v>407</v>
@@ -12327,7 +12324,7 @@
         <v>113</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D452" s="2">
         <v>301</v>
@@ -12353,7 +12350,7 @@
         <v>113</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D453" s="2">
         <v>181</v>
@@ -12379,7 +12376,7 @@
         <v>113</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D454" s="2">
         <v>186</v>
@@ -12405,7 +12402,7 @@
         <v>113</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D455" s="2">
         <v>424</v>
@@ -12431,7 +12428,7 @@
         <v>113</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D456" s="2">
         <v>268</v>
@@ -12457,7 +12454,7 @@
         <v>113</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D457" s="2">
         <v>277</v>
@@ -12483,7 +12480,7 @@
         <v>113</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D458" s="2">
         <v>89</v>
@@ -12509,7 +12506,7 @@
         <v>113</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D459" s="2">
         <v>219</v>
@@ -12535,7 +12532,7 @@
         <v>113</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D460" s="2">
         <v>273</v>
@@ -12561,7 +12558,7 @@
         <v>113</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D461" s="2">
         <v>254</v>
@@ -12587,7 +12584,7 @@
         <v>113</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D462" s="2">
         <v>243</v>
@@ -12613,7 +12610,7 @@
         <v>113</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D463" s="2">
         <v>349</v>
@@ -12639,7 +12636,7 @@
         <v>113</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D464" s="2">
         <v>245</v>
@@ -12665,7 +12662,7 @@
         <v>113</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D465" s="2">
         <v>174</v>
@@ -12691,7 +12688,7 @@
         <v>113</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D466" s="2">
         <v>80</v>
@@ -12717,7 +12714,7 @@
         <v>113</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D467" s="2">
         <v>210</v>
@@ -12743,7 +12740,7 @@
         <v>113</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D468" s="2">
         <v>281</v>
@@ -12769,7 +12766,7 @@
         <v>113</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D469" s="2">
         <v>80</v>
@@ -12795,7 +12792,7 @@
         <v>114</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D470" s="2">
         <v>106</v>
@@ -12821,7 +12818,7 @@
         <v>114</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D471" s="2">
         <v>53</v>
@@ -12847,7 +12844,7 @@
         <v>114</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D472" s="2">
         <v>80</v>
@@ -12873,7 +12870,7 @@
         <v>114</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D473" s="2">
         <v>92</v>
@@ -12899,7 +12896,7 @@
         <v>114</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D474" s="2">
         <v>146</v>
@@ -12925,7 +12922,7 @@
         <v>114</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D475" s="2">
         <v>465</v>
@@ -12951,7 +12948,7 @@
         <v>114</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D476" s="2">
         <v>361</v>
@@ -12977,7 +12974,7 @@
         <v>114</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D477" s="2">
         <v>420</v>
@@ -13003,7 +13000,7 @@
         <v>114</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D478" s="2">
         <v>471</v>
@@ -13029,7 +13026,7 @@
         <v>114</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D479" s="2">
         <v>174</v>
@@ -13055,7 +13052,7 @@
         <v>114</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D480" s="2">
         <v>95</v>
@@ -13081,7 +13078,7 @@
         <v>114</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D481" s="2">
         <v>305</v>
@@ -13107,7 +13104,7 @@
         <v>114</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D482" s="2">
         <v>465</v>
@@ -13133,7 +13130,7 @@
         <v>114</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D483" s="2">
         <v>418</v>
@@ -13159,7 +13156,7 @@
         <v>114</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D484" s="2">
         <v>478</v>
@@ -13185,7 +13182,7 @@
         <v>114</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D485" s="2">
         <v>434</v>
@@ -13211,7 +13208,7 @@
         <v>114</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D486" s="2">
         <v>459</v>
@@ -13237,7 +13234,7 @@
         <v>114</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D487" s="2">
         <v>99</v>
@@ -13263,7 +13260,7 @@
         <v>114</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D488" s="2">
         <v>104</v>
@@ -13289,7 +13286,7 @@
         <v>114</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D489" s="2">
         <v>166</v>
@@ -13315,7 +13312,7 @@
         <v>114</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D490" s="2">
         <v>277</v>
@@ -13341,7 +13338,7 @@
         <v>114</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D491" s="2">
         <v>329</v>
@@ -13367,7 +13364,7 @@
         <v>114</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D492" s="2">
         <v>193</v>
@@ -13393,7 +13390,7 @@
         <v>114</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D493" s="2">
         <v>70</v>
@@ -13419,7 +13416,7 @@
         <v>114</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D494" s="2">
         <v>174</v>
@@ -13445,7 +13442,7 @@
         <v>114</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D495" s="2">
         <v>305</v>
@@ -13471,7 +13468,7 @@
         <v>114</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D496" s="2">
         <v>274</v>
@@ -13497,7 +13494,7 @@
         <v>114</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D497" s="2">
         <v>185</v>
@@ -13523,7 +13520,7 @@
         <v>114</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D498" s="2">
         <v>249</v>
@@ -13549,7 +13546,7 @@
         <v>114</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D499" s="2">
         <v>203</v>
@@ -13575,7 +13572,7 @@
         <v>114</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D500" s="2">
         <v>315</v>
@@ -13601,7 +13598,7 @@
         <v>114</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D501" s="2">
         <v>211</v>
@@ -13627,7 +13624,7 @@
         <v>114</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D502" s="2">
         <v>262</v>
@@ -13653,7 +13650,7 @@
         <v>114</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D503" s="2">
         <v>346</v>
@@ -13679,7 +13676,7 @@
         <v>114</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D504" s="2">
         <v>232</v>
@@ -13705,7 +13702,7 @@
         <v>114</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D505" s="2">
         <v>142</v>
@@ -13731,7 +13728,7 @@
         <v>115</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D506" s="2">
         <v>316</v>
@@ -13757,7 +13754,7 @@
         <v>115</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D507" s="2">
         <v>221</v>
@@ -13783,7 +13780,7 @@
         <v>115</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D508" s="2">
         <v>318</v>
@@ -13809,7 +13806,7 @@
         <v>115</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D509" s="2">
         <v>147</v>
@@ -13835,7 +13832,7 @@
         <v>115</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D510" s="2">
         <v>396</v>
@@ -13861,7 +13858,7 @@
         <v>115</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D511" s="2">
         <v>409</v>
@@ -13887,7 +13884,7 @@
         <v>115</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D512" s="2">
         <v>278</v>
@@ -13913,7 +13910,7 @@
         <v>115</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D513" s="2">
         <v>103</v>
@@ -13939,7 +13936,7 @@
         <v>115</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D514" s="2">
         <v>419</v>
@@ -13965,7 +13962,7 @@
         <v>115</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D515" s="2">
         <v>243</v>
@@ -13991,7 +13988,7 @@
         <v>115</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D516" s="2">
         <v>280</v>
@@ -14017,7 +14014,7 @@
         <v>115</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D517" s="2">
         <v>206</v>
@@ -14043,7 +14040,7 @@
         <v>115</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D518" s="2">
         <v>114</v>
@@ -14069,7 +14066,7 @@
         <v>115</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D519" s="2">
         <v>58</v>
@@ -14095,7 +14092,7 @@
         <v>115</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D520" s="2">
         <v>198</v>
@@ -14121,7 +14118,7 @@
         <v>115</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D521" s="2">
         <v>138</v>
@@ -14147,7 +14144,7 @@
         <v>115</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D522" s="2">
         <v>417</v>
@@ -14173,7 +14170,7 @@
         <v>115</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D523" s="2">
         <v>141</v>
@@ -14199,7 +14196,7 @@
         <v>115</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D524" s="2">
         <v>456</v>
@@ -14225,7 +14222,7 @@
         <v>115</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D525" s="2">
         <v>316</v>
@@ -14251,7 +14248,7 @@
         <v>115</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D526" s="2">
         <v>357</v>
@@ -14277,7 +14274,7 @@
         <v>115</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D527" s="2">
         <v>143</v>
@@ -14303,7 +14300,7 @@
         <v>115</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D528" s="2">
         <v>177</v>
@@ -14329,7 +14326,7 @@
         <v>115</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D529" s="2">
         <v>226</v>
@@ -14355,7 +14352,7 @@
         <v>115</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D530" s="2">
         <v>344</v>
@@ -14381,7 +14378,7 @@
         <v>115</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D531" s="2">
         <v>143</v>
@@ -14407,7 +14404,7 @@
         <v>115</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D532" s="2">
         <v>97</v>
@@ -14433,7 +14430,7 @@
         <v>115</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D533" s="2">
         <v>193</v>
@@ -14459,7 +14456,7 @@
         <v>115</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D534" s="2">
         <v>56</v>
@@ -14485,7 +14482,7 @@
         <v>115</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D535" s="2">
         <v>121</v>
@@ -14511,7 +14508,7 @@
         <v>115</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D536" s="2">
         <v>150</v>
@@ -14537,7 +14534,7 @@
         <v>115</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D537" s="2">
         <v>344</v>
@@ -14563,7 +14560,7 @@
         <v>115</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D538" s="2">
         <v>188</v>
@@ -14589,7 +14586,7 @@
         <v>115</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D539" s="2">
         <v>342</v>
@@ -14615,7 +14612,7 @@
         <v>115</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D540" s="2">
         <v>234</v>
@@ -14641,7 +14638,7 @@
         <v>115</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D541" s="2">
         <v>239</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="61">
   <si>
     <t>Month</t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>Oats</t>
-  </si>
-  <si>
-    <t>Bread</t>
   </si>
   <si>
     <t>Pasta</t>
@@ -624,7 +621,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2">
         <v>373</v>
@@ -650,7 +647,7 @@
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2">
         <v>423</v>
@@ -676,7 +673,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2">
         <v>147</v>
@@ -702,7 +699,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2">
         <v>431</v>
@@ -728,7 +725,7 @@
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2">
         <v>305</v>
@@ -754,7 +751,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2">
         <v>167</v>
@@ -780,7 +777,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" s="2">
         <v>101</v>
@@ -806,7 +803,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" s="2">
         <v>73</v>
@@ -832,7 +829,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2">
         <v>445</v>
@@ -858,7 +855,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2">
         <v>180</v>
@@ -884,7 +881,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="2">
         <v>221</v>
@@ -910,7 +907,7 @@
         <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2">
         <v>153</v>
@@ -936,7 +933,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" s="2">
         <v>283</v>
@@ -962,7 +959,7 @@
         <v>101</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" s="2">
         <v>220</v>
@@ -988,7 +985,7 @@
         <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="2">
         <v>338</v>
@@ -1014,7 +1011,7 @@
         <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="2">
         <v>209</v>
@@ -1040,7 +1037,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2">
         <v>186</v>
@@ -1066,7 +1063,7 @@
         <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2">
         <v>383</v>
@@ -1092,7 +1089,7 @@
         <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="2">
         <v>253</v>
@@ -1118,7 +1115,7 @@
         <v>101</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2">
         <v>159</v>
@@ -1144,7 +1141,7 @@
         <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2">
         <v>212</v>
@@ -1170,7 +1167,7 @@
         <v>101</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" s="2">
         <v>377</v>
@@ -1196,7 +1193,7 @@
         <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" s="2">
         <v>126</v>
@@ -1222,7 +1219,7 @@
         <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D25" s="2">
         <v>283</v>
@@ -1248,7 +1245,7 @@
         <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D26" s="2">
         <v>235</v>
@@ -1274,7 +1271,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D27" s="2">
         <v>170</v>
@@ -1300,7 +1297,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" s="2">
         <v>321</v>
@@ -1326,7 +1323,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2">
         <v>127</v>
@@ -1352,7 +1349,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D30" s="2">
         <v>162</v>
@@ -1378,7 +1375,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" s="2">
         <v>265</v>
@@ -1404,7 +1401,7 @@
         <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="2">
         <v>193</v>
@@ -1430,7 +1427,7 @@
         <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D33" s="2">
         <v>211</v>
@@ -1456,7 +1453,7 @@
         <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D34" s="2">
         <v>328</v>
@@ -1482,7 +1479,7 @@
         <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="2">
         <v>127</v>
@@ -1508,7 +1505,7 @@
         <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" s="2">
         <v>176</v>
@@ -1534,7 +1531,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2">
         <v>278</v>
@@ -1560,7 +1557,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1586,7 +1583,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1612,7 +1609,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1638,7 +1635,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1664,7 +1661,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1690,7 +1687,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1716,7 +1713,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1742,7 +1739,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1768,7 +1765,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1794,7 +1791,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1820,7 +1817,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1846,7 +1843,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1872,7 +1869,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1898,7 +1895,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1924,7 +1921,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1950,7 +1947,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1976,7 +1973,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -2002,7 +1999,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2028,7 +2025,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2054,7 +2051,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2080,7 +2077,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2106,7 +2103,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2132,7 +2129,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2158,7 +2155,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2184,7 +2181,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2210,7 +2207,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2236,7 +2233,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2262,7 +2259,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2288,7 +2285,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2314,7 +2311,7 @@
         <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D67" s="2">
         <v>259</v>
@@ -2340,7 +2337,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>
@@ -2366,7 +2363,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D69" s="2">
         <v>173</v>
@@ -2392,7 +2389,7 @@
         <v>102</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D70" s="2">
         <v>186</v>
@@ -2418,7 +2415,7 @@
         <v>102</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D71" s="2">
         <v>274</v>
@@ -2444,7 +2441,7 @@
         <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D72" s="2">
         <v>238</v>
@@ -2470,7 +2467,7 @@
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D73" s="2">
         <v>109</v>
@@ -3432,7 +3429,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3458,7 +3455,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3484,7 +3481,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3510,7 +3507,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3536,7 +3533,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3562,7 +3559,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3588,7 +3585,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3614,7 +3611,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3640,7 +3637,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3666,7 +3663,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3692,7 +3689,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>
@@ -3718,7 +3715,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3744,7 +3741,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3770,7 +3767,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3796,7 +3793,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3822,7 +3819,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3848,7 +3845,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -3874,7 +3871,7 @@
         <v>104</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D127" s="2">
         <v>141</v>
@@ -3900,7 +3897,7 @@
         <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D128" s="2">
         <v>303</v>
@@ -3926,7 +3923,7 @@
         <v>104</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D129" s="2">
         <v>281</v>
@@ -3952,7 +3949,7 @@
         <v>104</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D130" s="2">
         <v>453</v>
@@ -3978,7 +3975,7 @@
         <v>104</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D131" s="2">
         <v>310</v>
@@ -4004,7 +4001,7 @@
         <v>104</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D132" s="2">
         <v>243</v>
@@ -4030,7 +4027,7 @@
         <v>104</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D133" s="2">
         <v>248</v>
@@ -4056,7 +4053,7 @@
         <v>104</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D134" s="2">
         <v>253</v>
@@ -4082,7 +4079,7 @@
         <v>104</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D135" s="2">
         <v>197</v>
@@ -4108,7 +4105,7 @@
         <v>104</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D136" s="2">
         <v>184</v>
@@ -4134,7 +4131,7 @@
         <v>104</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D137" s="2">
         <v>119</v>
@@ -4160,7 +4157,7 @@
         <v>104</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D138" s="2">
         <v>192</v>
@@ -4186,7 +4183,7 @@
         <v>104</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D139" s="2">
         <v>237</v>
@@ -4212,7 +4209,7 @@
         <v>104</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D140" s="2">
         <v>71</v>
@@ -4238,7 +4235,7 @@
         <v>104</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D141" s="2">
         <v>170</v>
@@ -4264,7 +4261,7 @@
         <v>104</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D142" s="2">
         <v>201</v>
@@ -4290,7 +4287,7 @@
         <v>104</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D143" s="2">
         <v>226</v>
@@ -4316,7 +4313,7 @@
         <v>104</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D144" s="2">
         <v>251</v>
@@ -4342,7 +4339,7 @@
         <v>104</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D145" s="2">
         <v>281</v>
@@ -4368,7 +4365,7 @@
         <v>105</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D146" s="2">
         <v>494</v>
@@ -4394,7 +4391,7 @@
         <v>105</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D147" s="2">
         <v>383</v>
@@ -4420,7 +4417,7 @@
         <v>105</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D148" s="2">
         <v>243</v>
@@ -4446,7 +4443,7 @@
         <v>105</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D149" s="2">
         <v>384</v>
@@ -4472,7 +4469,7 @@
         <v>105</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D150" s="2">
         <v>316</v>
@@ -4498,7 +4495,7 @@
         <v>105</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D151" s="2">
         <v>362</v>
@@ -4524,7 +4521,7 @@
         <v>105</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D152" s="2">
         <v>479</v>
@@ -4550,7 +4547,7 @@
         <v>105</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D153" s="2">
         <v>317</v>
@@ -4576,7 +4573,7 @@
         <v>105</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D154" s="2">
         <v>240</v>
@@ -4602,7 +4599,7 @@
         <v>105</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D155" s="2">
         <v>290</v>
@@ -4628,7 +4625,7 @@
         <v>105</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D156" s="2">
         <v>477</v>
@@ -4654,7 +4651,7 @@
         <v>105</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D157" s="2">
         <v>362</v>
@@ -4680,7 +4677,7 @@
         <v>105</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D158" s="2">
         <v>54</v>
@@ -4706,7 +4703,7 @@
         <v>105</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D159" s="2">
         <v>281</v>
@@ -4732,7 +4729,7 @@
         <v>105</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D160" s="2">
         <v>381</v>
@@ -4758,7 +4755,7 @@
         <v>105</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D161" s="2">
         <v>351</v>
@@ -4784,7 +4781,7 @@
         <v>105</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D162" s="2">
         <v>309</v>
@@ -4810,7 +4807,7 @@
         <v>105</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D163" s="2">
         <v>383</v>
@@ -4836,7 +4833,7 @@
         <v>105</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D164" s="2">
         <v>407</v>
@@ -4862,7 +4859,7 @@
         <v>105</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D165" s="2">
         <v>171</v>
@@ -4888,7 +4885,7 @@
         <v>105</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D166" s="2">
         <v>274</v>
@@ -4914,7 +4911,7 @@
         <v>105</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D167" s="2">
         <v>295</v>
@@ -4940,7 +4937,7 @@
         <v>105</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D168" s="2">
         <v>418</v>
@@ -4966,7 +4963,7 @@
         <v>105</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D169" s="2">
         <v>84</v>
@@ -4992,7 +4989,7 @@
         <v>105</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D170" s="2">
         <v>247</v>
@@ -5018,7 +5015,7 @@
         <v>105</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D171" s="2">
         <v>179</v>
@@ -5044,7 +5041,7 @@
         <v>105</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D172" s="2">
         <v>322</v>
@@ -5070,7 +5067,7 @@
         <v>105</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D173" s="2">
         <v>271</v>
@@ -5096,7 +5093,7 @@
         <v>105</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D174" s="2">
         <v>281</v>
@@ -5122,7 +5119,7 @@
         <v>105</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D175" s="2">
         <v>174</v>
@@ -5148,7 +5145,7 @@
         <v>105</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D176" s="2">
         <v>305</v>
@@ -5174,7 +5171,7 @@
         <v>105</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D177" s="2">
         <v>254</v>
@@ -5200,7 +5197,7 @@
         <v>105</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D178" s="2">
         <v>312</v>
@@ -5226,7 +5223,7 @@
         <v>105</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D179" s="2">
         <v>115</v>
@@ -5252,7 +5249,7 @@
         <v>105</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D180" s="2">
         <v>161</v>
@@ -5278,7 +5275,7 @@
         <v>105</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D181" s="2">
         <v>240</v>
@@ -5304,7 +5301,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -5330,7 +5327,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5356,7 +5353,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5382,7 +5379,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5408,7 +5405,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -5434,7 +5431,7 @@
         <v>106</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D187" s="2">
         <v>342</v>
@@ -5460,7 +5457,7 @@
         <v>106</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D188" s="2">
         <v>285</v>
@@ -5486,7 +5483,7 @@
         <v>106</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D189" s="2">
         <v>453</v>
@@ -5512,7 +5509,7 @@
         <v>106</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D190" s="2">
         <v>69</v>
@@ -5538,7 +5535,7 @@
         <v>106</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D191" s="2">
         <v>154</v>
@@ -5564,7 +5561,7 @@
         <v>106</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D192" s="2">
         <v>246</v>
@@ -5590,7 +5587,7 @@
         <v>106</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D193" s="2">
         <v>446</v>
@@ -5616,7 +5613,7 @@
         <v>106</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D194" s="2">
         <v>467</v>
@@ -5642,7 +5639,7 @@
         <v>106</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D195" s="2">
         <v>374</v>
@@ -5668,7 +5665,7 @@
         <v>106</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D196" s="2">
         <v>266</v>
@@ -5694,7 +5691,7 @@
         <v>106</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D197" s="2">
         <v>281</v>
@@ -5720,7 +5717,7 @@
         <v>106</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D198" s="2">
         <v>277</v>
@@ -5746,7 +5743,7 @@
         <v>106</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D199" s="2">
         <v>153</v>
@@ -5772,7 +5769,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D200" s="2">
         <v>176</v>
@@ -5798,7 +5795,7 @@
         <v>106</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D201" s="2">
         <v>281</v>
@@ -5824,7 +5821,7 @@
         <v>106</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D202" s="2">
         <v>52</v>
@@ -5850,7 +5847,7 @@
         <v>106</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D203" s="2">
         <v>94</v>
@@ -5876,7 +5873,7 @@
         <v>106</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D204" s="2">
         <v>181</v>
@@ -5902,7 +5899,7 @@
         <v>106</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D205" s="2">
         <v>336</v>
@@ -5928,7 +5925,7 @@
         <v>106</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D206" s="2">
         <v>349</v>
@@ -5954,7 +5951,7 @@
         <v>106</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D207" s="2">
         <v>127</v>
@@ -5980,7 +5977,7 @@
         <v>106</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D208" s="2">
         <v>376</v>
@@ -6006,7 +6003,7 @@
         <v>106</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D209" s="2">
         <v>98</v>
@@ -6032,7 +6029,7 @@
         <v>106</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D210" s="2">
         <v>152</v>
@@ -6058,7 +6055,7 @@
         <v>106</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D211" s="2">
         <v>235</v>
@@ -6084,7 +6081,7 @@
         <v>106</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D212" s="2">
         <v>105</v>
@@ -6110,7 +6107,7 @@
         <v>106</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D213" s="2">
         <v>150</v>
@@ -6136,7 +6133,7 @@
         <v>106</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D214" s="2">
         <v>215</v>
@@ -6162,7 +6159,7 @@
         <v>106</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D215" s="2">
         <v>216</v>
@@ -6188,7 +6185,7 @@
         <v>106</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D216" s="2">
         <v>214</v>
@@ -6214,7 +6211,7 @@
         <v>106</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D217" s="2">
         <v>194</v>
@@ -6240,7 +6237,7 @@
         <v>107</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D218" s="2">
         <v>184</v>
@@ -6266,7 +6263,7 @@
         <v>107</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D219" s="2">
         <v>379</v>
@@ -6292,7 +6289,7 @@
         <v>107</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D220" s="2">
         <v>424</v>
@@ -6318,7 +6315,7 @@
         <v>107</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D221" s="2">
         <v>93</v>
@@ -6344,7 +6341,7 @@
         <v>107</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D222" s="2">
         <v>219</v>
@@ -6370,7 +6367,7 @@
         <v>107</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D223" s="2">
         <v>165</v>
@@ -6396,7 +6393,7 @@
         <v>107</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D224" s="2">
         <v>462</v>
@@ -6422,7 +6419,7 @@
         <v>107</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D225" s="2">
         <v>332</v>
@@ -6448,7 +6445,7 @@
         <v>107</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D226" s="2">
         <v>162</v>
@@ -6474,7 +6471,7 @@
         <v>107</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D227" s="2">
         <v>305</v>
@@ -6500,7 +6497,7 @@
         <v>107</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D228" s="2">
         <v>446</v>
@@ -6526,7 +6523,7 @@
         <v>107</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D229" s="2">
         <v>196</v>
@@ -6552,7 +6549,7 @@
         <v>107</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D230" s="2">
         <v>443</v>
@@ -6578,7 +6575,7 @@
         <v>107</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D231" s="2">
         <v>158</v>
@@ -6604,7 +6601,7 @@
         <v>107</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D232" s="2">
         <v>191</v>
@@ -6630,7 +6627,7 @@
         <v>107</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D233" s="2">
         <v>321</v>
@@ -6656,7 +6653,7 @@
         <v>107</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D234" s="2">
         <v>316</v>
@@ -6682,7 +6679,7 @@
         <v>107</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D235" s="2">
         <v>71</v>
@@ -6708,7 +6705,7 @@
         <v>107</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D236" s="2">
         <v>171</v>
@@ -6734,7 +6731,7 @@
         <v>107</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D237" s="2">
         <v>450</v>
@@ -6760,7 +6757,7 @@
         <v>107</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D238" s="2">
         <v>354</v>
@@ -6786,7 +6783,7 @@
         <v>107</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D239" s="2">
         <v>475</v>
@@ -6812,7 +6809,7 @@
         <v>107</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D240" s="2">
         <v>130</v>
@@ -6838,7 +6835,7 @@
         <v>107</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D241" s="2">
         <v>140</v>
@@ -6864,7 +6861,7 @@
         <v>107</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D242" s="2">
         <v>253</v>
@@ -6890,7 +6887,7 @@
         <v>107</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D243" s="2">
         <v>246</v>
@@ -6916,7 +6913,7 @@
         <v>107</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D244" s="2">
         <v>297</v>
@@ -6942,7 +6939,7 @@
         <v>107</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D245" s="2">
         <v>201</v>
@@ -6968,7 +6965,7 @@
         <v>107</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D246" s="2">
         <v>339</v>
@@ -6994,7 +6991,7 @@
         <v>107</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D247" s="2">
         <v>132</v>
@@ -7020,7 +7017,7 @@
         <v>107</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D248" s="2">
         <v>239</v>
@@ -7046,7 +7043,7 @@
         <v>107</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D249" s="2">
         <v>169</v>
@@ -7072,7 +7069,7 @@
         <v>107</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D250" s="2">
         <v>217</v>
@@ -7098,7 +7095,7 @@
         <v>107</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D251" s="2">
         <v>340</v>
@@ -7124,7 +7121,7 @@
         <v>107</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D252" s="2">
         <v>192</v>
@@ -7150,7 +7147,7 @@
         <v>107</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D253" s="2">
         <v>243</v>
@@ -7176,7 +7173,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -7202,7 +7199,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7228,7 +7225,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -7254,7 +7251,7 @@
         <v>108</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D257" s="2">
         <v>451</v>
@@ -7280,7 +7277,7 @@
         <v>108</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D258" s="2">
         <v>183</v>
@@ -7306,7 +7303,7 @@
         <v>108</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D259" s="2">
         <v>311</v>
@@ -7332,7 +7329,7 @@
         <v>108</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D260" s="2">
         <v>365</v>
@@ -7358,7 +7355,7 @@
         <v>108</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D261" s="2">
         <v>411</v>
@@ -7384,7 +7381,7 @@
         <v>108</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D262" s="2">
         <v>130</v>
@@ -7410,7 +7407,7 @@
         <v>108</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D263" s="2">
         <v>69</v>
@@ -7436,7 +7433,7 @@
         <v>108</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D264" s="2">
         <v>391</v>
@@ -7462,7 +7459,7 @@
         <v>108</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D265" s="2">
         <v>475</v>
@@ -7488,7 +7485,7 @@
         <v>108</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D266" s="2">
         <v>386</v>
@@ -7514,7 +7511,7 @@
         <v>108</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D267" s="2">
         <v>345</v>
@@ -7540,7 +7537,7 @@
         <v>108</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D268" s="2">
         <v>57</v>
@@ -7566,7 +7563,7 @@
         <v>108</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D269" s="2">
         <v>489</v>
@@ -7592,7 +7589,7 @@
         <v>108</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D270" s="2">
         <v>88</v>
@@ -7618,7 +7615,7 @@
         <v>108</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D271" s="2">
         <v>417</v>
@@ -7644,7 +7641,7 @@
         <v>108</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D272" s="2">
         <v>437</v>
@@ -7670,7 +7667,7 @@
         <v>108</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D273" s="2">
         <v>249</v>
@@ -7696,7 +7693,7 @@
         <v>108</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D274" s="2">
         <v>86</v>
@@ -7722,7 +7719,7 @@
         <v>108</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D275" s="2">
         <v>191</v>
@@ -7748,7 +7745,7 @@
         <v>108</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D276" s="2">
         <v>298</v>
@@ -7774,7 +7771,7 @@
         <v>108</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D277" s="2">
         <v>235</v>
@@ -7800,7 +7797,7 @@
         <v>108</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D278" s="2">
         <v>201</v>
@@ -7826,7 +7823,7 @@
         <v>108</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D279" s="2">
         <v>158</v>
@@ -7852,7 +7849,7 @@
         <v>108</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D280" s="2">
         <v>135</v>
@@ -7878,7 +7875,7 @@
         <v>108</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D281" s="2">
         <v>333</v>
@@ -7904,7 +7901,7 @@
         <v>108</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D282" s="2">
         <v>352</v>
@@ -7930,7 +7927,7 @@
         <v>108</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D283" s="2">
         <v>66</v>
@@ -7956,7 +7953,7 @@
         <v>108</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D284" s="2">
         <v>116</v>
@@ -7982,7 +7979,7 @@
         <v>108</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D285" s="2">
         <v>214</v>
@@ -8008,7 +8005,7 @@
         <v>108</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D286" s="2">
         <v>210</v>
@@ -8034,7 +8031,7 @@
         <v>108</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D287" s="2">
         <v>295</v>
@@ -8060,7 +8057,7 @@
         <v>108</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D288" s="2">
         <v>112</v>
@@ -8086,7 +8083,7 @@
         <v>108</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D289" s="2">
         <v>222</v>
@@ -8112,7 +8109,7 @@
         <v>109</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D290" s="2">
         <v>212</v>
@@ -8138,7 +8135,7 @@
         <v>109</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D291" s="2">
         <v>457</v>
@@ -8164,7 +8161,7 @@
         <v>109</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D292" s="2">
         <v>203</v>
@@ -8190,7 +8187,7 @@
         <v>109</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D293" s="2">
         <v>247</v>
@@ -8216,7 +8213,7 @@
         <v>109</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D294" s="2">
         <v>113</v>
@@ -8242,7 +8239,7 @@
         <v>109</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D295" s="2">
         <v>107</v>
@@ -8268,7 +8265,7 @@
         <v>109</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D296" s="2">
         <v>338</v>
@@ -8294,7 +8291,7 @@
         <v>109</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D297" s="2">
         <v>259</v>
@@ -8320,7 +8317,7 @@
         <v>109</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D298" s="2">
         <v>430</v>
@@ -8346,7 +8343,7 @@
         <v>109</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D299" s="2">
         <v>329</v>
@@ -8372,7 +8369,7 @@
         <v>109</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D300" s="2">
         <v>369</v>
@@ -8398,7 +8395,7 @@
         <v>109</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D301" s="2">
         <v>262</v>
@@ -8424,7 +8421,7 @@
         <v>109</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D302" s="2">
         <v>253</v>
@@ -8450,7 +8447,7 @@
         <v>109</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D303" s="2">
         <v>257</v>
@@ -8476,7 +8473,7 @@
         <v>109</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D304" s="2">
         <v>446</v>
@@ -8502,7 +8499,7 @@
         <v>109</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D305" s="2">
         <v>270</v>
@@ -8528,7 +8525,7 @@
         <v>109</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D306" s="2">
         <v>486</v>
@@ -8554,7 +8551,7 @@
         <v>109</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D307" s="2">
         <v>484</v>
@@ -8580,7 +8577,7 @@
         <v>109</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D308" s="2">
         <v>277</v>
@@ -8606,7 +8603,7 @@
         <v>109</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D309" s="2">
         <v>298</v>
@@ -8632,7 +8629,7 @@
         <v>109</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D310" s="2">
         <v>148</v>
@@ -8658,7 +8655,7 @@
         <v>109</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D311" s="2">
         <v>218</v>
@@ -8684,7 +8681,7 @@
         <v>109</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D312" s="2">
         <v>253</v>
@@ -8710,7 +8707,7 @@
         <v>109</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D313" s="2">
         <v>266</v>
@@ -8736,7 +8733,7 @@
         <v>109</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D314" s="2">
         <v>290</v>
@@ -8762,7 +8759,7 @@
         <v>109</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D315" s="2">
         <v>197</v>
@@ -8788,7 +8785,7 @@
         <v>109</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D316" s="2">
         <v>160</v>
@@ -8814,7 +8811,7 @@
         <v>109</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D317" s="2">
         <v>272</v>
@@ -8840,7 +8837,7 @@
         <v>109</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D318" s="2">
         <v>254</v>
@@ -8866,7 +8863,7 @@
         <v>109</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D319" s="2">
         <v>160</v>
@@ -8892,7 +8889,7 @@
         <v>109</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D320" s="2">
         <v>150</v>
@@ -8918,7 +8915,7 @@
         <v>109</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D321" s="2">
         <v>247</v>
@@ -8944,7 +8941,7 @@
         <v>109</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D322" s="2">
         <v>263</v>
@@ -8970,7 +8967,7 @@
         <v>109</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D323" s="2">
         <v>267</v>
@@ -8996,7 +8993,7 @@
         <v>109</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D324" s="2">
         <v>223</v>
@@ -9022,7 +9019,7 @@
         <v>109</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D325" s="2">
         <v>170</v>
@@ -9048,7 +9045,7 @@
         <v>110</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D326" s="2">
         <v>175</v>
@@ -9074,7 +9071,7 @@
         <v>110</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D327" s="2">
         <v>333</v>
@@ -9100,7 +9097,7 @@
         <v>110</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D328" s="2">
         <v>442</v>
@@ -9126,7 +9123,7 @@
         <v>110</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D329" s="2">
         <v>131</v>
@@ -9152,7 +9149,7 @@
         <v>110</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D330" s="2">
         <v>275</v>
@@ -9178,7 +9175,7 @@
         <v>110</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D331" s="2">
         <v>170</v>
@@ -9204,7 +9201,7 @@
         <v>110</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D332" s="2">
         <v>94</v>
@@ -9230,7 +9227,7 @@
         <v>110</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D333" s="2">
         <v>56</v>
@@ -9256,7 +9253,7 @@
         <v>110</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D334" s="2">
         <v>297</v>
@@ -9282,7 +9279,7 @@
         <v>110</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D335" s="2">
         <v>389</v>
@@ -9308,7 +9305,7 @@
         <v>110</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D336" s="2">
         <v>88</v>
@@ -9334,7 +9331,7 @@
         <v>110</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D337" s="2">
         <v>101</v>
@@ -9360,7 +9357,7 @@
         <v>110</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D338" s="2">
         <v>237</v>
@@ -9386,7 +9383,7 @@
         <v>110</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D339" s="2">
         <v>251</v>
@@ -9412,7 +9409,7 @@
         <v>110</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D340" s="2">
         <v>62</v>
@@ -9438,7 +9435,7 @@
         <v>110</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D341" s="2">
         <v>144</v>
@@ -9464,7 +9461,7 @@
         <v>110</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D342" s="2">
         <v>180</v>
@@ -9490,7 +9487,7 @@
         <v>110</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D343" s="2">
         <v>358</v>
@@ -9516,7 +9513,7 @@
         <v>110</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D344" s="2">
         <v>452</v>
@@ -9542,7 +9539,7 @@
         <v>110</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D345" s="2">
         <v>121</v>
@@ -9568,7 +9565,7 @@
         <v>110</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D346" s="2">
         <v>354</v>
@@ -9594,7 +9591,7 @@
         <v>110</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D347" s="2">
         <v>151</v>
@@ -9620,7 +9617,7 @@
         <v>110</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D348" s="2">
         <v>270</v>
@@ -9646,7 +9643,7 @@
         <v>110</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D349" s="2">
         <v>361</v>
@@ -9672,7 +9669,7 @@
         <v>110</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D350" s="2">
         <v>148</v>
@@ -9698,7 +9695,7 @@
         <v>110</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D351" s="2">
         <v>223</v>
@@ -9724,7 +9721,7 @@
         <v>110</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D352" s="2">
         <v>79</v>
@@ -9750,7 +9747,7 @@
         <v>110</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D353" s="2">
         <v>104</v>
@@ -9776,7 +9773,7 @@
         <v>110</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D354" s="2">
         <v>294</v>
@@ -9802,7 +9799,7 @@
         <v>110</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D355" s="2">
         <v>248</v>
@@ -9828,7 +9825,7 @@
         <v>110</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D356" s="2">
         <v>215</v>
@@ -9854,7 +9851,7 @@
         <v>110</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D357" s="2">
         <v>258</v>
@@ -9880,7 +9877,7 @@
         <v>110</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D358" s="2">
         <v>201</v>
@@ -9906,7 +9903,7 @@
         <v>110</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D359" s="2">
         <v>238</v>
@@ -9932,7 +9929,7 @@
         <v>110</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D360" s="2">
         <v>286</v>
@@ -9958,7 +9955,7 @@
         <v>110</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D361" s="2">
         <v>386</v>
@@ -9984,7 +9981,7 @@
         <v>111</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D362" s="2">
         <v>497</v>
@@ -10010,7 +10007,7 @@
         <v>111</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D363" s="2">
         <v>372</v>
@@ -10036,7 +10033,7 @@
         <v>111</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D364" s="2">
         <v>377</v>
@@ -10062,7 +10059,7 @@
         <v>111</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D365" s="2">
         <v>450</v>
@@ -10088,7 +10085,7 @@
         <v>111</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D366" s="2">
         <v>381</v>
@@ -10114,7 +10111,7 @@
         <v>111</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D367" s="2">
         <v>132</v>
@@ -10140,7 +10137,7 @@
         <v>111</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D368" s="2">
         <v>160</v>
@@ -10166,7 +10163,7 @@
         <v>111</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D369" s="2">
         <v>80</v>
@@ -10192,7 +10189,7 @@
         <v>111</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D370" s="2">
         <v>124</v>
@@ -10218,7 +10215,7 @@
         <v>111</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D371" s="2">
         <v>468</v>
@@ -10244,7 +10241,7 @@
         <v>111</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D372" s="2">
         <v>131</v>
@@ -10270,7 +10267,7 @@
         <v>111</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D373" s="2">
         <v>171</v>
@@ -10296,7 +10293,7 @@
         <v>111</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D374" s="2">
         <v>470</v>
@@ -10322,7 +10319,7 @@
         <v>111</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D375" s="2">
         <v>423</v>
@@ -10348,7 +10345,7 @@
         <v>111</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D376" s="2">
         <v>392</v>
@@ -10374,7 +10371,7 @@
         <v>111</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D377" s="2">
         <v>330</v>
@@ -10400,7 +10397,7 @@
         <v>111</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D378" s="2">
         <v>287</v>
@@ -10426,7 +10423,7 @@
         <v>111</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D379" s="2">
         <v>171</v>
@@ -10452,7 +10449,7 @@
         <v>111</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D380" s="2">
         <v>470</v>
@@ -10478,7 +10475,7 @@
         <v>111</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D381" s="2">
         <v>345</v>
@@ -10504,7 +10501,7 @@
         <v>111</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D382" s="2">
         <v>78</v>
@@ -10530,7 +10527,7 @@
         <v>111</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D383" s="2">
         <v>389</v>
@@ -10556,7 +10553,7 @@
         <v>111</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D384" s="2">
         <v>129</v>
@@ -10582,7 +10579,7 @@
         <v>111</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D385" s="2">
         <v>449</v>
@@ -10608,7 +10605,7 @@
         <v>111</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D386" s="2">
         <v>224</v>
@@ -10634,7 +10631,7 @@
         <v>111</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D387" s="2">
         <v>99</v>
@@ -10660,7 +10657,7 @@
         <v>111</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D388" s="2">
         <v>84</v>
@@ -10686,7 +10683,7 @@
         <v>111</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D389" s="2">
         <v>206</v>
@@ -10712,7 +10709,7 @@
         <v>111</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D390" s="2">
         <v>356</v>
@@ -10738,7 +10735,7 @@
         <v>111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D391" s="2">
         <v>370</v>
@@ -10764,7 +10761,7 @@
         <v>111</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D392" s="2">
         <v>211</v>
@@ -10790,7 +10787,7 @@
         <v>111</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D393" s="2">
         <v>198</v>
@@ -10816,7 +10813,7 @@
         <v>111</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D394" s="2">
         <v>246</v>
@@ -10842,7 +10839,7 @@
         <v>111</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D395" s="2">
         <v>119</v>
@@ -10868,7 +10865,7 @@
         <v>111</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D396" s="2">
         <v>228</v>
@@ -10894,7 +10891,7 @@
         <v>111</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D397" s="2">
         <v>166</v>
@@ -10920,7 +10917,7 @@
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D398" s="2">
         <v>421</v>
@@ -10946,7 +10943,7 @@
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D399" s="2">
         <v>99</v>
@@ -10972,7 +10969,7 @@
         <v>112</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D400" s="2">
         <v>474</v>
@@ -10998,7 +10995,7 @@
         <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D401" s="2">
         <v>398</v>
@@ -11024,7 +11021,7 @@
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D402" s="2">
         <v>147</v>
@@ -11050,7 +11047,7 @@
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D403" s="2">
         <v>443</v>
@@ -11076,7 +11073,7 @@
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D404" s="2">
         <v>259</v>
@@ -11102,7 +11099,7 @@
         <v>112</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D405" s="2">
         <v>264</v>
@@ -11128,7 +11125,7 @@
         <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D406" s="2">
         <v>450</v>
@@ -11154,7 +11151,7 @@
         <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D407" s="2">
         <v>490</v>
@@ -11180,7 +11177,7 @@
         <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D408" s="2">
         <v>457</v>
@@ -11206,7 +11203,7 @@
         <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D409" s="2">
         <v>481</v>
@@ -11232,7 +11229,7 @@
         <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D410" s="2">
         <v>452</v>
@@ -11258,7 +11255,7 @@
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D411" s="2">
         <v>194</v>
@@ -11284,7 +11281,7 @@
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D412" s="2">
         <v>399</v>
@@ -11310,7 +11307,7 @@
         <v>112</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D413" s="2">
         <v>264</v>
@@ -11336,7 +11333,7 @@
         <v>112</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D414" s="2">
         <v>109</v>
@@ -11362,7 +11359,7 @@
         <v>112</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D415" s="2">
         <v>437</v>
@@ -11388,7 +11385,7 @@
         <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D416" s="2">
         <v>447</v>
@@ -11414,7 +11411,7 @@
         <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D417" s="2">
         <v>421</v>
@@ -11440,7 +11437,7 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D418" s="2">
         <v>80</v>
@@ -11466,7 +11463,7 @@
         <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D419" s="2">
         <v>493</v>
@@ -11492,7 +11489,7 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D420" s="2">
         <v>105</v>
@@ -11518,7 +11515,7 @@
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D421" s="2">
         <v>432</v>
@@ -11544,7 +11541,7 @@
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D422" s="2">
         <v>332</v>
@@ -11570,7 +11567,7 @@
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D423" s="2">
         <v>238</v>
@@ -11596,7 +11593,7 @@
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D424" s="2">
         <v>300</v>
@@ -11622,7 +11619,7 @@
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D425" s="2">
         <v>249</v>
@@ -11648,7 +11645,7 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D426" s="2">
         <v>336</v>
@@ -11674,7 +11671,7 @@
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D427" s="2">
         <v>114</v>
@@ -11700,7 +11697,7 @@
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D428" s="2">
         <v>175</v>
@@ -11726,7 +11723,7 @@
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D429" s="2">
         <v>473</v>
@@ -11752,7 +11749,7 @@
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D430" s="2">
         <v>202</v>
@@ -11778,7 +11775,7 @@
         <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D431" s="2">
         <v>215</v>
@@ -11804,7 +11801,7 @@
         <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D432" s="2">
         <v>252</v>
@@ -11830,7 +11827,7 @@
         <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D433" s="2">
         <v>223</v>
@@ -11856,7 +11853,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>
@@ -11882,7 +11879,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11908,7 +11905,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11934,7 +11931,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>
@@ -11960,7 +11957,7 @@
         <v>113</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D438" s="2">
         <v>219</v>
@@ -11986,7 +11983,7 @@
         <v>113</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D439" s="2">
         <v>99</v>
@@ -12012,7 +12009,7 @@
         <v>113</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D440" s="2">
         <v>177</v>
@@ -12038,7 +12035,7 @@
         <v>113</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D441" s="2">
         <v>380</v>
@@ -12064,7 +12061,7 @@
         <v>113</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D442" s="2">
         <v>464</v>
@@ -12090,7 +12087,7 @@
         <v>113</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D443" s="2">
         <v>460</v>
@@ -12116,7 +12113,7 @@
         <v>113</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D444" s="2">
         <v>299</v>
@@ -12142,7 +12139,7 @@
         <v>113</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D445" s="2">
         <v>243</v>
@@ -12168,7 +12165,7 @@
         <v>113</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D446" s="2">
         <v>154</v>
@@ -12194,7 +12191,7 @@
         <v>113</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D447" s="2">
         <v>239</v>
@@ -12220,7 +12217,7 @@
         <v>113</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D448" s="2">
         <v>410</v>
@@ -12246,7 +12243,7 @@
         <v>113</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D449" s="2">
         <v>273</v>
@@ -12272,7 +12269,7 @@
         <v>113</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D450" s="2">
         <v>90</v>
@@ -12298,7 +12295,7 @@
         <v>113</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D451" s="2">
         <v>407</v>
@@ -12324,7 +12321,7 @@
         <v>113</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D452" s="2">
         <v>301</v>
@@ -12350,7 +12347,7 @@
         <v>113</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D453" s="2">
         <v>181</v>
@@ -12376,7 +12373,7 @@
         <v>113</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D454" s="2">
         <v>186</v>
@@ -12402,7 +12399,7 @@
         <v>113</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D455" s="2">
         <v>424</v>
@@ -12428,7 +12425,7 @@
         <v>113</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D456" s="2">
         <v>268</v>
@@ -12454,7 +12451,7 @@
         <v>113</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D457" s="2">
         <v>277</v>
@@ -12480,7 +12477,7 @@
         <v>113</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D458" s="2">
         <v>89</v>
@@ -12506,7 +12503,7 @@
         <v>113</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D459" s="2">
         <v>219</v>
@@ -12532,7 +12529,7 @@
         <v>113</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D460" s="2">
         <v>273</v>
@@ -12558,7 +12555,7 @@
         <v>113</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D461" s="2">
         <v>254</v>
@@ -12584,7 +12581,7 @@
         <v>113</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D462" s="2">
         <v>243</v>
@@ -12610,7 +12607,7 @@
         <v>113</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D463" s="2">
         <v>349</v>
@@ -12636,7 +12633,7 @@
         <v>113</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D464" s="2">
         <v>245</v>
@@ -12662,7 +12659,7 @@
         <v>113</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D465" s="2">
         <v>174</v>
@@ -12688,7 +12685,7 @@
         <v>113</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D466" s="2">
         <v>80</v>
@@ -12714,7 +12711,7 @@
         <v>113</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D467" s="2">
         <v>210</v>
@@ -12740,7 +12737,7 @@
         <v>113</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D468" s="2">
         <v>281</v>
@@ -12766,7 +12763,7 @@
         <v>113</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D469" s="2">
         <v>80</v>
@@ -12792,7 +12789,7 @@
         <v>114</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D470" s="2">
         <v>106</v>
@@ -12818,7 +12815,7 @@
         <v>114</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D471" s="2">
         <v>53</v>
@@ -12844,7 +12841,7 @@
         <v>114</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D472" s="2">
         <v>80</v>
@@ -12870,7 +12867,7 @@
         <v>114</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D473" s="2">
         <v>92</v>
@@ -12896,7 +12893,7 @@
         <v>114</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D474" s="2">
         <v>146</v>
@@ -12922,7 +12919,7 @@
         <v>114</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D475" s="2">
         <v>465</v>
@@ -12948,7 +12945,7 @@
         <v>114</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D476" s="2">
         <v>361</v>
@@ -12974,7 +12971,7 @@
         <v>114</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D477" s="2">
         <v>420</v>
@@ -13000,7 +12997,7 @@
         <v>114</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D478" s="2">
         <v>471</v>
@@ -13026,7 +13023,7 @@
         <v>114</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D479" s="2">
         <v>174</v>
@@ -13052,7 +13049,7 @@
         <v>114</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D480" s="2">
         <v>95</v>
@@ -13078,7 +13075,7 @@
         <v>114</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D481" s="2">
         <v>305</v>
@@ -13104,7 +13101,7 @@
         <v>114</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D482" s="2">
         <v>465</v>
@@ -13130,7 +13127,7 @@
         <v>114</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D483" s="2">
         <v>418</v>
@@ -13156,7 +13153,7 @@
         <v>114</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D484" s="2">
         <v>478</v>
@@ -13182,7 +13179,7 @@
         <v>114</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D485" s="2">
         <v>434</v>
@@ -13208,7 +13205,7 @@
         <v>114</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D486" s="2">
         <v>459</v>
@@ -13234,7 +13231,7 @@
         <v>114</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D487" s="2">
         <v>99</v>
@@ -13260,7 +13257,7 @@
         <v>114</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D488" s="2">
         <v>104</v>
@@ -13286,7 +13283,7 @@
         <v>114</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D489" s="2">
         <v>166</v>
@@ -13312,7 +13309,7 @@
         <v>114</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D490" s="2">
         <v>277</v>
@@ -13338,7 +13335,7 @@
         <v>114</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D491" s="2">
         <v>329</v>
@@ -13364,7 +13361,7 @@
         <v>114</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D492" s="2">
         <v>193</v>
@@ -13390,7 +13387,7 @@
         <v>114</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D493" s="2">
         <v>70</v>
@@ -13416,7 +13413,7 @@
         <v>114</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D494" s="2">
         <v>174</v>
@@ -13442,7 +13439,7 @@
         <v>114</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D495" s="2">
         <v>305</v>
@@ -13468,7 +13465,7 @@
         <v>114</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D496" s="2">
         <v>274</v>
@@ -13494,7 +13491,7 @@
         <v>114</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D497" s="2">
         <v>185</v>
@@ -13520,7 +13517,7 @@
         <v>114</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D498" s="2">
         <v>249</v>
@@ -13546,7 +13543,7 @@
         <v>114</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D499" s="2">
         <v>203</v>
@@ -13572,7 +13569,7 @@
         <v>114</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D500" s="2">
         <v>315</v>
@@ -13598,7 +13595,7 @@
         <v>114</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D501" s="2">
         <v>211</v>
@@ -13624,7 +13621,7 @@
         <v>114</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D502" s="2">
         <v>262</v>
@@ -13650,7 +13647,7 @@
         <v>114</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D503" s="2">
         <v>346</v>
@@ -13676,7 +13673,7 @@
         <v>114</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D504" s="2">
         <v>232</v>
@@ -13702,7 +13699,7 @@
         <v>114</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D505" s="2">
         <v>142</v>
@@ -13728,7 +13725,7 @@
         <v>115</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D506" s="2">
         <v>316</v>
@@ -13754,7 +13751,7 @@
         <v>115</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D507" s="2">
         <v>221</v>
@@ -13780,7 +13777,7 @@
         <v>115</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D508" s="2">
         <v>318</v>
@@ -13806,7 +13803,7 @@
         <v>115</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D509" s="2">
         <v>147</v>
@@ -13832,7 +13829,7 @@
         <v>115</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D510" s="2">
         <v>396</v>
@@ -13858,7 +13855,7 @@
         <v>115</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D511" s="2">
         <v>409</v>
@@ -13884,7 +13881,7 @@
         <v>115</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D512" s="2">
         <v>278</v>
@@ -13910,7 +13907,7 @@
         <v>115</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D513" s="2">
         <v>103</v>
@@ -13936,7 +13933,7 @@
         <v>115</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D514" s="2">
         <v>419</v>
@@ -13962,7 +13959,7 @@
         <v>115</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D515" s="2">
         <v>243</v>
@@ -13988,7 +13985,7 @@
         <v>115</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D516" s="2">
         <v>280</v>
@@ -14014,7 +14011,7 @@
         <v>115</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D517" s="2">
         <v>206</v>
@@ -14040,7 +14037,7 @@
         <v>115</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D518" s="2">
         <v>114</v>
@@ -14066,7 +14063,7 @@
         <v>115</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D519" s="2">
         <v>58</v>
@@ -14092,7 +14089,7 @@
         <v>115</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D520" s="2">
         <v>198</v>
@@ -14118,7 +14115,7 @@
         <v>115</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D521" s="2">
         <v>138</v>
@@ -14144,7 +14141,7 @@
         <v>115</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D522" s="2">
         <v>417</v>
@@ -14170,7 +14167,7 @@
         <v>115</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D523" s="2">
         <v>141</v>
@@ -14196,7 +14193,7 @@
         <v>115</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D524" s="2">
         <v>456</v>
@@ -14222,7 +14219,7 @@
         <v>115</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D525" s="2">
         <v>316</v>
@@ -14248,7 +14245,7 @@
         <v>115</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D526" s="2">
         <v>357</v>
@@ -14274,7 +14271,7 @@
         <v>115</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D527" s="2">
         <v>143</v>
@@ -14300,7 +14297,7 @@
         <v>115</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D528" s="2">
         <v>177</v>
@@ -14326,7 +14323,7 @@
         <v>115</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D529" s="2">
         <v>226</v>
@@ -14352,7 +14349,7 @@
         <v>115</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D530" s="2">
         <v>344</v>
@@ -14378,7 +14375,7 @@
         <v>115</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D531" s="2">
         <v>143</v>
@@ -14404,7 +14401,7 @@
         <v>115</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D532" s="2">
         <v>97</v>
@@ -14430,7 +14427,7 @@
         <v>115</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D533" s="2">
         <v>193</v>
@@ -14456,7 +14453,7 @@
         <v>115</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D534" s="2">
         <v>56</v>
@@ -14482,7 +14479,7 @@
         <v>115</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D535" s="2">
         <v>121</v>
@@ -14508,7 +14505,7 @@
         <v>115</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D536" s="2">
         <v>150</v>
@@ -14534,7 +14531,7 @@
         <v>115</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D537" s="2">
         <v>344</v>
@@ -14560,7 +14557,7 @@
         <v>115</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D538" s="2">
         <v>188</v>
@@ -14586,7 +14583,7 @@
         <v>115</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D539" s="2">
         <v>342</v>
@@ -14612,7 +14609,7 @@
         <v>115</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D540" s="2">
         <v>234</v>
@@ -14638,7 +14635,7 @@
         <v>115</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D541" s="2">
         <v>239</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="60">
   <si>
     <t>Month</t>
   </si>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t>Tomato Sauce</t>
-  </si>
-  <si>
-    <t>Butter</t>
   </si>
   <si>
     <t>Juice</t>
@@ -621,7 +618,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" s="2">
         <v>373</v>
@@ -647,7 +644,7 @@
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2">
         <v>423</v>
@@ -673,7 +670,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2">
         <v>147</v>
@@ -699,7 +696,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2">
         <v>431</v>
@@ -725,7 +722,7 @@
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" s="2">
         <v>305</v>
@@ -751,7 +748,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2">
         <v>167</v>
@@ -777,7 +774,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2">
         <v>101</v>
@@ -803,7 +800,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2">
         <v>73</v>
@@ -829,7 +826,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2">
         <v>445</v>
@@ -855,7 +852,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2">
         <v>180</v>
@@ -881,7 +878,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="2">
         <v>221</v>
@@ -907,7 +904,7 @@
         <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="2">
         <v>153</v>
@@ -933,7 +930,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2">
         <v>283</v>
@@ -959,7 +956,7 @@
         <v>101</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="2">
         <v>220</v>
@@ -985,7 +982,7 @@
         <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="2">
         <v>338</v>
@@ -1011,7 +1008,7 @@
         <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2">
         <v>209</v>
@@ -1037,7 +1034,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2">
         <v>186</v>
@@ -1063,7 +1060,7 @@
         <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="2">
         <v>383</v>
@@ -1089,7 +1086,7 @@
         <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2">
         <v>253</v>
@@ -1115,7 +1112,7 @@
         <v>101</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2">
         <v>159</v>
@@ -1141,7 +1138,7 @@
         <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2">
         <v>212</v>
@@ -1167,7 +1164,7 @@
         <v>101</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2">
         <v>377</v>
@@ -1193,7 +1190,7 @@
         <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24" s="2">
         <v>126</v>
@@ -1219,7 +1216,7 @@
         <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2">
         <v>283</v>
@@ -1245,7 +1242,7 @@
         <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" s="2">
         <v>235</v>
@@ -1271,7 +1268,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27" s="2">
         <v>170</v>
@@ -1297,7 +1294,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2">
         <v>321</v>
@@ -1323,7 +1320,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2">
         <v>127</v>
@@ -1349,7 +1346,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="2">
         <v>162</v>
@@ -1375,7 +1372,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2">
         <v>265</v>
@@ -1401,7 +1398,7 @@
         <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32" s="2">
         <v>193</v>
@@ -1427,7 +1424,7 @@
         <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2">
         <v>211</v>
@@ -1453,7 +1450,7 @@
         <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D34" s="2">
         <v>328</v>
@@ -1479,7 +1476,7 @@
         <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D35" s="2">
         <v>127</v>
@@ -1505,7 +1502,7 @@
         <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2">
         <v>176</v>
@@ -1531,7 +1528,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2">
         <v>278</v>
@@ -1557,7 +1554,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1583,7 +1580,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1609,7 +1606,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1635,7 +1632,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1661,7 +1658,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1687,7 +1684,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1713,7 +1710,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1739,7 +1736,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1765,7 +1762,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1791,7 +1788,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1817,7 +1814,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1843,7 +1840,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1869,7 +1866,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1895,7 +1892,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1921,7 +1918,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1947,7 +1944,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1973,7 +1970,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -1999,7 +1996,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2025,7 +2022,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2051,7 +2048,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2077,7 +2074,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2103,7 +2100,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2129,7 +2126,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2155,7 +2152,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2181,7 +2178,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2207,7 +2204,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2233,7 +2230,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2259,7 +2256,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2285,7 +2282,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2311,7 +2308,7 @@
         <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D67" s="2">
         <v>259</v>
@@ -2337,7 +2334,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>
@@ -2363,7 +2360,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D69" s="2">
         <v>173</v>
@@ -2389,7 +2386,7 @@
         <v>102</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D70" s="2">
         <v>186</v>
@@ -2415,7 +2412,7 @@
         <v>102</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D71" s="2">
         <v>274</v>
@@ -2441,7 +2438,7 @@
         <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D72" s="2">
         <v>238</v>
@@ -2467,7 +2464,7 @@
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D73" s="2">
         <v>109</v>
@@ -3429,7 +3426,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3455,7 +3452,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3481,7 +3478,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3507,7 +3504,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3533,7 +3530,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3559,7 +3556,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3585,7 +3582,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3611,7 +3608,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3637,7 +3634,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3663,7 +3660,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3689,7 +3686,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>
@@ -3715,7 +3712,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3741,7 +3738,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3767,7 +3764,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3793,7 +3790,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3819,7 +3816,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3845,7 +3842,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -3871,7 +3868,7 @@
         <v>104</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D127" s="2">
         <v>141</v>
@@ -3897,7 +3894,7 @@
         <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D128" s="2">
         <v>303</v>
@@ -3923,7 +3920,7 @@
         <v>104</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D129" s="2">
         <v>281</v>
@@ -3949,7 +3946,7 @@
         <v>104</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D130" s="2">
         <v>453</v>
@@ -3975,7 +3972,7 @@
         <v>104</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D131" s="2">
         <v>310</v>
@@ -4001,7 +3998,7 @@
         <v>104</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D132" s="2">
         <v>243</v>
@@ -4027,7 +4024,7 @@
         <v>104</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D133" s="2">
         <v>248</v>
@@ -4053,7 +4050,7 @@
         <v>104</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D134" s="2">
         <v>253</v>
@@ -4079,7 +4076,7 @@
         <v>104</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D135" s="2">
         <v>197</v>
@@ -4105,7 +4102,7 @@
         <v>104</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D136" s="2">
         <v>184</v>
@@ -4131,7 +4128,7 @@
         <v>104</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D137" s="2">
         <v>119</v>
@@ -4157,7 +4154,7 @@
         <v>104</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D138" s="2">
         <v>192</v>
@@ -4183,7 +4180,7 @@
         <v>104</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D139" s="2">
         <v>237</v>
@@ -4209,7 +4206,7 @@
         <v>104</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D140" s="2">
         <v>71</v>
@@ -4235,7 +4232,7 @@
         <v>104</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D141" s="2">
         <v>170</v>
@@ -4261,7 +4258,7 @@
         <v>104</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D142" s="2">
         <v>201</v>
@@ -4287,7 +4284,7 @@
         <v>104</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D143" s="2">
         <v>226</v>
@@ -4313,7 +4310,7 @@
         <v>104</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D144" s="2">
         <v>251</v>
@@ -4339,7 +4336,7 @@
         <v>104</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D145" s="2">
         <v>281</v>
@@ -5301,7 +5298,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -5327,7 +5324,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5353,7 +5350,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5379,7 +5376,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5405,7 +5402,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -5431,7 +5428,7 @@
         <v>106</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D187" s="2">
         <v>342</v>
@@ -5457,7 +5454,7 @@
         <v>106</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D188" s="2">
         <v>285</v>
@@ -5483,7 +5480,7 @@
         <v>106</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D189" s="2">
         <v>453</v>
@@ -5509,7 +5506,7 @@
         <v>106</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D190" s="2">
         <v>69</v>
@@ -5535,7 +5532,7 @@
         <v>106</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D191" s="2">
         <v>154</v>
@@ -5561,7 +5558,7 @@
         <v>106</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D192" s="2">
         <v>246</v>
@@ -5587,7 +5584,7 @@
         <v>106</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D193" s="2">
         <v>446</v>
@@ -5613,7 +5610,7 @@
         <v>106</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D194" s="2">
         <v>467</v>
@@ -5639,7 +5636,7 @@
         <v>106</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D195" s="2">
         <v>374</v>
@@ -5665,7 +5662,7 @@
         <v>106</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D196" s="2">
         <v>266</v>
@@ -5691,7 +5688,7 @@
         <v>106</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D197" s="2">
         <v>281</v>
@@ -5717,7 +5714,7 @@
         <v>106</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D198" s="2">
         <v>277</v>
@@ -5743,7 +5740,7 @@
         <v>106</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D199" s="2">
         <v>153</v>
@@ -5769,7 +5766,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D200" s="2">
         <v>176</v>
@@ -5795,7 +5792,7 @@
         <v>106</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D201" s="2">
         <v>281</v>
@@ -5821,7 +5818,7 @@
         <v>106</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D202" s="2">
         <v>52</v>
@@ -5847,7 +5844,7 @@
         <v>106</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D203" s="2">
         <v>94</v>
@@ -5873,7 +5870,7 @@
         <v>106</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D204" s="2">
         <v>181</v>
@@ -5899,7 +5896,7 @@
         <v>106</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D205" s="2">
         <v>336</v>
@@ -5925,7 +5922,7 @@
         <v>106</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D206" s="2">
         <v>349</v>
@@ -5951,7 +5948,7 @@
         <v>106</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D207" s="2">
         <v>127</v>
@@ -5977,7 +5974,7 @@
         <v>106</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D208" s="2">
         <v>376</v>
@@ -6003,7 +6000,7 @@
         <v>106</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D209" s="2">
         <v>98</v>
@@ -6029,7 +6026,7 @@
         <v>106</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D210" s="2">
         <v>152</v>
@@ -6055,7 +6052,7 @@
         <v>106</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D211" s="2">
         <v>235</v>
@@ -6081,7 +6078,7 @@
         <v>106</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D212" s="2">
         <v>105</v>
@@ -6107,7 +6104,7 @@
         <v>106</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D213" s="2">
         <v>150</v>
@@ -6133,7 +6130,7 @@
         <v>106</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D214" s="2">
         <v>215</v>
@@ -6159,7 +6156,7 @@
         <v>106</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D215" s="2">
         <v>216</v>
@@ -6185,7 +6182,7 @@
         <v>106</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D216" s="2">
         <v>214</v>
@@ -6211,7 +6208,7 @@
         <v>106</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D217" s="2">
         <v>194</v>
@@ -7173,7 +7170,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -7199,7 +7196,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7225,7 +7222,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -7251,7 +7248,7 @@
         <v>108</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D257" s="2">
         <v>451</v>
@@ -7277,7 +7274,7 @@
         <v>108</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D258" s="2">
         <v>183</v>
@@ -7303,7 +7300,7 @@
         <v>108</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D259" s="2">
         <v>311</v>
@@ -7329,7 +7326,7 @@
         <v>108</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D260" s="2">
         <v>365</v>
@@ -7355,7 +7352,7 @@
         <v>108</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D261" s="2">
         <v>411</v>
@@ -7381,7 +7378,7 @@
         <v>108</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D262" s="2">
         <v>130</v>
@@ -7407,7 +7404,7 @@
         <v>108</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D263" s="2">
         <v>69</v>
@@ -7433,7 +7430,7 @@
         <v>108</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D264" s="2">
         <v>391</v>
@@ -7459,7 +7456,7 @@
         <v>108</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D265" s="2">
         <v>475</v>
@@ -7485,7 +7482,7 @@
         <v>108</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D266" s="2">
         <v>386</v>
@@ -7511,7 +7508,7 @@
         <v>108</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D267" s="2">
         <v>345</v>
@@ -7537,7 +7534,7 @@
         <v>108</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D268" s="2">
         <v>57</v>
@@ -7563,7 +7560,7 @@
         <v>108</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D269" s="2">
         <v>489</v>
@@ -7589,7 +7586,7 @@
         <v>108</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D270" s="2">
         <v>88</v>
@@ -7615,7 +7612,7 @@
         <v>108</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D271" s="2">
         <v>417</v>
@@ -7641,7 +7638,7 @@
         <v>108</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D272" s="2">
         <v>437</v>
@@ -7667,7 +7664,7 @@
         <v>108</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D273" s="2">
         <v>249</v>
@@ -7693,7 +7690,7 @@
         <v>108</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D274" s="2">
         <v>86</v>
@@ -7719,7 +7716,7 @@
         <v>108</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D275" s="2">
         <v>191</v>
@@ -7745,7 +7742,7 @@
         <v>108</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D276" s="2">
         <v>298</v>
@@ -7771,7 +7768,7 @@
         <v>108</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D277" s="2">
         <v>235</v>
@@ -7797,7 +7794,7 @@
         <v>108</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D278" s="2">
         <v>201</v>
@@ -7823,7 +7820,7 @@
         <v>108</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D279" s="2">
         <v>158</v>
@@ -7849,7 +7846,7 @@
         <v>108</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D280" s="2">
         <v>135</v>
@@ -7875,7 +7872,7 @@
         <v>108</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D281" s="2">
         <v>333</v>
@@ -7901,7 +7898,7 @@
         <v>108</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D282" s="2">
         <v>352</v>
@@ -7927,7 +7924,7 @@
         <v>108</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D283" s="2">
         <v>66</v>
@@ -7953,7 +7950,7 @@
         <v>108</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D284" s="2">
         <v>116</v>
@@ -7979,7 +7976,7 @@
         <v>108</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D285" s="2">
         <v>214</v>
@@ -8005,7 +8002,7 @@
         <v>108</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D286" s="2">
         <v>210</v>
@@ -8031,7 +8028,7 @@
         <v>108</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D287" s="2">
         <v>295</v>
@@ -8057,7 +8054,7 @@
         <v>108</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D288" s="2">
         <v>112</v>
@@ -8083,7 +8080,7 @@
         <v>108</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D289" s="2">
         <v>222</v>
@@ -9045,7 +9042,7 @@
         <v>110</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D326" s="2">
         <v>175</v>
@@ -9071,7 +9068,7 @@
         <v>110</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D327" s="2">
         <v>333</v>
@@ -9097,7 +9094,7 @@
         <v>110</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D328" s="2">
         <v>442</v>
@@ -9123,7 +9120,7 @@
         <v>110</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D329" s="2">
         <v>131</v>
@@ -9149,7 +9146,7 @@
         <v>110</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D330" s="2">
         <v>275</v>
@@ -9175,7 +9172,7 @@
         <v>110</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D331" s="2">
         <v>170</v>
@@ -9201,7 +9198,7 @@
         <v>110</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D332" s="2">
         <v>94</v>
@@ -9227,7 +9224,7 @@
         <v>110</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D333" s="2">
         <v>56</v>
@@ -9253,7 +9250,7 @@
         <v>110</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D334" s="2">
         <v>297</v>
@@ -9279,7 +9276,7 @@
         <v>110</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D335" s="2">
         <v>389</v>
@@ -9305,7 +9302,7 @@
         <v>110</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D336" s="2">
         <v>88</v>
@@ -9331,7 +9328,7 @@
         <v>110</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D337" s="2">
         <v>101</v>
@@ -9357,7 +9354,7 @@
         <v>110</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D338" s="2">
         <v>237</v>
@@ -9383,7 +9380,7 @@
         <v>110</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D339" s="2">
         <v>251</v>
@@ -9409,7 +9406,7 @@
         <v>110</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D340" s="2">
         <v>62</v>
@@ -9435,7 +9432,7 @@
         <v>110</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D341" s="2">
         <v>144</v>
@@ -9461,7 +9458,7 @@
         <v>110</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D342" s="2">
         <v>180</v>
@@ -9487,7 +9484,7 @@
         <v>110</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D343" s="2">
         <v>358</v>
@@ -9513,7 +9510,7 @@
         <v>110</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D344" s="2">
         <v>452</v>
@@ -9539,7 +9536,7 @@
         <v>110</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D345" s="2">
         <v>121</v>
@@ -9565,7 +9562,7 @@
         <v>110</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D346" s="2">
         <v>354</v>
@@ -9591,7 +9588,7 @@
         <v>110</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D347" s="2">
         <v>151</v>
@@ -9617,7 +9614,7 @@
         <v>110</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D348" s="2">
         <v>270</v>
@@ -9643,7 +9640,7 @@
         <v>110</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D349" s="2">
         <v>361</v>
@@ -9669,7 +9666,7 @@
         <v>110</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D350" s="2">
         <v>148</v>
@@ -9695,7 +9692,7 @@
         <v>110</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D351" s="2">
         <v>223</v>
@@ -9721,7 +9718,7 @@
         <v>110</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D352" s="2">
         <v>79</v>
@@ -9747,7 +9744,7 @@
         <v>110</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D353" s="2">
         <v>104</v>
@@ -9773,7 +9770,7 @@
         <v>110</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D354" s="2">
         <v>294</v>
@@ -9799,7 +9796,7 @@
         <v>110</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D355" s="2">
         <v>248</v>
@@ -9825,7 +9822,7 @@
         <v>110</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D356" s="2">
         <v>215</v>
@@ -9851,7 +9848,7 @@
         <v>110</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D357" s="2">
         <v>258</v>
@@ -9877,7 +9874,7 @@
         <v>110</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D358" s="2">
         <v>201</v>
@@ -9903,7 +9900,7 @@
         <v>110</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D359" s="2">
         <v>238</v>
@@ -9929,7 +9926,7 @@
         <v>110</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D360" s="2">
         <v>286</v>
@@ -9955,7 +9952,7 @@
         <v>110</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D361" s="2">
         <v>386</v>
@@ -9981,7 +9978,7 @@
         <v>111</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D362" s="2">
         <v>497</v>
@@ -10007,7 +10004,7 @@
         <v>111</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D363" s="2">
         <v>372</v>
@@ -10033,7 +10030,7 @@
         <v>111</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D364" s="2">
         <v>377</v>
@@ -10059,7 +10056,7 @@
         <v>111</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D365" s="2">
         <v>450</v>
@@ -10085,7 +10082,7 @@
         <v>111</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D366" s="2">
         <v>381</v>
@@ -10111,7 +10108,7 @@
         <v>111</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D367" s="2">
         <v>132</v>
@@ -10137,7 +10134,7 @@
         <v>111</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D368" s="2">
         <v>160</v>
@@ -10163,7 +10160,7 @@
         <v>111</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D369" s="2">
         <v>80</v>
@@ -10189,7 +10186,7 @@
         <v>111</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D370" s="2">
         <v>124</v>
@@ -10215,7 +10212,7 @@
         <v>111</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D371" s="2">
         <v>468</v>
@@ -10241,7 +10238,7 @@
         <v>111</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D372" s="2">
         <v>131</v>
@@ -10267,7 +10264,7 @@
         <v>111</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D373" s="2">
         <v>171</v>
@@ -10293,7 +10290,7 @@
         <v>111</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D374" s="2">
         <v>470</v>
@@ -10319,7 +10316,7 @@
         <v>111</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D375" s="2">
         <v>423</v>
@@ -10345,7 +10342,7 @@
         <v>111</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D376" s="2">
         <v>392</v>
@@ -10371,7 +10368,7 @@
         <v>111</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D377" s="2">
         <v>330</v>
@@ -10397,7 +10394,7 @@
         <v>111</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D378" s="2">
         <v>287</v>
@@ -10423,7 +10420,7 @@
         <v>111</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D379" s="2">
         <v>171</v>
@@ -10449,7 +10446,7 @@
         <v>111</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D380" s="2">
         <v>470</v>
@@ -10475,7 +10472,7 @@
         <v>111</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D381" s="2">
         <v>345</v>
@@ -10501,7 +10498,7 @@
         <v>111</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D382" s="2">
         <v>78</v>
@@ -10527,7 +10524,7 @@
         <v>111</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D383" s="2">
         <v>389</v>
@@ -10553,7 +10550,7 @@
         <v>111</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D384" s="2">
         <v>129</v>
@@ -10579,7 +10576,7 @@
         <v>111</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D385" s="2">
         <v>449</v>
@@ -10605,7 +10602,7 @@
         <v>111</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D386" s="2">
         <v>224</v>
@@ -10631,7 +10628,7 @@
         <v>111</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D387" s="2">
         <v>99</v>
@@ -10657,7 +10654,7 @@
         <v>111</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D388" s="2">
         <v>84</v>
@@ -10683,7 +10680,7 @@
         <v>111</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D389" s="2">
         <v>206</v>
@@ -10709,7 +10706,7 @@
         <v>111</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D390" s="2">
         <v>356</v>
@@ -10735,7 +10732,7 @@
         <v>111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D391" s="2">
         <v>370</v>
@@ -10761,7 +10758,7 @@
         <v>111</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D392" s="2">
         <v>211</v>
@@ -10787,7 +10784,7 @@
         <v>111</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D393" s="2">
         <v>198</v>
@@ -10813,7 +10810,7 @@
         <v>111</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D394" s="2">
         <v>246</v>
@@ -10839,7 +10836,7 @@
         <v>111</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D395" s="2">
         <v>119</v>
@@ -10865,7 +10862,7 @@
         <v>111</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D396" s="2">
         <v>228</v>
@@ -10891,7 +10888,7 @@
         <v>111</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D397" s="2">
         <v>166</v>
@@ -10917,7 +10914,7 @@
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D398" s="2">
         <v>421</v>
@@ -10943,7 +10940,7 @@
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D399" s="2">
         <v>99</v>
@@ -10969,7 +10966,7 @@
         <v>112</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D400" s="2">
         <v>474</v>
@@ -10995,7 +10992,7 @@
         <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D401" s="2">
         <v>398</v>
@@ -11021,7 +11018,7 @@
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D402" s="2">
         <v>147</v>
@@ -11047,7 +11044,7 @@
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D403" s="2">
         <v>443</v>
@@ -11073,7 +11070,7 @@
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D404" s="2">
         <v>259</v>
@@ -11099,7 +11096,7 @@
         <v>112</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D405" s="2">
         <v>264</v>
@@ -11125,7 +11122,7 @@
         <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D406" s="2">
         <v>450</v>
@@ -11151,7 +11148,7 @@
         <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D407" s="2">
         <v>490</v>
@@ -11177,7 +11174,7 @@
         <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D408" s="2">
         <v>457</v>
@@ -11203,7 +11200,7 @@
         <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D409" s="2">
         <v>481</v>
@@ -11229,7 +11226,7 @@
         <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D410" s="2">
         <v>452</v>
@@ -11255,7 +11252,7 @@
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D411" s="2">
         <v>194</v>
@@ -11281,7 +11278,7 @@
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D412" s="2">
         <v>399</v>
@@ -11307,7 +11304,7 @@
         <v>112</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D413" s="2">
         <v>264</v>
@@ -11333,7 +11330,7 @@
         <v>112</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D414" s="2">
         <v>109</v>
@@ -11359,7 +11356,7 @@
         <v>112</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D415" s="2">
         <v>437</v>
@@ -11385,7 +11382,7 @@
         <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D416" s="2">
         <v>447</v>
@@ -11411,7 +11408,7 @@
         <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D417" s="2">
         <v>421</v>
@@ -11437,7 +11434,7 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D418" s="2">
         <v>80</v>
@@ -11463,7 +11460,7 @@
         <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D419" s="2">
         <v>493</v>
@@ -11489,7 +11486,7 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D420" s="2">
         <v>105</v>
@@ -11515,7 +11512,7 @@
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D421" s="2">
         <v>432</v>
@@ -11541,7 +11538,7 @@
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D422" s="2">
         <v>332</v>
@@ -11567,7 +11564,7 @@
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D423" s="2">
         <v>238</v>
@@ -11593,7 +11590,7 @@
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D424" s="2">
         <v>300</v>
@@ -11619,7 +11616,7 @@
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D425" s="2">
         <v>249</v>
@@ -11645,7 +11642,7 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D426" s="2">
         <v>336</v>
@@ -11671,7 +11668,7 @@
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D427" s="2">
         <v>114</v>
@@ -11697,7 +11694,7 @@
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D428" s="2">
         <v>175</v>
@@ -11723,7 +11720,7 @@
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D429" s="2">
         <v>473</v>
@@ -11749,7 +11746,7 @@
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D430" s="2">
         <v>202</v>
@@ -11775,7 +11772,7 @@
         <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D431" s="2">
         <v>215</v>
@@ -11801,7 +11798,7 @@
         <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D432" s="2">
         <v>252</v>
@@ -11827,7 +11824,7 @@
         <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D433" s="2">
         <v>223</v>
@@ -11853,7 +11850,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>
@@ -11879,7 +11876,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11905,7 +11902,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11931,7 +11928,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>
@@ -11957,7 +11954,7 @@
         <v>113</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D438" s="2">
         <v>219</v>
@@ -11983,7 +11980,7 @@
         <v>113</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D439" s="2">
         <v>99</v>
@@ -12009,7 +12006,7 @@
         <v>113</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D440" s="2">
         <v>177</v>
@@ -12035,7 +12032,7 @@
         <v>113</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D441" s="2">
         <v>380</v>
@@ -12061,7 +12058,7 @@
         <v>113</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D442" s="2">
         <v>464</v>
@@ -12087,7 +12084,7 @@
         <v>113</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D443" s="2">
         <v>460</v>
@@ -12113,7 +12110,7 @@
         <v>113</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D444" s="2">
         <v>299</v>
@@ -12139,7 +12136,7 @@
         <v>113</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D445" s="2">
         <v>243</v>
@@ -12165,7 +12162,7 @@
         <v>113</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D446" s="2">
         <v>154</v>
@@ -12191,7 +12188,7 @@
         <v>113</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D447" s="2">
         <v>239</v>
@@ -12217,7 +12214,7 @@
         <v>113</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D448" s="2">
         <v>410</v>
@@ -12243,7 +12240,7 @@
         <v>113</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D449" s="2">
         <v>273</v>
@@ -12269,7 +12266,7 @@
         <v>113</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D450" s="2">
         <v>90</v>
@@ -12295,7 +12292,7 @@
         <v>113</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D451" s="2">
         <v>407</v>
@@ -12321,7 +12318,7 @@
         <v>113</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D452" s="2">
         <v>301</v>
@@ -12347,7 +12344,7 @@
         <v>113</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D453" s="2">
         <v>181</v>
@@ -12373,7 +12370,7 @@
         <v>113</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D454" s="2">
         <v>186</v>
@@ -12399,7 +12396,7 @@
         <v>113</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D455" s="2">
         <v>424</v>
@@ -12425,7 +12422,7 @@
         <v>113</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D456" s="2">
         <v>268</v>
@@ -12451,7 +12448,7 @@
         <v>113</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D457" s="2">
         <v>277</v>
@@ -12477,7 +12474,7 @@
         <v>113</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D458" s="2">
         <v>89</v>
@@ -12503,7 +12500,7 @@
         <v>113</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D459" s="2">
         <v>219</v>
@@ -12529,7 +12526,7 @@
         <v>113</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D460" s="2">
         <v>273</v>
@@ -12555,7 +12552,7 @@
         <v>113</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D461" s="2">
         <v>254</v>
@@ -12581,7 +12578,7 @@
         <v>113</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D462" s="2">
         <v>243</v>
@@ -12607,7 +12604,7 @@
         <v>113</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D463" s="2">
         <v>349</v>
@@ -12633,7 +12630,7 @@
         <v>113</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D464" s="2">
         <v>245</v>
@@ -12659,7 +12656,7 @@
         <v>113</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D465" s="2">
         <v>174</v>
@@ -12685,7 +12682,7 @@
         <v>113</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D466" s="2">
         <v>80</v>
@@ -12711,7 +12708,7 @@
         <v>113</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D467" s="2">
         <v>210</v>
@@ -12737,7 +12734,7 @@
         <v>113</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D468" s="2">
         <v>281</v>
@@ -12763,7 +12760,7 @@
         <v>113</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D469" s="2">
         <v>80</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="60">
   <si>
     <t>Month</t>
   </si>
@@ -201,7 +201,7 @@
     <t>Pain</t>
   </si>
   <si>
-    <t xml:space="preserve"> Lait</t>
+    <t>Riz</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1372,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D31" s="2">
         <v>265</v>
@@ -2490,7 +2490,7 @@
         <v>103</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D74" s="2">
         <v>380</v>
@@ -2516,7 +2516,7 @@
         <v>103</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D75" s="2">
         <v>383</v>
@@ -2542,7 +2542,7 @@
         <v>103</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D76" s="2">
         <v>168</v>
@@ -2568,7 +2568,7 @@
         <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D77" s="2">
         <v>73</v>
@@ -2594,7 +2594,7 @@
         <v>103</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D78" s="2">
         <v>282</v>
@@ -2620,7 +2620,7 @@
         <v>103</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D79" s="2">
         <v>362</v>
@@ -2646,7 +2646,7 @@
         <v>103</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D80" s="2">
         <v>386</v>
@@ -2672,7 +2672,7 @@
         <v>103</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D81" s="2">
         <v>323</v>
@@ -2698,7 +2698,7 @@
         <v>103</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D82" s="2">
         <v>51</v>
@@ -2724,7 +2724,7 @@
         <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D83" s="2">
         <v>452</v>
@@ -2750,7 +2750,7 @@
         <v>103</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D84" s="2">
         <v>55</v>
@@ -2776,7 +2776,7 @@
         <v>103</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D85" s="2">
         <v>341</v>
@@ -2802,7 +2802,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D86" s="2">
         <v>155</v>
@@ -2828,7 +2828,7 @@
         <v>103</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D87" s="2">
         <v>496</v>
@@ -2854,7 +2854,7 @@
         <v>103</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D88" s="2">
         <v>462</v>
@@ -2880,7 +2880,7 @@
         <v>103</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D89" s="2">
         <v>394</v>
@@ -2906,7 +2906,7 @@
         <v>103</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D90" s="2">
         <v>207</v>
@@ -2932,7 +2932,7 @@
         <v>103</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D91" s="2">
         <v>336</v>
@@ -2958,7 +2958,7 @@
         <v>103</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D92" s="2">
         <v>481</v>
@@ -2984,7 +2984,7 @@
         <v>103</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D93" s="2">
         <v>180</v>
@@ -3010,7 +3010,7 @@
         <v>103</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D94" s="2">
         <v>337</v>
@@ -3036,7 +3036,7 @@
         <v>103</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D95" s="2">
         <v>88</v>
@@ -3062,7 +3062,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D96" s="2">
         <v>221</v>
@@ -3088,7 +3088,7 @@
         <v>103</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D97" s="2">
         <v>442</v>
@@ -3114,7 +3114,7 @@
         <v>103</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D98" s="2">
         <v>216</v>
@@ -3140,7 +3140,7 @@
         <v>103</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D99" s="2">
         <v>237</v>
@@ -3166,7 +3166,7 @@
         <v>103</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D100" s="2">
         <v>336</v>
@@ -3192,7 +3192,7 @@
         <v>103</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D101" s="2">
         <v>281</v>
@@ -3218,7 +3218,7 @@
         <v>103</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D102" s="2">
         <v>216</v>
@@ -3244,7 +3244,7 @@
         <v>103</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D103" s="2">
         <v>214</v>
@@ -3270,7 +3270,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D104" s="2">
         <v>323</v>
@@ -3296,7 +3296,7 @@
         <v>103</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D105" s="2">
         <v>305</v>
@@ -3322,7 +3322,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D106" s="2">
         <v>258</v>
@@ -3348,7 +3348,7 @@
         <v>103</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D107" s="2">
         <v>235</v>
@@ -3374,7 +3374,7 @@
         <v>103</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D108" s="2">
         <v>250</v>
@@ -3400,7 +3400,7 @@
         <v>103</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2">
         <v>225</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2176" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="59">
   <si>
     <t>Month</t>
   </si>
@@ -156,9 +156,6 @@
     <t>2023-12</t>
   </si>
   <si>
-    <t>Oats</t>
-  </si>
-  <si>
     <t>Pasta</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
   </si>
   <si>
     <t>Sugar</t>
-  </si>
-  <si>
-    <t>Tomato Sauce</t>
   </si>
   <si>
     <t>Juice</t>
@@ -202,6 +196,9 @@
   </si>
   <si>
     <t>Riz</t>
+  </si>
+  <si>
+    <t>Couscous</t>
   </si>
 </sst>
 </file>
@@ -618,7 +615,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2">
         <v>373</v>
@@ -644,7 +641,7 @@
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2">
         <v>423</v>
@@ -670,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2">
         <v>147</v>
@@ -696,7 +693,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2">
         <v>431</v>
@@ -722,7 +719,7 @@
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2">
         <v>305</v>
@@ -748,7 +745,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2">
         <v>167</v>
@@ -774,7 +771,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D8" s="2">
         <v>101</v>
@@ -800,7 +797,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9" s="2">
         <v>73</v>
@@ -826,7 +823,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D10" s="2">
         <v>445</v>
@@ -852,7 +849,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D11" s="2">
         <v>180</v>
@@ -878,7 +875,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="2">
         <v>221</v>
@@ -904,7 +901,7 @@
         <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" s="2">
         <v>153</v>
@@ -930,7 +927,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" s="2">
         <v>283</v>
@@ -956,7 +953,7 @@
         <v>101</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2">
         <v>220</v>
@@ -982,7 +979,7 @@
         <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" s="2">
         <v>338</v>
@@ -1008,7 +1005,7 @@
         <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2">
         <v>209</v>
@@ -1034,7 +1031,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" s="2">
         <v>186</v>
@@ -1060,7 +1057,7 @@
         <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D19" s="2">
         <v>383</v>
@@ -1086,7 +1083,7 @@
         <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D20" s="2">
         <v>253</v>
@@ -1112,7 +1109,7 @@
         <v>101</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2">
         <v>159</v>
@@ -1138,7 +1135,7 @@
         <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D22" s="2">
         <v>212</v>
@@ -1164,7 +1161,7 @@
         <v>101</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2">
         <v>377</v>
@@ -1190,7 +1187,7 @@
         <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D24" s="2">
         <v>126</v>
@@ -1216,7 +1213,7 @@
         <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D25" s="2">
         <v>283</v>
@@ -1242,7 +1239,7 @@
         <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D26" s="2">
         <v>235</v>
@@ -1268,7 +1265,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D27" s="2">
         <v>170</v>
@@ -1294,7 +1291,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D28" s="2">
         <v>321</v>
@@ -1320,7 +1317,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D29" s="2">
         <v>127</v>
@@ -1346,7 +1343,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D30" s="2">
         <v>162</v>
@@ -1372,7 +1369,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D31" s="2">
         <v>265</v>
@@ -1398,7 +1395,7 @@
         <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D32" s="2">
         <v>193</v>
@@ -1424,7 +1421,7 @@
         <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D33" s="2">
         <v>211</v>
@@ -1450,7 +1447,7 @@
         <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D34" s="2">
         <v>328</v>
@@ -1476,7 +1473,7 @@
         <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D35" s="2">
         <v>127</v>
@@ -1502,7 +1499,7 @@
         <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D36" s="2">
         <v>176</v>
@@ -1528,7 +1525,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D37" s="2">
         <v>278</v>
@@ -1554,7 +1551,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1580,7 +1577,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1606,7 +1603,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1632,7 +1629,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1658,7 +1655,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1684,7 +1681,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1710,7 +1707,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1736,7 +1733,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1762,7 +1759,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1788,7 +1785,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1814,7 +1811,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1840,7 +1837,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1866,7 +1863,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1892,7 +1889,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1918,7 +1915,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1944,7 +1941,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1970,7 +1967,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -1996,7 +1993,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2022,7 +2019,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2048,7 +2045,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2074,7 +2071,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2100,7 +2097,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2126,7 +2123,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2152,7 +2149,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2178,7 +2175,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2204,7 +2201,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2230,7 +2227,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2256,7 +2253,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2282,7 +2279,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2308,7 +2305,7 @@
         <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D67" s="2">
         <v>259</v>
@@ -2334,7 +2331,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>
@@ -2360,7 +2357,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D69" s="2">
         <v>173</v>
@@ -2386,7 +2383,7 @@
         <v>102</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D70" s="2">
         <v>186</v>
@@ -2412,7 +2409,7 @@
         <v>102</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D71" s="2">
         <v>274</v>
@@ -2438,7 +2435,7 @@
         <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D72" s="2">
         <v>238</v>
@@ -2464,7 +2461,7 @@
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D73" s="2">
         <v>109</v>
@@ -2490,7 +2487,7 @@
         <v>103</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D74" s="2">
         <v>380</v>
@@ -2516,7 +2513,7 @@
         <v>103</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D75" s="2">
         <v>383</v>
@@ -2542,7 +2539,7 @@
         <v>103</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D76" s="2">
         <v>168</v>
@@ -2568,7 +2565,7 @@
         <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D77" s="2">
         <v>73</v>
@@ -2594,7 +2591,7 @@
         <v>103</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D78" s="2">
         <v>282</v>
@@ -2620,7 +2617,7 @@
         <v>103</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D79" s="2">
         <v>362</v>
@@ -2646,7 +2643,7 @@
         <v>103</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D80" s="2">
         <v>386</v>
@@ -2672,7 +2669,7 @@
         <v>103</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D81" s="2">
         <v>323</v>
@@ -2698,7 +2695,7 @@
         <v>103</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D82" s="2">
         <v>51</v>
@@ -2724,7 +2721,7 @@
         <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D83" s="2">
         <v>452</v>
@@ -2750,7 +2747,7 @@
         <v>103</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D84" s="2">
         <v>55</v>
@@ -2776,7 +2773,7 @@
         <v>103</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D85" s="2">
         <v>341</v>
@@ -2802,7 +2799,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D86" s="2">
         <v>155</v>
@@ -2828,7 +2825,7 @@
         <v>103</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D87" s="2">
         <v>496</v>
@@ -2854,7 +2851,7 @@
         <v>103</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D88" s="2">
         <v>462</v>
@@ -2880,7 +2877,7 @@
         <v>103</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D89" s="2">
         <v>394</v>
@@ -2906,7 +2903,7 @@
         <v>103</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D90" s="2">
         <v>207</v>
@@ -2932,7 +2929,7 @@
         <v>103</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D91" s="2">
         <v>336</v>
@@ -2958,7 +2955,7 @@
         <v>103</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D92" s="2">
         <v>481</v>
@@ -2984,7 +2981,7 @@
         <v>103</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D93" s="2">
         <v>180</v>
@@ -3010,7 +3007,7 @@
         <v>103</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D94" s="2">
         <v>337</v>
@@ -3036,7 +3033,7 @@
         <v>103</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D95" s="2">
         <v>88</v>
@@ -3062,7 +3059,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D96" s="2">
         <v>221</v>
@@ -3088,7 +3085,7 @@
         <v>103</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D97" s="2">
         <v>442</v>
@@ -3114,7 +3111,7 @@
         <v>103</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D98" s="2">
         <v>216</v>
@@ -3140,7 +3137,7 @@
         <v>103</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D99" s="2">
         <v>237</v>
@@ -3166,7 +3163,7 @@
         <v>103</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D100" s="2">
         <v>336</v>
@@ -3192,7 +3189,7 @@
         <v>103</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D101" s="2">
         <v>281</v>
@@ -3218,7 +3215,7 @@
         <v>103</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D102" s="2">
         <v>216</v>
@@ -3244,7 +3241,7 @@
         <v>103</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D103" s="2">
         <v>214</v>
@@ -3270,7 +3267,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D104" s="2">
         <v>323</v>
@@ -3296,7 +3293,7 @@
         <v>103</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D105" s="2">
         <v>305</v>
@@ -3322,7 +3319,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D106" s="2">
         <v>258</v>
@@ -3348,7 +3345,7 @@
         <v>103</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D107" s="2">
         <v>235</v>
@@ -3374,7 +3371,7 @@
         <v>103</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D108" s="2">
         <v>250</v>
@@ -3400,7 +3397,7 @@
         <v>103</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D109" s="2">
         <v>225</v>
@@ -3426,7 +3423,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3452,7 +3449,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3478,7 +3475,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3504,7 +3501,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3530,7 +3527,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3556,7 +3553,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3582,7 +3579,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3608,7 +3605,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3634,7 +3631,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3660,7 +3657,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3686,7 +3683,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>
@@ -3712,7 +3709,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3738,7 +3735,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3764,7 +3761,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3790,7 +3787,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3816,7 +3813,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3842,7 +3839,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -3868,7 +3865,7 @@
         <v>104</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D127" s="2">
         <v>141</v>
@@ -3894,7 +3891,7 @@
         <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D128" s="2">
         <v>303</v>
@@ -3920,7 +3917,7 @@
         <v>104</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D129" s="2">
         <v>281</v>
@@ -3946,7 +3943,7 @@
         <v>104</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D130" s="2">
         <v>453</v>
@@ -3972,7 +3969,7 @@
         <v>104</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D131" s="2">
         <v>310</v>
@@ -3998,7 +3995,7 @@
         <v>104</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D132" s="2">
         <v>243</v>
@@ -4024,7 +4021,7 @@
         <v>104</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D133" s="2">
         <v>248</v>
@@ -4050,7 +4047,7 @@
         <v>104</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D134" s="2">
         <v>253</v>
@@ -4076,7 +4073,7 @@
         <v>104</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D135" s="2">
         <v>197</v>
@@ -4102,7 +4099,7 @@
         <v>104</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D136" s="2">
         <v>184</v>
@@ -4128,7 +4125,7 @@
         <v>104</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D137" s="2">
         <v>119</v>
@@ -4154,7 +4151,7 @@
         <v>104</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D138" s="2">
         <v>192</v>
@@ -4180,7 +4177,7 @@
         <v>104</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D139" s="2">
         <v>237</v>
@@ -4206,7 +4203,7 @@
         <v>104</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D140" s="2">
         <v>71</v>
@@ -4232,7 +4229,7 @@
         <v>104</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D141" s="2">
         <v>170</v>
@@ -4258,7 +4255,7 @@
         <v>104</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D142" s="2">
         <v>201</v>
@@ -4284,7 +4281,7 @@
         <v>104</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D143" s="2">
         <v>226</v>
@@ -4310,7 +4307,7 @@
         <v>104</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D144" s="2">
         <v>251</v>
@@ -4336,7 +4333,7 @@
         <v>104</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D145" s="2">
         <v>281</v>
@@ -4362,7 +4359,7 @@
         <v>105</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D146" s="2">
         <v>494</v>
@@ -4388,7 +4385,7 @@
         <v>105</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D147" s="2">
         <v>383</v>
@@ -4414,7 +4411,7 @@
         <v>105</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D148" s="2">
         <v>243</v>
@@ -4440,7 +4437,7 @@
         <v>105</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D149" s="2">
         <v>384</v>
@@ -4466,7 +4463,7 @@
         <v>105</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D150" s="2">
         <v>316</v>
@@ -4492,7 +4489,7 @@
         <v>105</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D151" s="2">
         <v>362</v>
@@ -4518,7 +4515,7 @@
         <v>105</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D152" s="2">
         <v>479</v>
@@ -4544,7 +4541,7 @@
         <v>105</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D153" s="2">
         <v>317</v>
@@ -4570,7 +4567,7 @@
         <v>105</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D154" s="2">
         <v>240</v>
@@ -4596,7 +4593,7 @@
         <v>105</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D155" s="2">
         <v>290</v>
@@ -4622,7 +4619,7 @@
         <v>105</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D156" s="2">
         <v>477</v>
@@ -4648,7 +4645,7 @@
         <v>105</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D157" s="2">
         <v>362</v>
@@ -4674,7 +4671,7 @@
         <v>105</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D158" s="2">
         <v>54</v>
@@ -4700,7 +4697,7 @@
         <v>105</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D159" s="2">
         <v>281</v>
@@ -4726,7 +4723,7 @@
         <v>105</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D160" s="2">
         <v>381</v>
@@ -4752,7 +4749,7 @@
         <v>105</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D161" s="2">
         <v>351</v>
@@ -4778,7 +4775,7 @@
         <v>105</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D162" s="2">
         <v>309</v>
@@ -4804,7 +4801,7 @@
         <v>105</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D163" s="2">
         <v>383</v>
@@ -4830,7 +4827,7 @@
         <v>105</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D164" s="2">
         <v>407</v>
@@ -4856,7 +4853,7 @@
         <v>105</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D165" s="2">
         <v>171</v>
@@ -4882,7 +4879,7 @@
         <v>105</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D166" s="2">
         <v>274</v>
@@ -4908,7 +4905,7 @@
         <v>105</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D167" s="2">
         <v>295</v>
@@ -4934,7 +4931,7 @@
         <v>105</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D168" s="2">
         <v>418</v>
@@ -4960,7 +4957,7 @@
         <v>105</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D169" s="2">
         <v>84</v>
@@ -4986,7 +4983,7 @@
         <v>105</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D170" s="2">
         <v>247</v>
@@ -5012,7 +5009,7 @@
         <v>105</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D171" s="2">
         <v>179</v>
@@ -5038,7 +5035,7 @@
         <v>105</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D172" s="2">
         <v>322</v>
@@ -5064,7 +5061,7 @@
         <v>105</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D173" s="2">
         <v>271</v>
@@ -5090,7 +5087,7 @@
         <v>105</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D174" s="2">
         <v>281</v>
@@ -5116,7 +5113,7 @@
         <v>105</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D175" s="2">
         <v>174</v>
@@ -5142,7 +5139,7 @@
         <v>105</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D176" s="2">
         <v>305</v>
@@ -5168,7 +5165,7 @@
         <v>105</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D177" s="2">
         <v>254</v>
@@ -5194,7 +5191,7 @@
         <v>105</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D178" s="2">
         <v>312</v>
@@ -5220,7 +5217,7 @@
         <v>105</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D179" s="2">
         <v>115</v>
@@ -5246,7 +5243,7 @@
         <v>105</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D180" s="2">
         <v>161</v>
@@ -5272,7 +5269,7 @@
         <v>105</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D181" s="2">
         <v>240</v>
@@ -5298,7 +5295,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -5324,7 +5321,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5350,7 +5347,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5376,7 +5373,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5402,7 +5399,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -5428,7 +5425,7 @@
         <v>106</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D187" s="2">
         <v>342</v>
@@ -5454,7 +5451,7 @@
         <v>106</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D188" s="2">
         <v>285</v>
@@ -5480,7 +5477,7 @@
         <v>106</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D189" s="2">
         <v>453</v>
@@ -5506,7 +5503,7 @@
         <v>106</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D190" s="2">
         <v>69</v>
@@ -5532,7 +5529,7 @@
         <v>106</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D191" s="2">
         <v>154</v>
@@ -5558,7 +5555,7 @@
         <v>106</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D192" s="2">
         <v>246</v>
@@ -5584,7 +5581,7 @@
         <v>106</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D193" s="2">
         <v>446</v>
@@ -5610,7 +5607,7 @@
         <v>106</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D194" s="2">
         <v>467</v>
@@ -5636,7 +5633,7 @@
         <v>106</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D195" s="2">
         <v>374</v>
@@ -5662,7 +5659,7 @@
         <v>106</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D196" s="2">
         <v>266</v>
@@ -5688,7 +5685,7 @@
         <v>106</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D197" s="2">
         <v>281</v>
@@ -5714,7 +5711,7 @@
         <v>106</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D198" s="2">
         <v>277</v>
@@ -5740,7 +5737,7 @@
         <v>106</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D199" s="2">
         <v>153</v>
@@ -5766,7 +5763,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D200" s="2">
         <v>176</v>
@@ -5792,7 +5789,7 @@
         <v>106</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D201" s="2">
         <v>281</v>
@@ -5818,7 +5815,7 @@
         <v>106</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D202" s="2">
         <v>52</v>
@@ -5844,7 +5841,7 @@
         <v>106</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D203" s="2">
         <v>94</v>
@@ -5870,7 +5867,7 @@
         <v>106</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D204" s="2">
         <v>181</v>
@@ -5896,7 +5893,7 @@
         <v>106</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D205" s="2">
         <v>336</v>
@@ -5922,7 +5919,7 @@
         <v>106</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D206" s="2">
         <v>349</v>
@@ -5948,7 +5945,7 @@
         <v>106</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D207" s="2">
         <v>127</v>
@@ -5974,7 +5971,7 @@
         <v>106</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D208" s="2">
         <v>376</v>
@@ -6000,7 +5997,7 @@
         <v>106</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D209" s="2">
         <v>98</v>
@@ -6026,7 +6023,7 @@
         <v>106</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D210" s="2">
         <v>152</v>
@@ -6052,7 +6049,7 @@
         <v>106</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D211" s="2">
         <v>235</v>
@@ -6078,7 +6075,7 @@
         <v>106</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D212" s="2">
         <v>105</v>
@@ -6104,7 +6101,7 @@
         <v>106</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D213" s="2">
         <v>150</v>
@@ -6130,7 +6127,7 @@
         <v>106</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D214" s="2">
         <v>215</v>
@@ -6156,7 +6153,7 @@
         <v>106</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D215" s="2">
         <v>216</v>
@@ -6182,7 +6179,7 @@
         <v>106</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D216" s="2">
         <v>214</v>
@@ -6208,7 +6205,7 @@
         <v>106</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D217" s="2">
         <v>194</v>
@@ -6234,7 +6231,7 @@
         <v>107</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D218" s="2">
         <v>184</v>
@@ -6260,7 +6257,7 @@
         <v>107</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D219" s="2">
         <v>379</v>
@@ -6286,7 +6283,7 @@
         <v>107</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D220" s="2">
         <v>424</v>
@@ -6312,7 +6309,7 @@
         <v>107</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D221" s="2">
         <v>93</v>
@@ -6338,7 +6335,7 @@
         <v>107</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D222" s="2">
         <v>219</v>
@@ -6364,7 +6361,7 @@
         <v>107</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D223" s="2">
         <v>165</v>
@@ -6390,7 +6387,7 @@
         <v>107</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D224" s="2">
         <v>462</v>
@@ -6416,7 +6413,7 @@
         <v>107</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D225" s="2">
         <v>332</v>
@@ -6442,7 +6439,7 @@
         <v>107</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D226" s="2">
         <v>162</v>
@@ -6468,7 +6465,7 @@
         <v>107</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D227" s="2">
         <v>305</v>
@@ -6494,7 +6491,7 @@
         <v>107</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D228" s="2">
         <v>446</v>
@@ -6520,7 +6517,7 @@
         <v>107</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D229" s="2">
         <v>196</v>
@@ -6546,7 +6543,7 @@
         <v>107</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D230" s="2">
         <v>443</v>
@@ -6572,7 +6569,7 @@
         <v>107</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D231" s="2">
         <v>158</v>
@@ -6598,7 +6595,7 @@
         <v>107</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D232" s="2">
         <v>191</v>
@@ -6624,7 +6621,7 @@
         <v>107</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D233" s="2">
         <v>321</v>
@@ -6650,7 +6647,7 @@
         <v>107</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D234" s="2">
         <v>316</v>
@@ -6676,7 +6673,7 @@
         <v>107</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D235" s="2">
         <v>71</v>
@@ -6702,7 +6699,7 @@
         <v>107</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D236" s="2">
         <v>171</v>
@@ -6728,7 +6725,7 @@
         <v>107</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D237" s="2">
         <v>450</v>
@@ -6754,7 +6751,7 @@
         <v>107</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D238" s="2">
         <v>354</v>
@@ -6780,7 +6777,7 @@
         <v>107</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D239" s="2">
         <v>475</v>
@@ -6806,7 +6803,7 @@
         <v>107</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D240" s="2">
         <v>130</v>
@@ -6832,7 +6829,7 @@
         <v>107</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D241" s="2">
         <v>140</v>
@@ -6858,7 +6855,7 @@
         <v>107</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D242" s="2">
         <v>253</v>
@@ -6884,7 +6881,7 @@
         <v>107</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D243" s="2">
         <v>246</v>
@@ -6910,7 +6907,7 @@
         <v>107</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D244" s="2">
         <v>297</v>
@@ -6936,7 +6933,7 @@
         <v>107</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D245" s="2">
         <v>201</v>
@@ -6962,7 +6959,7 @@
         <v>107</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D246" s="2">
         <v>339</v>
@@ -6988,7 +6985,7 @@
         <v>107</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D247" s="2">
         <v>132</v>
@@ -7014,7 +7011,7 @@
         <v>107</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D248" s="2">
         <v>239</v>
@@ -7040,7 +7037,7 @@
         <v>107</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D249" s="2">
         <v>169</v>
@@ -7066,7 +7063,7 @@
         <v>107</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D250" s="2">
         <v>217</v>
@@ -7092,7 +7089,7 @@
         <v>107</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D251" s="2">
         <v>340</v>
@@ -7118,7 +7115,7 @@
         <v>107</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D252" s="2">
         <v>192</v>
@@ -7144,7 +7141,7 @@
         <v>107</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D253" s="2">
         <v>243</v>
@@ -7170,7 +7167,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -7196,7 +7193,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7222,7 +7219,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -7248,7 +7245,7 @@
         <v>108</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D257" s="2">
         <v>451</v>
@@ -7274,7 +7271,7 @@
         <v>108</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D258" s="2">
         <v>183</v>
@@ -7300,7 +7297,7 @@
         <v>108</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D259" s="2">
         <v>311</v>
@@ -7326,7 +7323,7 @@
         <v>108</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D260" s="2">
         <v>365</v>
@@ -7352,7 +7349,7 @@
         <v>108</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D261" s="2">
         <v>411</v>
@@ -7378,7 +7375,7 @@
         <v>108</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D262" s="2">
         <v>130</v>
@@ -7404,7 +7401,7 @@
         <v>108</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D263" s="2">
         <v>69</v>
@@ -7430,7 +7427,7 @@
         <v>108</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D264" s="2">
         <v>391</v>
@@ -7456,7 +7453,7 @@
         <v>108</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D265" s="2">
         <v>475</v>
@@ -7482,7 +7479,7 @@
         <v>108</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D266" s="2">
         <v>386</v>
@@ -7508,7 +7505,7 @@
         <v>108</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D267" s="2">
         <v>345</v>
@@ -7534,7 +7531,7 @@
         <v>108</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D268" s="2">
         <v>57</v>
@@ -7560,7 +7557,7 @@
         <v>108</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D269" s="2">
         <v>489</v>
@@ -7586,7 +7583,7 @@
         <v>108</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D270" s="2">
         <v>88</v>
@@ -7612,7 +7609,7 @@
         <v>108</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D271" s="2">
         <v>417</v>
@@ -7638,7 +7635,7 @@
         <v>108</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D272" s="2">
         <v>437</v>
@@ -7664,7 +7661,7 @@
         <v>108</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D273" s="2">
         <v>249</v>
@@ -7690,7 +7687,7 @@
         <v>108</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D274" s="2">
         <v>86</v>
@@ -7716,7 +7713,7 @@
         <v>108</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D275" s="2">
         <v>191</v>
@@ -7742,7 +7739,7 @@
         <v>108</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D276" s="2">
         <v>298</v>
@@ -7768,7 +7765,7 @@
         <v>108</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D277" s="2">
         <v>235</v>
@@ -7794,7 +7791,7 @@
         <v>108</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D278" s="2">
         <v>201</v>
@@ -7820,7 +7817,7 @@
         <v>108</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D279" s="2">
         <v>158</v>
@@ -7846,7 +7843,7 @@
         <v>108</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D280" s="2">
         <v>135</v>
@@ -7872,7 +7869,7 @@
         <v>108</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D281" s="2">
         <v>333</v>
@@ -7898,7 +7895,7 @@
         <v>108</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D282" s="2">
         <v>352</v>
@@ -7924,7 +7921,7 @@
         <v>108</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D283" s="2">
         <v>66</v>
@@ -7950,7 +7947,7 @@
         <v>108</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D284" s="2">
         <v>116</v>
@@ -7976,7 +7973,7 @@
         <v>108</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D285" s="2">
         <v>214</v>
@@ -8002,7 +7999,7 @@
         <v>108</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D286" s="2">
         <v>210</v>
@@ -8028,7 +8025,7 @@
         <v>108</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D287" s="2">
         <v>295</v>
@@ -8054,7 +8051,7 @@
         <v>108</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D288" s="2">
         <v>112</v>
@@ -8080,7 +8077,7 @@
         <v>108</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D289" s="2">
         <v>222</v>
@@ -8106,7 +8103,7 @@
         <v>109</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D290" s="2">
         <v>212</v>
@@ -8132,7 +8129,7 @@
         <v>109</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D291" s="2">
         <v>457</v>
@@ -8158,7 +8155,7 @@
         <v>109</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D292" s="2">
         <v>203</v>
@@ -8184,7 +8181,7 @@
         <v>109</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D293" s="2">
         <v>247</v>
@@ -8210,7 +8207,7 @@
         <v>109</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D294" s="2">
         <v>113</v>
@@ -8236,7 +8233,7 @@
         <v>109</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D295" s="2">
         <v>107</v>
@@ -8262,7 +8259,7 @@
         <v>109</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D296" s="2">
         <v>338</v>
@@ -8288,7 +8285,7 @@
         <v>109</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D297" s="2">
         <v>259</v>
@@ -8314,7 +8311,7 @@
         <v>109</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D298" s="2">
         <v>430</v>
@@ -8340,7 +8337,7 @@
         <v>109</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D299" s="2">
         <v>329</v>
@@ -8366,7 +8363,7 @@
         <v>109</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D300" s="2">
         <v>369</v>
@@ -8392,7 +8389,7 @@
         <v>109</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D301" s="2">
         <v>262</v>
@@ -8418,7 +8415,7 @@
         <v>109</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D302" s="2">
         <v>253</v>
@@ -8444,7 +8441,7 @@
         <v>109</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D303" s="2">
         <v>257</v>
@@ -8470,7 +8467,7 @@
         <v>109</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D304" s="2">
         <v>446</v>
@@ -8496,7 +8493,7 @@
         <v>109</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D305" s="2">
         <v>270</v>
@@ -8522,7 +8519,7 @@
         <v>109</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D306" s="2">
         <v>486</v>
@@ -8548,7 +8545,7 @@
         <v>109</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D307" s="2">
         <v>484</v>
@@ -8574,7 +8571,7 @@
         <v>109</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D308" s="2">
         <v>277</v>
@@ -8600,7 +8597,7 @@
         <v>109</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D309" s="2">
         <v>298</v>
@@ -8626,7 +8623,7 @@
         <v>109</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D310" s="2">
         <v>148</v>
@@ -8652,7 +8649,7 @@
         <v>109</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D311" s="2">
         <v>218</v>
@@ -8678,7 +8675,7 @@
         <v>109</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D312" s="2">
         <v>253</v>
@@ -8704,7 +8701,7 @@
         <v>109</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D313" s="2">
         <v>266</v>
@@ -8730,7 +8727,7 @@
         <v>109</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D314" s="2">
         <v>290</v>
@@ -8756,7 +8753,7 @@
         <v>109</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D315" s="2">
         <v>197</v>
@@ -8782,7 +8779,7 @@
         <v>109</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D316" s="2">
         <v>160</v>
@@ -8808,7 +8805,7 @@
         <v>109</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D317" s="2">
         <v>272</v>
@@ -8834,7 +8831,7 @@
         <v>109</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D318" s="2">
         <v>254</v>
@@ -8860,7 +8857,7 @@
         <v>109</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D319" s="2">
         <v>160</v>
@@ -8886,7 +8883,7 @@
         <v>109</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D320" s="2">
         <v>150</v>
@@ -8912,7 +8909,7 @@
         <v>109</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D321" s="2">
         <v>247</v>
@@ -8938,7 +8935,7 @@
         <v>109</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D322" s="2">
         <v>263</v>
@@ -8964,7 +8961,7 @@
         <v>109</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D323" s="2">
         <v>267</v>
@@ -8990,7 +8987,7 @@
         <v>109</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D324" s="2">
         <v>223</v>
@@ -9016,7 +9013,7 @@
         <v>109</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D325" s="2">
         <v>170</v>
@@ -9042,7 +9039,7 @@
         <v>110</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D326" s="2">
         <v>175</v>
@@ -9068,7 +9065,7 @@
         <v>110</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D327" s="2">
         <v>333</v>
@@ -9094,7 +9091,7 @@
         <v>110</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D328" s="2">
         <v>442</v>
@@ -9120,7 +9117,7 @@
         <v>110</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D329" s="2">
         <v>131</v>
@@ -9146,7 +9143,7 @@
         <v>110</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D330" s="2">
         <v>275</v>
@@ -9172,7 +9169,7 @@
         <v>110</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D331" s="2">
         <v>170</v>
@@ -9198,7 +9195,7 @@
         <v>110</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D332" s="2">
         <v>94</v>
@@ -9224,7 +9221,7 @@
         <v>110</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D333" s="2">
         <v>56</v>
@@ -9250,7 +9247,7 @@
         <v>110</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D334" s="2">
         <v>297</v>
@@ -9276,7 +9273,7 @@
         <v>110</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D335" s="2">
         <v>389</v>
@@ -9302,7 +9299,7 @@
         <v>110</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D336" s="2">
         <v>88</v>
@@ -9328,7 +9325,7 @@
         <v>110</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D337" s="2">
         <v>101</v>
@@ -9354,7 +9351,7 @@
         <v>110</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D338" s="2">
         <v>237</v>
@@ -9380,7 +9377,7 @@
         <v>110</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D339" s="2">
         <v>251</v>
@@ -9406,7 +9403,7 @@
         <v>110</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D340" s="2">
         <v>62</v>
@@ -9432,7 +9429,7 @@
         <v>110</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D341" s="2">
         <v>144</v>
@@ -9458,7 +9455,7 @@
         <v>110</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D342" s="2">
         <v>180</v>
@@ -9484,7 +9481,7 @@
         <v>110</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D343" s="2">
         <v>358</v>
@@ -9510,7 +9507,7 @@
         <v>110</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D344" s="2">
         <v>452</v>
@@ -9536,7 +9533,7 @@
         <v>110</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D345" s="2">
         <v>121</v>
@@ -9562,7 +9559,7 @@
         <v>110</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D346" s="2">
         <v>354</v>
@@ -9588,7 +9585,7 @@
         <v>110</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D347" s="2">
         <v>151</v>
@@ -9614,7 +9611,7 @@
         <v>110</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D348" s="2">
         <v>270</v>
@@ -9640,7 +9637,7 @@
         <v>110</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D349" s="2">
         <v>361</v>
@@ -9666,7 +9663,7 @@
         <v>110</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D350" s="2">
         <v>148</v>
@@ -9692,7 +9689,7 @@
         <v>110</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D351" s="2">
         <v>223</v>
@@ -9718,7 +9715,7 @@
         <v>110</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D352" s="2">
         <v>79</v>
@@ -9744,7 +9741,7 @@
         <v>110</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D353" s="2">
         <v>104</v>
@@ -9770,7 +9767,7 @@
         <v>110</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D354" s="2">
         <v>294</v>
@@ -9796,7 +9793,7 @@
         <v>110</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D355" s="2">
         <v>248</v>
@@ -9822,7 +9819,7 @@
         <v>110</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D356" s="2">
         <v>215</v>
@@ -9848,7 +9845,7 @@
         <v>110</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D357" s="2">
         <v>258</v>
@@ -9874,7 +9871,7 @@
         <v>110</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D358" s="2">
         <v>201</v>
@@ -9900,7 +9897,7 @@
         <v>110</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D359" s="2">
         <v>238</v>
@@ -9926,7 +9923,7 @@
         <v>110</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D360" s="2">
         <v>286</v>
@@ -9952,7 +9949,7 @@
         <v>110</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D361" s="2">
         <v>386</v>
@@ -9978,7 +9975,7 @@
         <v>111</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D362" s="2">
         <v>497</v>
@@ -10004,7 +10001,7 @@
         <v>111</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D363" s="2">
         <v>372</v>
@@ -10030,7 +10027,7 @@
         <v>111</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D364" s="2">
         <v>377</v>
@@ -10056,7 +10053,7 @@
         <v>111</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D365" s="2">
         <v>450</v>
@@ -10082,7 +10079,7 @@
         <v>111</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D366" s="2">
         <v>381</v>
@@ -10108,7 +10105,7 @@
         <v>111</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D367" s="2">
         <v>132</v>
@@ -10134,7 +10131,7 @@
         <v>111</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D368" s="2">
         <v>160</v>
@@ -10160,7 +10157,7 @@
         <v>111</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D369" s="2">
         <v>80</v>
@@ -10186,7 +10183,7 @@
         <v>111</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D370" s="2">
         <v>124</v>
@@ -10212,7 +10209,7 @@
         <v>111</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D371" s="2">
         <v>468</v>
@@ -10238,7 +10235,7 @@
         <v>111</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D372" s="2">
         <v>131</v>
@@ -10264,7 +10261,7 @@
         <v>111</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D373" s="2">
         <v>171</v>
@@ -10290,7 +10287,7 @@
         <v>111</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D374" s="2">
         <v>470</v>
@@ -10316,7 +10313,7 @@
         <v>111</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D375" s="2">
         <v>423</v>
@@ -10342,7 +10339,7 @@
         <v>111</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D376" s="2">
         <v>392</v>
@@ -10368,7 +10365,7 @@
         <v>111</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D377" s="2">
         <v>330</v>
@@ -10394,7 +10391,7 @@
         <v>111</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D378" s="2">
         <v>287</v>
@@ -10420,7 +10417,7 @@
         <v>111</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D379" s="2">
         <v>171</v>
@@ -10446,7 +10443,7 @@
         <v>111</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D380" s="2">
         <v>470</v>
@@ -10472,7 +10469,7 @@
         <v>111</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D381" s="2">
         <v>345</v>
@@ -10498,7 +10495,7 @@
         <v>111</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D382" s="2">
         <v>78</v>
@@ -10524,7 +10521,7 @@
         <v>111</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D383" s="2">
         <v>389</v>
@@ -10550,7 +10547,7 @@
         <v>111</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D384" s="2">
         <v>129</v>
@@ -10576,7 +10573,7 @@
         <v>111</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D385" s="2">
         <v>449</v>
@@ -10602,7 +10599,7 @@
         <v>111</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D386" s="2">
         <v>224</v>
@@ -10628,7 +10625,7 @@
         <v>111</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D387" s="2">
         <v>99</v>
@@ -10654,7 +10651,7 @@
         <v>111</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D388" s="2">
         <v>84</v>
@@ -10680,7 +10677,7 @@
         <v>111</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D389" s="2">
         <v>206</v>
@@ -10706,7 +10703,7 @@
         <v>111</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D390" s="2">
         <v>356</v>
@@ -10732,7 +10729,7 @@
         <v>111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D391" s="2">
         <v>370</v>
@@ -10758,7 +10755,7 @@
         <v>111</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D392" s="2">
         <v>211</v>
@@ -10784,7 +10781,7 @@
         <v>111</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D393" s="2">
         <v>198</v>
@@ -10810,7 +10807,7 @@
         <v>111</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D394" s="2">
         <v>246</v>
@@ -10836,7 +10833,7 @@
         <v>111</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D395" s="2">
         <v>119</v>
@@ -10862,7 +10859,7 @@
         <v>111</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D396" s="2">
         <v>228</v>
@@ -10888,7 +10885,7 @@
         <v>111</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D397" s="2">
         <v>166</v>
@@ -10914,7 +10911,7 @@
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D398" s="2">
         <v>421</v>
@@ -10940,7 +10937,7 @@
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D399" s="2">
         <v>99</v>
@@ -10966,7 +10963,7 @@
         <v>112</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D400" s="2">
         <v>474</v>
@@ -10992,7 +10989,7 @@
         <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D401" s="2">
         <v>398</v>
@@ -11018,7 +11015,7 @@
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D402" s="2">
         <v>147</v>
@@ -11044,7 +11041,7 @@
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D403" s="2">
         <v>443</v>
@@ -11070,7 +11067,7 @@
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D404" s="2">
         <v>259</v>
@@ -11096,7 +11093,7 @@
         <v>112</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D405" s="2">
         <v>264</v>
@@ -11122,7 +11119,7 @@
         <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D406" s="2">
         <v>450</v>
@@ -11148,7 +11145,7 @@
         <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D407" s="2">
         <v>490</v>
@@ -11174,7 +11171,7 @@
         <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D408" s="2">
         <v>457</v>
@@ -11200,7 +11197,7 @@
         <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D409" s="2">
         <v>481</v>
@@ -11226,7 +11223,7 @@
         <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D410" s="2">
         <v>452</v>
@@ -11252,7 +11249,7 @@
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D411" s="2">
         <v>194</v>
@@ -11278,7 +11275,7 @@
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D412" s="2">
         <v>399</v>
@@ -11304,7 +11301,7 @@
         <v>112</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D413" s="2">
         <v>264</v>
@@ -11330,7 +11327,7 @@
         <v>112</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D414" s="2">
         <v>109</v>
@@ -11356,7 +11353,7 @@
         <v>112</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D415" s="2">
         <v>437</v>
@@ -11382,7 +11379,7 @@
         <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D416" s="2">
         <v>447</v>
@@ -11408,7 +11405,7 @@
         <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D417" s="2">
         <v>421</v>
@@ -11434,7 +11431,7 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D418" s="2">
         <v>80</v>
@@ -11460,7 +11457,7 @@
         <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D419" s="2">
         <v>493</v>
@@ -11486,7 +11483,7 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D420" s="2">
         <v>105</v>
@@ -11512,7 +11509,7 @@
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D421" s="2">
         <v>432</v>
@@ -11538,7 +11535,7 @@
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D422" s="2">
         <v>332</v>
@@ -11564,7 +11561,7 @@
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D423" s="2">
         <v>238</v>
@@ -11590,7 +11587,7 @@
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D424" s="2">
         <v>300</v>
@@ -11616,7 +11613,7 @@
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D425" s="2">
         <v>249</v>
@@ -11642,7 +11639,7 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D426" s="2">
         <v>336</v>
@@ -11668,7 +11665,7 @@
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D427" s="2">
         <v>114</v>
@@ -11694,7 +11691,7 @@
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D428" s="2">
         <v>175</v>
@@ -11720,7 +11717,7 @@
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D429" s="2">
         <v>473</v>
@@ -11746,7 +11743,7 @@
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D430" s="2">
         <v>202</v>
@@ -11772,7 +11769,7 @@
         <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D431" s="2">
         <v>215</v>
@@ -11798,7 +11795,7 @@
         <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D432" s="2">
         <v>252</v>
@@ -11824,7 +11821,7 @@
         <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D433" s="2">
         <v>223</v>
@@ -11850,7 +11847,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>
@@ -11876,7 +11873,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11902,7 +11899,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11928,7 +11925,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>
@@ -11954,7 +11951,7 @@
         <v>113</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D438" s="2">
         <v>219</v>
@@ -11980,7 +11977,7 @@
         <v>113</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D439" s="2">
         <v>99</v>
@@ -12006,7 +12003,7 @@
         <v>113</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D440" s="2">
         <v>177</v>
@@ -12032,7 +12029,7 @@
         <v>113</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D441" s="2">
         <v>380</v>
@@ -12058,7 +12055,7 @@
         <v>113</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D442" s="2">
         <v>464</v>
@@ -12084,7 +12081,7 @@
         <v>113</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D443" s="2">
         <v>460</v>
@@ -12110,7 +12107,7 @@
         <v>113</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D444" s="2">
         <v>299</v>
@@ -12136,7 +12133,7 @@
         <v>113</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D445" s="2">
         <v>243</v>
@@ -12162,7 +12159,7 @@
         <v>113</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D446" s="2">
         <v>154</v>
@@ -12188,7 +12185,7 @@
         <v>113</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D447" s="2">
         <v>239</v>
@@ -12214,7 +12211,7 @@
         <v>113</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D448" s="2">
         <v>410</v>
@@ -12240,7 +12237,7 @@
         <v>113</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D449" s="2">
         <v>273</v>
@@ -12266,7 +12263,7 @@
         <v>113</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D450" s="2">
         <v>90</v>
@@ -12292,7 +12289,7 @@
         <v>113</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D451" s="2">
         <v>407</v>
@@ -12318,7 +12315,7 @@
         <v>113</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D452" s="2">
         <v>301</v>
@@ -12344,7 +12341,7 @@
         <v>113</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D453" s="2">
         <v>181</v>
@@ -12370,7 +12367,7 @@
         <v>113</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D454" s="2">
         <v>186</v>
@@ -12396,7 +12393,7 @@
         <v>113</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D455" s="2">
         <v>424</v>
@@ -12422,7 +12419,7 @@
         <v>113</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D456" s="2">
         <v>268</v>
@@ -12448,7 +12445,7 @@
         <v>113</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D457" s="2">
         <v>277</v>
@@ -12474,7 +12471,7 @@
         <v>113</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D458" s="2">
         <v>89</v>
@@ -12500,7 +12497,7 @@
         <v>113</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D459" s="2">
         <v>219</v>
@@ -12526,7 +12523,7 @@
         <v>113</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D460" s="2">
         <v>273</v>
@@ -12552,7 +12549,7 @@
         <v>113</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D461" s="2">
         <v>254</v>
@@ -12578,7 +12575,7 @@
         <v>113</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D462" s="2">
         <v>243</v>
@@ -12604,7 +12601,7 @@
         <v>113</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D463" s="2">
         <v>349</v>
@@ -12630,7 +12627,7 @@
         <v>113</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D464" s="2">
         <v>245</v>
@@ -12656,7 +12653,7 @@
         <v>113</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D465" s="2">
         <v>174</v>
@@ -12682,7 +12679,7 @@
         <v>113</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D466" s="2">
         <v>80</v>
@@ -12708,7 +12705,7 @@
         <v>113</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D467" s="2">
         <v>210</v>
@@ -12734,7 +12731,7 @@
         <v>113</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D468" s="2">
         <v>281</v>
@@ -12760,7 +12757,7 @@
         <v>113</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D469" s="2">
         <v>80</v>
@@ -12786,7 +12783,7 @@
         <v>114</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D470" s="2">
         <v>106</v>
@@ -12812,7 +12809,7 @@
         <v>114</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D471" s="2">
         <v>53</v>
@@ -12838,7 +12835,7 @@
         <v>114</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D472" s="2">
         <v>80</v>
@@ -12864,7 +12861,7 @@
         <v>114</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D473" s="2">
         <v>92</v>
@@ -12890,7 +12887,7 @@
         <v>114</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D474" s="2">
         <v>146</v>
@@ -12916,7 +12913,7 @@
         <v>114</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D475" s="2">
         <v>465</v>
@@ -12942,7 +12939,7 @@
         <v>114</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D476" s="2">
         <v>361</v>
@@ -12968,7 +12965,7 @@
         <v>114</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D477" s="2">
         <v>420</v>
@@ -12994,7 +12991,7 @@
         <v>114</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D478" s="2">
         <v>471</v>
@@ -13020,7 +13017,7 @@
         <v>114</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D479" s="2">
         <v>174</v>
@@ -13046,7 +13043,7 @@
         <v>114</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D480" s="2">
         <v>95</v>
@@ -13072,7 +13069,7 @@
         <v>114</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D481" s="2">
         <v>305</v>
@@ -13098,7 +13095,7 @@
         <v>114</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D482" s="2">
         <v>465</v>
@@ -13124,7 +13121,7 @@
         <v>114</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D483" s="2">
         <v>418</v>
@@ -13150,7 +13147,7 @@
         <v>114</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D484" s="2">
         <v>478</v>
@@ -13176,7 +13173,7 @@
         <v>114</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D485" s="2">
         <v>434</v>
@@ -13202,7 +13199,7 @@
         <v>114</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D486" s="2">
         <v>459</v>
@@ -13228,7 +13225,7 @@
         <v>114</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D487" s="2">
         <v>99</v>
@@ -13254,7 +13251,7 @@
         <v>114</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D488" s="2">
         <v>104</v>
@@ -13280,7 +13277,7 @@
         <v>114</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D489" s="2">
         <v>166</v>
@@ -13306,7 +13303,7 @@
         <v>114</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D490" s="2">
         <v>277</v>
@@ -13332,7 +13329,7 @@
         <v>114</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D491" s="2">
         <v>329</v>
@@ -13358,7 +13355,7 @@
         <v>114</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D492" s="2">
         <v>193</v>
@@ -13384,7 +13381,7 @@
         <v>114</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D493" s="2">
         <v>70</v>
@@ -13410,7 +13407,7 @@
         <v>114</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D494" s="2">
         <v>174</v>
@@ -13436,7 +13433,7 @@
         <v>114</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D495" s="2">
         <v>305</v>
@@ -13462,7 +13459,7 @@
         <v>114</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D496" s="2">
         <v>274</v>
@@ -13488,7 +13485,7 @@
         <v>114</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D497" s="2">
         <v>185</v>
@@ -13514,7 +13511,7 @@
         <v>114</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D498" s="2">
         <v>249</v>
@@ -13540,7 +13537,7 @@
         <v>114</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D499" s="2">
         <v>203</v>
@@ -13566,7 +13563,7 @@
         <v>114</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D500" s="2">
         <v>315</v>
@@ -13592,7 +13589,7 @@
         <v>114</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D501" s="2">
         <v>211</v>
@@ -13618,7 +13615,7 @@
         <v>114</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D502" s="2">
         <v>262</v>
@@ -13644,7 +13641,7 @@
         <v>114</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D503" s="2">
         <v>346</v>
@@ -13670,7 +13667,7 @@
         <v>114</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D504" s="2">
         <v>232</v>
@@ -13696,7 +13693,7 @@
         <v>114</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D505" s="2">
         <v>142</v>
@@ -13722,7 +13719,7 @@
         <v>115</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D506" s="2">
         <v>316</v>
@@ -13748,7 +13745,7 @@
         <v>115</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D507" s="2">
         <v>221</v>
@@ -13774,7 +13771,7 @@
         <v>115</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D508" s="2">
         <v>318</v>
@@ -13800,7 +13797,7 @@
         <v>115</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D509" s="2">
         <v>147</v>
@@ -13826,7 +13823,7 @@
         <v>115</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D510" s="2">
         <v>396</v>
@@ -13852,7 +13849,7 @@
         <v>115</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D511" s="2">
         <v>409</v>
@@ -13878,7 +13875,7 @@
         <v>115</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D512" s="2">
         <v>278</v>
@@ -13904,7 +13901,7 @@
         <v>115</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D513" s="2">
         <v>103</v>
@@ -13930,7 +13927,7 @@
         <v>115</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D514" s="2">
         <v>419</v>
@@ -13956,7 +13953,7 @@
         <v>115</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D515" s="2">
         <v>243</v>
@@ -13982,7 +13979,7 @@
         <v>115</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D516" s="2">
         <v>280</v>
@@ -14008,7 +14005,7 @@
         <v>115</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D517" s="2">
         <v>206</v>
@@ -14034,7 +14031,7 @@
         <v>115</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D518" s="2">
         <v>114</v>
@@ -14060,7 +14057,7 @@
         <v>115</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D519" s="2">
         <v>58</v>
@@ -14086,7 +14083,7 @@
         <v>115</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D520" s="2">
         <v>198</v>
@@ -14112,7 +14109,7 @@
         <v>115</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D521" s="2">
         <v>138</v>
@@ -14138,7 +14135,7 @@
         <v>115</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D522" s="2">
         <v>417</v>
@@ -14164,7 +14161,7 @@
         <v>115</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D523" s="2">
         <v>141</v>
@@ -14190,7 +14187,7 @@
         <v>115</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D524" s="2">
         <v>456</v>
@@ -14216,7 +14213,7 @@
         <v>115</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D525" s="2">
         <v>316</v>
@@ -14242,7 +14239,7 @@
         <v>115</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D526" s="2">
         <v>357</v>
@@ -14268,7 +14265,7 @@
         <v>115</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D527" s="2">
         <v>143</v>
@@ -14294,7 +14291,7 @@
         <v>115</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D528" s="2">
         <v>177</v>
@@ -14320,7 +14317,7 @@
         <v>115</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D529" s="2">
         <v>226</v>
@@ -14346,7 +14343,7 @@
         <v>115</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D530" s="2">
         <v>344</v>
@@ -14372,7 +14369,7 @@
         <v>115</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D531" s="2">
         <v>143</v>
@@ -14398,7 +14395,7 @@
         <v>115</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D532" s="2">
         <v>97</v>
@@ -14424,7 +14421,7 @@
         <v>115</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D533" s="2">
         <v>193</v>
@@ -14450,7 +14447,7 @@
         <v>115</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D534" s="2">
         <v>56</v>
@@ -14476,7 +14473,7 @@
         <v>115</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D535" s="2">
         <v>121</v>
@@ -14502,7 +14499,7 @@
         <v>115</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D536" s="2">
         <v>150</v>
@@ -14528,7 +14525,7 @@
         <v>115</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D537" s="2">
         <v>344</v>
@@ -14554,7 +14551,7 @@
         <v>115</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D538" s="2">
         <v>188</v>
@@ -14580,7 +14577,7 @@
         <v>115</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D539" s="2">
         <v>342</v>
@@ -14606,7 +14603,7 @@
         <v>115</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D540" s="2">
         <v>234</v>
@@ -14632,7 +14629,7 @@
         <v>115</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D541" s="2">
         <v>239</v>

--- a/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
+++ b/pages/hyperlocal_demand_forecasting_with_grocery_items.xlsx
@@ -156,9 +156,6 @@
     <t>2023-12</t>
   </si>
   <si>
-    <t>Pasta</t>
-  </si>
-  <si>
     <t>Tea</t>
   </si>
   <si>
@@ -199,6 +196,9 @@
   </si>
   <si>
     <t>Couscous</t>
+  </si>
+  <si>
+    <t>Œufs</t>
   </si>
 </sst>
 </file>
@@ -615,7 +615,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2">
         <v>373</v>
@@ -641,7 +641,7 @@
         <v>101</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2">
         <v>423</v>
@@ -667,7 +667,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" s="2">
         <v>147</v>
@@ -693,7 +693,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2">
         <v>431</v>
@@ -719,7 +719,7 @@
         <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2">
         <v>305</v>
@@ -745,7 +745,7 @@
         <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2">
         <v>167</v>
@@ -771,7 +771,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="2">
         <v>101</v>
@@ -797,7 +797,7 @@
         <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2">
         <v>73</v>
@@ -823,7 +823,7 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2">
         <v>445</v>
@@ -849,7 +849,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2">
         <v>180</v>
@@ -875,7 +875,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2">
         <v>221</v>
@@ -901,7 +901,7 @@
         <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2">
         <v>153</v>
@@ -927,7 +927,7 @@
         <v>101</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2">
         <v>283</v>
@@ -953,7 +953,7 @@
         <v>101</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2">
         <v>220</v>
@@ -979,7 +979,7 @@
         <v>101</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2">
         <v>338</v>
@@ -1005,7 +1005,7 @@
         <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2">
         <v>209</v>
@@ -1031,7 +1031,7 @@
         <v>101</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="2">
         <v>186</v>
@@ -1057,7 +1057,7 @@
         <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2">
         <v>383</v>
@@ -1083,7 +1083,7 @@
         <v>101</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="2">
         <v>253</v>
@@ -1109,7 +1109,7 @@
         <v>101</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="2">
         <v>159</v>
@@ -1135,7 +1135,7 @@
         <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="2">
         <v>212</v>
@@ -1161,7 +1161,7 @@
         <v>101</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="2">
         <v>377</v>
@@ -1187,7 +1187,7 @@
         <v>101</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="2">
         <v>126</v>
@@ -1213,7 +1213,7 @@
         <v>101</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="2">
         <v>283</v>
@@ -1239,7 +1239,7 @@
         <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2">
         <v>235</v>
@@ -1265,7 +1265,7 @@
         <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2">
         <v>170</v>
@@ -1291,7 +1291,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="2">
         <v>321</v>
@@ -1317,7 +1317,7 @@
         <v>101</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" s="2">
         <v>127</v>
@@ -1343,7 +1343,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="2">
         <v>162</v>
@@ -1369,7 +1369,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="2">
         <v>265</v>
@@ -1395,7 +1395,7 @@
         <v>101</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="2">
         <v>193</v>
@@ -1421,7 +1421,7 @@
         <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="2">
         <v>211</v>
@@ -1447,7 +1447,7 @@
         <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" s="2">
         <v>328</v>
@@ -1473,7 +1473,7 @@
         <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D35" s="2">
         <v>127</v>
@@ -1499,7 +1499,7 @@
         <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D36" s="2">
         <v>176</v>
@@ -1525,7 +1525,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D37" s="2">
         <v>278</v>
@@ -1551,7 +1551,7 @@
         <v>102</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D38" s="2">
         <v>255</v>
@@ -1577,7 +1577,7 @@
         <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D39" s="2">
         <v>340</v>
@@ -1603,7 +1603,7 @@
         <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D40" s="2">
         <v>105</v>
@@ -1629,7 +1629,7 @@
         <v>102</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D41" s="2">
         <v>171</v>
@@ -1655,7 +1655,7 @@
         <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D42" s="2">
         <v>291</v>
@@ -1681,7 +1681,7 @@
         <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D43" s="2">
         <v>262</v>
@@ -1707,7 +1707,7 @@
         <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44" s="2">
         <v>303</v>
@@ -1733,7 +1733,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D45" s="2">
         <v>472</v>
@@ -1759,7 +1759,7 @@
         <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D46" s="2">
         <v>88</v>
@@ -1785,7 +1785,7 @@
         <v>102</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D47" s="2">
         <v>488</v>
@@ -1811,7 +1811,7 @@
         <v>102</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D48" s="2">
         <v>149</v>
@@ -1837,7 +1837,7 @@
         <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D49" s="2">
         <v>366</v>
@@ -1863,7 +1863,7 @@
         <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D50" s="2">
         <v>122</v>
@@ -1889,7 +1889,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D51" s="2">
         <v>316</v>
@@ -1915,7 +1915,7 @@
         <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D52" s="2">
         <v>51</v>
@@ -1941,7 +1941,7 @@
         <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D53" s="2">
         <v>295</v>
@@ -1967,7 +1967,7 @@
         <v>102</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D54" s="2">
         <v>240</v>
@@ -1993,7 +1993,7 @@
         <v>102</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D55" s="2">
         <v>448</v>
@@ -2019,7 +2019,7 @@
         <v>102</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2">
         <v>264</v>
@@ -2045,7 +2045,7 @@
         <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D57" s="2">
         <v>391</v>
@@ -2071,7 +2071,7 @@
         <v>102</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D58" s="2">
         <v>299</v>
@@ -2097,7 +2097,7 @@
         <v>102</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D59" s="2">
         <v>322</v>
@@ -2123,7 +2123,7 @@
         <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D60" s="2">
         <v>62</v>
@@ -2149,7 +2149,7 @@
         <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D61" s="2">
         <v>440</v>
@@ -2175,7 +2175,7 @@
         <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D62" s="2">
         <v>375</v>
@@ -2201,7 +2201,7 @@
         <v>102</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D63" s="2">
         <v>247</v>
@@ -2227,7 +2227,7 @@
         <v>102</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D64" s="2">
         <v>195</v>
@@ -2253,7 +2253,7 @@
         <v>102</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D65" s="2">
         <v>259</v>
@@ -2279,7 +2279,7 @@
         <v>102</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D66" s="2">
         <v>236</v>
@@ -2305,7 +2305,7 @@
         <v>102</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D67" s="2">
         <v>259</v>
@@ -2331,7 +2331,7 @@
         <v>102</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D68" s="2">
         <v>260</v>
@@ -2357,7 +2357,7 @@
         <v>102</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D69" s="2">
         <v>173</v>
@@ -2383,7 +2383,7 @@
         <v>102</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D70" s="2">
         <v>186</v>
@@ -2409,7 +2409,7 @@
         <v>102</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D71" s="2">
         <v>274</v>
@@ -2435,7 +2435,7 @@
         <v>102</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D72" s="2">
         <v>238</v>
@@ -2461,7 +2461,7 @@
         <v>102</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D73" s="2">
         <v>109</v>
@@ -2487,7 +2487,7 @@
         <v>103</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D74" s="2">
         <v>380</v>
@@ -2513,7 +2513,7 @@
         <v>103</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D75" s="2">
         <v>383</v>
@@ -2539,7 +2539,7 @@
         <v>103</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D76" s="2">
         <v>168</v>
@@ -2565,7 +2565,7 @@
         <v>103</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D77" s="2">
         <v>73</v>
@@ -2591,7 +2591,7 @@
         <v>103</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D78" s="2">
         <v>282</v>
@@ -2617,7 +2617,7 @@
         <v>103</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D79" s="2">
         <v>362</v>
@@ -2643,7 +2643,7 @@
         <v>103</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D80" s="2">
         <v>386</v>
@@ -2669,7 +2669,7 @@
         <v>103</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D81" s="2">
         <v>323</v>
@@ -2695,7 +2695,7 @@
         <v>103</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D82" s="2">
         <v>51</v>
@@ -2721,7 +2721,7 @@
         <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D83" s="2">
         <v>452</v>
@@ -2747,7 +2747,7 @@
         <v>103</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D84" s="2">
         <v>55</v>
@@ -2773,7 +2773,7 @@
         <v>103</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D85" s="2">
         <v>341</v>
@@ -2799,7 +2799,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D86" s="2">
         <v>155</v>
@@ -2825,7 +2825,7 @@
         <v>103</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D87" s="2">
         <v>496</v>
@@ -2851,7 +2851,7 @@
         <v>103</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D88" s="2">
         <v>462</v>
@@ -2877,7 +2877,7 @@
         <v>103</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D89" s="2">
         <v>394</v>
@@ -2903,7 +2903,7 @@
         <v>103</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D90" s="2">
         <v>207</v>
@@ -2929,7 +2929,7 @@
         <v>103</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D91" s="2">
         <v>336</v>
@@ -2955,7 +2955,7 @@
         <v>103</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D92" s="2">
         <v>481</v>
@@ -2981,7 +2981,7 @@
         <v>103</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D93" s="2">
         <v>180</v>
@@ -3007,7 +3007,7 @@
         <v>103</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D94" s="2">
         <v>337</v>
@@ -3033,7 +3033,7 @@
         <v>103</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D95" s="2">
         <v>88</v>
@@ -3059,7 +3059,7 @@
         <v>103</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D96" s="2">
         <v>221</v>
@@ -3085,7 +3085,7 @@
         <v>103</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D97" s="2">
         <v>442</v>
@@ -3111,7 +3111,7 @@
         <v>103</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D98" s="2">
         <v>216</v>
@@ -3137,7 +3137,7 @@
         <v>103</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D99" s="2">
         <v>237</v>
@@ -3163,7 +3163,7 @@
         <v>103</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D100" s="2">
         <v>336</v>
@@ -3189,7 +3189,7 @@
         <v>103</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D101" s="2">
         <v>281</v>
@@ -3215,7 +3215,7 @@
         <v>103</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D102" s="2">
         <v>216</v>
@@ -3241,7 +3241,7 @@
         <v>103</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D103" s="2">
         <v>214</v>
@@ -3267,7 +3267,7 @@
         <v>103</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D104" s="2">
         <v>323</v>
@@ -3293,7 +3293,7 @@
         <v>103</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D105" s="2">
         <v>305</v>
@@ -3319,7 +3319,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D106" s="2">
         <v>258</v>
@@ -3345,7 +3345,7 @@
         <v>103</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D107" s="2">
         <v>235</v>
@@ -3371,7 +3371,7 @@
         <v>103</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D108" s="2">
         <v>250</v>
@@ -3397,7 +3397,7 @@
         <v>103</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D109" s="2">
         <v>225</v>
@@ -3423,7 +3423,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D110" s="2">
         <v>336</v>
@@ -3449,7 +3449,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D111" s="2">
         <v>70</v>
@@ -3475,7 +3475,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D112" s="2">
         <v>166</v>
@@ -3501,7 +3501,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D113" s="2">
         <v>157</v>
@@ -3527,7 +3527,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D114" s="2">
         <v>114</v>
@@ -3553,7 +3553,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D115" s="2">
         <v>246</v>
@@ -3579,7 +3579,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D116" s="2">
         <v>375</v>
@@ -3605,7 +3605,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D117" s="2">
         <v>241</v>
@@ -3631,7 +3631,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D118" s="2">
         <v>286</v>
@@ -3657,7 +3657,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D119" s="2">
         <v>118</v>
@@ -3683,7 +3683,7 @@
         <v>104</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D120" s="2">
         <v>494</v>
@@ -3709,7 +3709,7 @@
         <v>104</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D121" s="2">
         <v>233</v>
@@ -3735,7 +3735,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D122" s="2">
         <v>353</v>
@@ -3761,7 +3761,7 @@
         <v>104</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D123" s="2">
         <v>202</v>
@@ -3787,7 +3787,7 @@
         <v>104</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D124" s="2">
         <v>150</v>
@@ -3813,7 +3813,7 @@
         <v>104</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D125" s="2">
         <v>386</v>
@@ -3839,7 +3839,7 @@
         <v>104</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D126" s="2">
         <v>92</v>
@@ -3865,7 +3865,7 @@
         <v>104</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D127" s="2">
         <v>141</v>
@@ -3891,7 +3891,7 @@
         <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D128" s="2">
         <v>303</v>
@@ -3917,7 +3917,7 @@
         <v>104</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D129" s="2">
         <v>281</v>
@@ -3943,7 +3943,7 @@
         <v>104</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D130" s="2">
         <v>453</v>
@@ -3969,7 +3969,7 @@
         <v>104</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D131" s="2">
         <v>310</v>
@@ -3995,7 +3995,7 @@
         <v>104</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D132" s="2">
         <v>243</v>
@@ -4021,7 +4021,7 @@
         <v>104</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D133" s="2">
         <v>248</v>
@@ -4047,7 +4047,7 @@
         <v>104</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D134" s="2">
         <v>253</v>
@@ -4073,7 +4073,7 @@
         <v>104</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D135" s="2">
         <v>197</v>
@@ -4099,7 +4099,7 @@
         <v>104</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D136" s="2">
         <v>184</v>
@@ -4125,7 +4125,7 @@
         <v>104</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D137" s="2">
         <v>119</v>
@@ -4151,7 +4151,7 @@
         <v>104</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D138" s="2">
         <v>192</v>
@@ -4177,7 +4177,7 @@
         <v>104</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D139" s="2">
         <v>237</v>
@@ -4203,7 +4203,7 @@
         <v>104</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D140" s="2">
         <v>71</v>
@@ -4229,7 +4229,7 @@
         <v>104</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D141" s="2">
         <v>170</v>
@@ -4255,7 +4255,7 @@
         <v>104</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D142" s="2">
         <v>201</v>
@@ -4281,7 +4281,7 @@
         <v>104</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D143" s="2">
         <v>226</v>
@@ -4307,7 +4307,7 @@
         <v>104</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D144" s="2">
         <v>251</v>
@@ -4333,7 +4333,7 @@
         <v>104</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D145" s="2">
         <v>281</v>
@@ -4359,7 +4359,7 @@
         <v>105</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D146" s="2">
         <v>494</v>
@@ -4385,7 +4385,7 @@
         <v>105</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D147" s="2">
         <v>383</v>
@@ -4411,7 +4411,7 @@
         <v>105</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D148" s="2">
         <v>243</v>
@@ -4437,7 +4437,7 @@
         <v>105</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D149" s="2">
         <v>384</v>
@@ -4463,7 +4463,7 @@
         <v>105</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D150" s="2">
         <v>316</v>
@@ -4489,7 +4489,7 @@
         <v>105</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D151" s="2">
         <v>362</v>
@@ -4515,7 +4515,7 @@
         <v>105</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D152" s="2">
         <v>479</v>
@@ -4541,7 +4541,7 @@
         <v>105</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D153" s="2">
         <v>317</v>
@@ -4567,7 +4567,7 @@
         <v>105</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D154" s="2">
         <v>240</v>
@@ -4593,7 +4593,7 @@
         <v>105</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D155" s="2">
         <v>290</v>
@@ -4619,7 +4619,7 @@
         <v>105</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D156" s="2">
         <v>477</v>
@@ -4645,7 +4645,7 @@
         <v>105</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D157" s="2">
         <v>362</v>
@@ -4671,7 +4671,7 @@
         <v>105</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D158" s="2">
         <v>54</v>
@@ -4697,7 +4697,7 @@
         <v>105</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D159" s="2">
         <v>281</v>
@@ -4723,7 +4723,7 @@
         <v>105</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D160" s="2">
         <v>381</v>
@@ -4749,7 +4749,7 @@
         <v>105</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D161" s="2">
         <v>351</v>
@@ -4775,7 +4775,7 @@
         <v>105</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D162" s="2">
         <v>309</v>
@@ -4801,7 +4801,7 @@
         <v>105</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D163" s="2">
         <v>383</v>
@@ -4827,7 +4827,7 @@
         <v>105</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D164" s="2">
         <v>407</v>
@@ -4853,7 +4853,7 @@
         <v>105</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D165" s="2">
         <v>171</v>
@@ -4879,7 +4879,7 @@
         <v>105</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D166" s="2">
         <v>274</v>
@@ -4905,7 +4905,7 @@
         <v>105</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D167" s="2">
         <v>295</v>
@@ -4931,7 +4931,7 @@
         <v>105</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D168" s="2">
         <v>418</v>
@@ -4957,7 +4957,7 @@
         <v>105</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D169" s="2">
         <v>84</v>
@@ -4983,7 +4983,7 @@
         <v>105</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D170" s="2">
         <v>247</v>
@@ -5009,7 +5009,7 @@
         <v>105</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D171" s="2">
         <v>179</v>
@@ -5035,7 +5035,7 @@
         <v>105</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D172" s="2">
         <v>322</v>
@@ -5061,7 +5061,7 @@
         <v>105</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D173" s="2">
         <v>271</v>
@@ -5087,7 +5087,7 @@
         <v>105</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D174" s="2">
         <v>281</v>
@@ -5113,7 +5113,7 @@
         <v>105</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D175" s="2">
         <v>174</v>
@@ -5139,7 +5139,7 @@
         <v>105</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D176" s="2">
         <v>305</v>
@@ -5165,7 +5165,7 @@
         <v>105</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D177" s="2">
         <v>254</v>
@@ -5191,7 +5191,7 @@
         <v>105</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D178" s="2">
         <v>312</v>
@@ -5217,7 +5217,7 @@
         <v>105</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D179" s="2">
         <v>115</v>
@@ -5243,7 +5243,7 @@
         <v>105</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D180" s="2">
         <v>161</v>
@@ -5269,7 +5269,7 @@
         <v>105</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D181" s="2">
         <v>240</v>
@@ -5295,7 +5295,7 @@
         <v>106</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D182" s="2">
         <v>469</v>
@@ -5321,7 +5321,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D183" s="2">
         <v>311</v>
@@ -5347,7 +5347,7 @@
         <v>106</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D184" s="2">
         <v>105</v>
@@ -5373,7 +5373,7 @@
         <v>106</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D185" s="2">
         <v>297</v>
@@ -5399,7 +5399,7 @@
         <v>106</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D186" s="2">
         <v>412</v>
@@ -5425,7 +5425,7 @@
         <v>106</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D187" s="2">
         <v>342</v>
@@ -5451,7 +5451,7 @@
         <v>106</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D188" s="2">
         <v>285</v>
@@ -5477,7 +5477,7 @@
         <v>106</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D189" s="2">
         <v>453</v>
@@ -5503,7 +5503,7 @@
         <v>106</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D190" s="2">
         <v>69</v>
@@ -5529,7 +5529,7 @@
         <v>106</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D191" s="2">
         <v>154</v>
@@ -5555,7 +5555,7 @@
         <v>106</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D192" s="2">
         <v>246</v>
@@ -5581,7 +5581,7 @@
         <v>106</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D193" s="2">
         <v>446</v>
@@ -5607,7 +5607,7 @@
         <v>106</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D194" s="2">
         <v>467</v>
@@ -5633,7 +5633,7 @@
         <v>106</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D195" s="2">
         <v>374</v>
@@ -5659,7 +5659,7 @@
         <v>106</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D196" s="2">
         <v>266</v>
@@ -5685,7 +5685,7 @@
         <v>106</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D197" s="2">
         <v>281</v>
@@ -5711,7 +5711,7 @@
         <v>106</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D198" s="2">
         <v>277</v>
@@ -5737,7 +5737,7 @@
         <v>106</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D199" s="2">
         <v>153</v>
@@ -5763,7 +5763,7 @@
         <v>106</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D200" s="2">
         <v>176</v>
@@ -5789,7 +5789,7 @@
         <v>106</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D201" s="2">
         <v>281</v>
@@ -5815,7 +5815,7 @@
         <v>106</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D202" s="2">
         <v>52</v>
@@ -5841,7 +5841,7 @@
         <v>106</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D203" s="2">
         <v>94</v>
@@ -5867,7 +5867,7 @@
         <v>106</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D204" s="2">
         <v>181</v>
@@ -5893,7 +5893,7 @@
         <v>106</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D205" s="2">
         <v>336</v>
@@ -5919,7 +5919,7 @@
         <v>106</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D206" s="2">
         <v>349</v>
@@ -5945,7 +5945,7 @@
         <v>106</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D207" s="2">
         <v>127</v>
@@ -5971,7 +5971,7 @@
         <v>106</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D208" s="2">
         <v>376</v>
@@ -5997,7 +5997,7 @@
         <v>106</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D209" s="2">
         <v>98</v>
@@ -6023,7 +6023,7 @@
         <v>106</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D210" s="2">
         <v>152</v>
@@ -6049,7 +6049,7 @@
         <v>106</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D211" s="2">
         <v>235</v>
@@ -6075,7 +6075,7 @@
         <v>106</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D212" s="2">
         <v>105</v>
@@ -6101,7 +6101,7 @@
         <v>106</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D213" s="2">
         <v>150</v>
@@ -6127,7 +6127,7 @@
         <v>106</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D214" s="2">
         <v>215</v>
@@ -6153,7 +6153,7 @@
         <v>106</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D215" s="2">
         <v>216</v>
@@ -6179,7 +6179,7 @@
         <v>106</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D216" s="2">
         <v>214</v>
@@ -6205,7 +6205,7 @@
         <v>106</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D217" s="2">
         <v>194</v>
@@ -6231,7 +6231,7 @@
         <v>107</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D218" s="2">
         <v>184</v>
@@ -6257,7 +6257,7 @@
         <v>107</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D219" s="2">
         <v>379</v>
@@ -6283,7 +6283,7 @@
         <v>107</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D220" s="2">
         <v>424</v>
@@ -6309,7 +6309,7 @@
         <v>107</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D221" s="2">
         <v>93</v>
@@ -6335,7 +6335,7 @@
         <v>107</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D222" s="2">
         <v>219</v>
@@ -6361,7 +6361,7 @@
         <v>107</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D223" s="2">
         <v>165</v>
@@ -6387,7 +6387,7 @@
         <v>107</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D224" s="2">
         <v>462</v>
@@ -6413,7 +6413,7 @@
         <v>107</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D225" s="2">
         <v>332</v>
@@ -6439,7 +6439,7 @@
         <v>107</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D226" s="2">
         <v>162</v>
@@ -6465,7 +6465,7 @@
         <v>107</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D227" s="2">
         <v>305</v>
@@ -6491,7 +6491,7 @@
         <v>107</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D228" s="2">
         <v>446</v>
@@ -6517,7 +6517,7 @@
         <v>107</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D229" s="2">
         <v>196</v>
@@ -6543,7 +6543,7 @@
         <v>107</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D230" s="2">
         <v>443</v>
@@ -6569,7 +6569,7 @@
         <v>107</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D231" s="2">
         <v>158</v>
@@ -6595,7 +6595,7 @@
         <v>107</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D232" s="2">
         <v>191</v>
@@ -6621,7 +6621,7 @@
         <v>107</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D233" s="2">
         <v>321</v>
@@ -6647,7 +6647,7 @@
         <v>107</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D234" s="2">
         <v>316</v>
@@ -6673,7 +6673,7 @@
         <v>107</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D235" s="2">
         <v>71</v>
@@ -6699,7 +6699,7 @@
         <v>107</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D236" s="2">
         <v>171</v>
@@ -6725,7 +6725,7 @@
         <v>107</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D237" s="2">
         <v>450</v>
@@ -6751,7 +6751,7 @@
         <v>107</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D238" s="2">
         <v>354</v>
@@ -6777,7 +6777,7 @@
         <v>107</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D239" s="2">
         <v>475</v>
@@ -6803,7 +6803,7 @@
         <v>107</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D240" s="2">
         <v>130</v>
@@ -6829,7 +6829,7 @@
         <v>107</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D241" s="2">
         <v>140</v>
@@ -6855,7 +6855,7 @@
         <v>107</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D242" s="2">
         <v>253</v>
@@ -6881,7 +6881,7 @@
         <v>107</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D243" s="2">
         <v>246</v>
@@ -6907,7 +6907,7 @@
         <v>107</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D244" s="2">
         <v>297</v>
@@ -6933,7 +6933,7 @@
         <v>107</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D245" s="2">
         <v>201</v>
@@ -6959,7 +6959,7 @@
         <v>107</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D246" s="2">
         <v>339</v>
@@ -6985,7 +6985,7 @@
         <v>107</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D247" s="2">
         <v>132</v>
@@ -7011,7 +7011,7 @@
         <v>107</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D248" s="2">
         <v>239</v>
@@ -7037,7 +7037,7 @@
         <v>107</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D249" s="2">
         <v>169</v>
@@ -7063,7 +7063,7 @@
         <v>107</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D250" s="2">
         <v>217</v>
@@ -7089,7 +7089,7 @@
         <v>107</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D251" s="2">
         <v>340</v>
@@ -7115,7 +7115,7 @@
         <v>107</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D252" s="2">
         <v>192</v>
@@ -7141,7 +7141,7 @@
         <v>107</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D253" s="2">
         <v>243</v>
@@ -7167,7 +7167,7 @@
         <v>108</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D254" s="2">
         <v>445</v>
@@ -7193,7 +7193,7 @@
         <v>108</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D255" s="2">
         <v>274</v>
@@ -7219,7 +7219,7 @@
         <v>108</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D256" s="2">
         <v>338</v>
@@ -7245,7 +7245,7 @@
         <v>108</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D257" s="2">
         <v>451</v>
@@ -7271,7 +7271,7 @@
         <v>108</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D258" s="2">
         <v>183</v>
@@ -7297,7 +7297,7 @@
         <v>108</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D259" s="2">
         <v>311</v>
@@ -7323,7 +7323,7 @@
         <v>108</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D260" s="2">
         <v>365</v>
@@ -7349,7 +7349,7 @@
         <v>108</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D261" s="2">
         <v>411</v>
@@ -7375,7 +7375,7 @@
         <v>108</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D262" s="2">
         <v>130</v>
@@ -7401,7 +7401,7 @@
         <v>108</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D263" s="2">
         <v>69</v>
@@ -7427,7 +7427,7 @@
         <v>108</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D264" s="2">
         <v>391</v>
@@ -7453,7 +7453,7 @@
         <v>108</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D265" s="2">
         <v>475</v>
@@ -7479,7 +7479,7 @@
         <v>108</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D266" s="2">
         <v>386</v>
@@ -7505,7 +7505,7 @@
         <v>108</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D267" s="2">
         <v>345</v>
@@ -7531,7 +7531,7 @@
         <v>108</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D268" s="2">
         <v>57</v>
@@ -7557,7 +7557,7 @@
         <v>108</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D269" s="2">
         <v>489</v>
@@ -7583,7 +7583,7 @@
         <v>108</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D270" s="2">
         <v>88</v>
@@ -7609,7 +7609,7 @@
         <v>108</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D271" s="2">
         <v>417</v>
@@ -7635,7 +7635,7 @@
         <v>108</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D272" s="2">
         <v>437</v>
@@ -7661,7 +7661,7 @@
         <v>108</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D273" s="2">
         <v>249</v>
@@ -7687,7 +7687,7 @@
         <v>108</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D274" s="2">
         <v>86</v>
@@ -7713,7 +7713,7 @@
         <v>108</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D275" s="2">
         <v>191</v>
@@ -7739,7 +7739,7 @@
         <v>108</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D276" s="2">
         <v>298</v>
@@ -7765,7 +7765,7 @@
         <v>108</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D277" s="2">
         <v>235</v>
@@ -7791,7 +7791,7 @@
         <v>108</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D278" s="2">
         <v>201</v>
@@ -7817,7 +7817,7 @@
         <v>108</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D279" s="2">
         <v>158</v>
@@ -7843,7 +7843,7 @@
         <v>108</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D280" s="2">
         <v>135</v>
@@ -7869,7 +7869,7 @@
         <v>108</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D281" s="2">
         <v>333</v>
@@ -7895,7 +7895,7 @@
         <v>108</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D282" s="2">
         <v>352</v>
@@ -7921,7 +7921,7 @@
         <v>108</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D283" s="2">
         <v>66</v>
@@ -7947,7 +7947,7 @@
         <v>108</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D284" s="2">
         <v>116</v>
@@ -7973,7 +7973,7 @@
         <v>108</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D285" s="2">
         <v>214</v>
@@ -7999,7 +7999,7 @@
         <v>108</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D286" s="2">
         <v>210</v>
@@ -8025,7 +8025,7 @@
         <v>108</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D287" s="2">
         <v>295</v>
@@ -8051,7 +8051,7 @@
         <v>108</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D288" s="2">
         <v>112</v>
@@ -8077,7 +8077,7 @@
         <v>108</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D289" s="2">
         <v>222</v>
@@ -8103,7 +8103,7 @@
         <v>109</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D290" s="2">
         <v>212</v>
@@ -8129,7 +8129,7 @@
         <v>109</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D291" s="2">
         <v>457</v>
@@ -8155,7 +8155,7 @@
         <v>109</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D292" s="2">
         <v>203</v>
@@ -8181,7 +8181,7 @@
         <v>109</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D293" s="2">
         <v>247</v>
@@ -8207,7 +8207,7 @@
         <v>109</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D294" s="2">
         <v>113</v>
@@ -8233,7 +8233,7 @@
         <v>109</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D295" s="2">
         <v>107</v>
@@ -8259,7 +8259,7 @@
         <v>109</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D296" s="2">
         <v>338</v>
@@ -8285,7 +8285,7 @@
         <v>109</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D297" s="2">
         <v>259</v>
@@ -8311,7 +8311,7 @@
         <v>109</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D298" s="2">
         <v>430</v>
@@ -8337,7 +8337,7 @@
         <v>109</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D299" s="2">
         <v>329</v>
@@ -8363,7 +8363,7 @@
         <v>109</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D300" s="2">
         <v>369</v>
@@ -8389,7 +8389,7 @@
         <v>109</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D301" s="2">
         <v>262</v>
@@ -8415,7 +8415,7 @@
         <v>109</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D302" s="2">
         <v>253</v>
@@ -8441,7 +8441,7 @@
         <v>109</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D303" s="2">
         <v>257</v>
@@ -8467,7 +8467,7 @@
         <v>109</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D304" s="2">
         <v>446</v>
@@ -8493,7 +8493,7 @@
         <v>109</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D305" s="2">
         <v>270</v>
@@ -8519,7 +8519,7 @@
         <v>109</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D306" s="2">
         <v>486</v>
@@ -8545,7 +8545,7 @@
         <v>109</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D307" s="2">
         <v>484</v>
@@ -8571,7 +8571,7 @@
         <v>109</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D308" s="2">
         <v>277</v>
@@ -8597,7 +8597,7 @@
         <v>109</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D309" s="2">
         <v>298</v>
@@ -8623,7 +8623,7 @@
         <v>109</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D310" s="2">
         <v>148</v>
@@ -8649,7 +8649,7 @@
         <v>109</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D311" s="2">
         <v>218</v>
@@ -8675,7 +8675,7 @@
         <v>109</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D312" s="2">
         <v>253</v>
@@ -8701,7 +8701,7 @@
         <v>109</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D313" s="2">
         <v>266</v>
@@ -8727,7 +8727,7 @@
         <v>109</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D314" s="2">
         <v>290</v>
@@ -8753,7 +8753,7 @@
         <v>109</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D315" s="2">
         <v>197</v>
@@ -8779,7 +8779,7 @@
         <v>109</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D316" s="2">
         <v>160</v>
@@ -8805,7 +8805,7 @@
         <v>109</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D317" s="2">
         <v>272</v>
@@ -8831,7 +8831,7 @@
         <v>109</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D318" s="2">
         <v>254</v>
@@ -8857,7 +8857,7 @@
         <v>109</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D319" s="2">
         <v>160</v>
@@ -8883,7 +8883,7 @@
         <v>109</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D320" s="2">
         <v>150</v>
@@ -8909,7 +8909,7 @@
         <v>109</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D321" s="2">
         <v>247</v>
@@ -8935,7 +8935,7 @@
         <v>109</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D322" s="2">
         <v>263</v>
@@ -8961,7 +8961,7 @@
         <v>109</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D323" s="2">
         <v>267</v>
@@ -8987,7 +8987,7 @@
         <v>109</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D324" s="2">
         <v>223</v>
@@ -9013,7 +9013,7 @@
         <v>109</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D325" s="2">
         <v>170</v>
@@ -9039,7 +9039,7 @@
         <v>110</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D326" s="2">
         <v>175</v>
@@ -9065,7 +9065,7 @@
         <v>110</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D327" s="2">
         <v>333</v>
@@ -9091,7 +9091,7 @@
         <v>110</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D328" s="2">
         <v>442</v>
@@ -9117,7 +9117,7 @@
         <v>110</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D329" s="2">
         <v>131</v>
@@ -9143,7 +9143,7 @@
         <v>110</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D330" s="2">
         <v>275</v>
@@ -9169,7 +9169,7 @@
         <v>110</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D331" s="2">
         <v>170</v>
@@ -9195,7 +9195,7 @@
         <v>110</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D332" s="2">
         <v>94</v>
@@ -9221,7 +9221,7 @@
         <v>110</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D333" s="2">
         <v>56</v>
@@ -9247,7 +9247,7 @@
         <v>110</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D334" s="2">
         <v>297</v>
@@ -9273,7 +9273,7 @@
         <v>110</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D335" s="2">
         <v>389</v>
@@ -9299,7 +9299,7 @@
         <v>110</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D336" s="2">
         <v>88</v>
@@ -9325,7 +9325,7 @@
         <v>110</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D337" s="2">
         <v>101</v>
@@ -9351,7 +9351,7 @@
         <v>110</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D338" s="2">
         <v>237</v>
@@ -9377,7 +9377,7 @@
         <v>110</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D339" s="2">
         <v>251</v>
@@ -9403,7 +9403,7 @@
         <v>110</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D340" s="2">
         <v>62</v>
@@ -9429,7 +9429,7 @@
         <v>110</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D341" s="2">
         <v>144</v>
@@ -9455,7 +9455,7 @@
         <v>110</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D342" s="2">
         <v>180</v>
@@ -9481,7 +9481,7 @@
         <v>110</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D343" s="2">
         <v>358</v>
@@ -9507,7 +9507,7 @@
         <v>110</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D344" s="2">
         <v>452</v>
@@ -9533,7 +9533,7 @@
         <v>110</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D345" s="2">
         <v>121</v>
@@ -9559,7 +9559,7 @@
         <v>110</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D346" s="2">
         <v>354</v>
@@ -9585,7 +9585,7 @@
         <v>110</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D347" s="2">
         <v>151</v>
@@ -9611,7 +9611,7 @@
         <v>110</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D348" s="2">
         <v>270</v>
@@ -9637,7 +9637,7 @@
         <v>110</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D349" s="2">
         <v>361</v>
@@ -9663,7 +9663,7 @@
         <v>110</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D350" s="2">
         <v>148</v>
@@ -9689,7 +9689,7 @@
         <v>110</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D351" s="2">
         <v>223</v>
@@ -9715,7 +9715,7 @@
         <v>110</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D352" s="2">
         <v>79</v>
@@ -9741,7 +9741,7 @@
         <v>110</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D353" s="2">
         <v>104</v>
@@ -9767,7 +9767,7 @@
         <v>110</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D354" s="2">
         <v>294</v>
@@ -9793,7 +9793,7 @@
         <v>110</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D355" s="2">
         <v>248</v>
@@ -9819,7 +9819,7 @@
         <v>110</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D356" s="2">
         <v>215</v>
@@ -9845,7 +9845,7 @@
         <v>110</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D357" s="2">
         <v>258</v>
@@ -9871,7 +9871,7 @@
         <v>110</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D358" s="2">
         <v>201</v>
@@ -9897,7 +9897,7 @@
         <v>110</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D359" s="2">
         <v>238</v>
@@ -9923,7 +9923,7 @@
         <v>110</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D360" s="2">
         <v>286</v>
@@ -9949,7 +9949,7 @@
         <v>110</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D361" s="2">
         <v>386</v>
@@ -9975,7 +9975,7 @@
         <v>111</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D362" s="2">
         <v>497</v>
@@ -10001,7 +10001,7 @@
         <v>111</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D363" s="2">
         <v>372</v>
@@ -10027,7 +10027,7 @@
         <v>111</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D364" s="2">
         <v>377</v>
@@ -10053,7 +10053,7 @@
         <v>111</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D365" s="2">
         <v>450</v>
@@ -10079,7 +10079,7 @@
         <v>111</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D366" s="2">
         <v>381</v>
@@ -10105,7 +10105,7 @@
         <v>111</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D367" s="2">
         <v>132</v>
@@ -10131,7 +10131,7 @@
         <v>111</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D368" s="2">
         <v>160</v>
@@ -10157,7 +10157,7 @@
         <v>111</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D369" s="2">
         <v>80</v>
@@ -10183,7 +10183,7 @@
         <v>111</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D370" s="2">
         <v>124</v>
@@ -10209,7 +10209,7 @@
         <v>111</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D371" s="2">
         <v>468</v>
@@ -10235,7 +10235,7 @@
         <v>111</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D372" s="2">
         <v>131</v>
@@ -10261,7 +10261,7 @@
         <v>111</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D373" s="2">
         <v>171</v>
@@ -10287,7 +10287,7 @@
         <v>111</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D374" s="2">
         <v>470</v>
@@ -10313,7 +10313,7 @@
         <v>111</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D375" s="2">
         <v>423</v>
@@ -10339,7 +10339,7 @@
         <v>111</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D376" s="2">
         <v>392</v>
@@ -10365,7 +10365,7 @@
         <v>111</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D377" s="2">
         <v>330</v>
@@ -10391,7 +10391,7 @@
         <v>111</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D378" s="2">
         <v>287</v>
@@ -10417,7 +10417,7 @@
         <v>111</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D379" s="2">
         <v>171</v>
@@ -10443,7 +10443,7 @@
         <v>111</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D380" s="2">
         <v>470</v>
@@ -10469,7 +10469,7 @@
         <v>111</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D381" s="2">
         <v>345</v>
@@ -10495,7 +10495,7 @@
         <v>111</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D382" s="2">
         <v>78</v>
@@ -10521,7 +10521,7 @@
         <v>111</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D383" s="2">
         <v>389</v>
@@ -10547,7 +10547,7 @@
         <v>111</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D384" s="2">
         <v>129</v>
@@ -10573,7 +10573,7 @@
         <v>111</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D385" s="2">
         <v>449</v>
@@ -10599,7 +10599,7 @@
         <v>111</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D386" s="2">
         <v>224</v>
@@ -10625,7 +10625,7 @@
         <v>111</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D387" s="2">
         <v>99</v>
@@ -10651,7 +10651,7 @@
         <v>111</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D388" s="2">
         <v>84</v>
@@ -10677,7 +10677,7 @@
         <v>111</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D389" s="2">
         <v>206</v>
@@ -10703,7 +10703,7 @@
         <v>111</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D390" s="2">
         <v>356</v>
@@ -10729,7 +10729,7 @@
         <v>111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D391" s="2">
         <v>370</v>
@@ -10755,7 +10755,7 @@
         <v>111</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D392" s="2">
         <v>211</v>
@@ -10781,7 +10781,7 @@
         <v>111</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D393" s="2">
         <v>198</v>
@@ -10807,7 +10807,7 @@
         <v>111</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D394" s="2">
         <v>246</v>
@@ -10833,7 +10833,7 @@
         <v>111</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D395" s="2">
         <v>119</v>
@@ -10859,7 +10859,7 @@
         <v>111</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D396" s="2">
         <v>228</v>
@@ -10885,7 +10885,7 @@
         <v>111</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D397" s="2">
         <v>166</v>
@@ -10911,7 +10911,7 @@
         <v>112</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D398" s="2">
         <v>421</v>
@@ -10937,7 +10937,7 @@
         <v>112</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D399" s="2">
         <v>99</v>
@@ -10963,7 +10963,7 @@
         <v>112</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D400" s="2">
         <v>474</v>
@@ -10989,7 +10989,7 @@
         <v>112</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D401" s="2">
         <v>398</v>
@@ -11015,7 +11015,7 @@
         <v>112</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D402" s="2">
         <v>147</v>
@@ -11041,7 +11041,7 @@
         <v>112</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D403" s="2">
         <v>443</v>
@@ -11067,7 +11067,7 @@
         <v>112</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D404" s="2">
         <v>259</v>
@@ -11093,7 +11093,7 @@
         <v>112</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D405" s="2">
         <v>264</v>
@@ -11119,7 +11119,7 @@
         <v>112</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D406" s="2">
         <v>450</v>
@@ -11145,7 +11145,7 @@
         <v>112</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D407" s="2">
         <v>490</v>
@@ -11171,7 +11171,7 @@
         <v>112</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D408" s="2">
         <v>457</v>
@@ -11197,7 +11197,7 @@
         <v>112</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D409" s="2">
         <v>481</v>
@@ -11223,7 +11223,7 @@
         <v>112</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D410" s="2">
         <v>452</v>
@@ -11249,7 +11249,7 @@
         <v>112</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D411" s="2">
         <v>194</v>
@@ -11275,7 +11275,7 @@
         <v>112</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D412" s="2">
         <v>399</v>
@@ -11301,7 +11301,7 @@
         <v>112</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D413" s="2">
         <v>264</v>
@@ -11327,7 +11327,7 @@
         <v>112</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D414" s="2">
         <v>109</v>
@@ -11353,7 +11353,7 @@
         <v>112</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D415" s="2">
         <v>437</v>
@@ -11379,7 +11379,7 @@
         <v>112</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D416" s="2">
         <v>447</v>
@@ -11405,7 +11405,7 @@
         <v>112</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D417" s="2">
         <v>421</v>
@@ -11431,7 +11431,7 @@
         <v>112</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D418" s="2">
         <v>80</v>
@@ -11457,7 +11457,7 @@
         <v>112</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D419" s="2">
         <v>493</v>
@@ -11483,7 +11483,7 @@
         <v>112</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D420" s="2">
         <v>105</v>
@@ -11509,7 +11509,7 @@
         <v>112</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D421" s="2">
         <v>432</v>
@@ -11535,7 +11535,7 @@
         <v>112</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D422" s="2">
         <v>332</v>
@@ -11561,7 +11561,7 @@
         <v>112</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D423" s="2">
         <v>238</v>
@@ -11587,7 +11587,7 @@
         <v>112</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D424" s="2">
         <v>300</v>
@@ -11613,7 +11613,7 @@
         <v>112</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D425" s="2">
         <v>249</v>
@@ -11639,7 +11639,7 @@
         <v>112</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D426" s="2">
         <v>336</v>
@@ -11665,7 +11665,7 @@
         <v>112</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D427" s="2">
         <v>114</v>
@@ -11691,7 +11691,7 @@
         <v>112</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D428" s="2">
         <v>175</v>
@@ -11717,7 +11717,7 @@
         <v>112</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D429" s="2">
         <v>473</v>
@@ -11743,7 +11743,7 @@
         <v>112</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D430" s="2">
         <v>202</v>
@@ -11769,7 +11769,7 @@
         <v>112</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D431" s="2">
         <v>215</v>
@@ -11795,7 +11795,7 @@
         <v>112</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D432" s="2">
         <v>252</v>
@@ -11821,7 +11821,7 @@
         <v>112</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D433" s="2">
         <v>223</v>
@@ -11847,7 +11847,7 @@
         <v>113</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D434" s="2">
         <v>412</v>
@@ -11873,7 +11873,7 @@
         <v>113</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D435" s="2">
         <v>84</v>
@@ -11899,7 +11899,7 @@
         <v>113</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D436" s="2">
         <v>309</v>
@@ -11925,7 +11925,7 @@
         <v>113</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D437" s="2">
         <v>128</v>
@@ -11951,7 +11951,7 @@
         <v>113</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D438" s="2">
         <v>219</v>
@@ -11977,7 +11977,7 @@
         <v>113</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D439" s="2">
         <v>99</v>
@@ -12003,7 +12003,7 @@
         <v>113</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D440" s="2">
         <v>177</v>
@@ -12029,7 +12029,7 @@
         <v>113</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D441" s="2">
         <v>380</v>
@@ -12055,7 +12055,7 @@
         <v>113</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D442" s="2">
         <v>464</v>
@@ -12081,7 +12081,7 @@
         <v>113</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D443" s="2">
         <v>460</v>
@@ -12107,7 +12107,7 @@
         <v>113</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D444" s="2">
         <v>299</v>
@@ -12133,7 +12133,7 @@
         <v>113</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D445" s="2">
         <v>243</v>
@@ -12159,7 +12159,7 @@
         <v>113</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D446" s="2">
         <v>154</v>
@@ -12185,7 +12185,7 @@
         <v>113</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D447" s="2">
         <v>239</v>
@@ -12211,7 +12211,7 @@
         <v>113</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D448" s="2">
         <v>410</v>
@@ -12237,7 +12237,7 @@
         <v>113</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D449" s="2">
         <v>273</v>
@@ -12263,7 +12263,7 @@
         <v>113</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D450" s="2">
         <v>90</v>
@@ -12289,7 +12289,7 @@
         <v>113</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D451" s="2">
         <v>407</v>
@@ -12315,7 +12315,7 @@
         <v>113</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D452" s="2">
         <v>301</v>
@@ -12341,7 +12341,7 @@
         <v>113</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D453" s="2">
         <v>181</v>
@@ -12367,7 +12367,7 @@
         <v>113</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D454" s="2">
         <v>186</v>
@@ -12393,7 +12393,7 @@
         <v>113</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D455" s="2">
         <v>424</v>
@@ -12419,7 +12419,7 @@
         <v>113</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D456" s="2">
         <v>268</v>
@@ -12445,7 +12445,7 @@
         <v>113</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D457" s="2">
         <v>277</v>
@@ -12471,7 +12471,7 @@
         <v>113</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D458" s="2">
         <v>89</v>
@@ -12497,7 +12497,7 @@
         <v>113</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D459" s="2">
         <v>219</v>
@@ -12523,7 +12523,7 @@
         <v>113</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D460" s="2">
         <v>273</v>
@@ -12549,7 +12549,7 @@
         <v>113</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D461" s="2">
         <v>254</v>
@@ -12575,7 +12575,7 @@
         <v>113</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D462" s="2">
         <v>243</v>
@@ -12601,7 +12601,7 @@
         <v>113</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D463" s="2">
         <v>349</v>
@@ -12627,7 +12627,7 @@
         <v>113</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D464" s="2">
         <v>245</v>
@@ -12653,7 +12653,7 @@
         <v>113</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D465" s="2">
         <v>174</v>
@@ -12679,7 +12679,7 @@
         <v>113</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D466" s="2">
         <v>80</v>
@@ -12705,7 +12705,7 @@
         <v>113</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D467" s="2">
         <v>210</v>
@@ -12731,7 +12731,7 @@
         <v>113</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D468" s="2">
         <v>281</v>
@@ -12757,7 +12757,7 @@
         <v>113</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D469" s="2">
         <v>80</v>
@@ -12783,7 +12783,7 @@
         <v>114</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D470" s="2">
         <v>106</v>
@@ -12809,7 +12809,7 @@
         <v>114</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D471" s="2">
         <v>53</v>
@@ -12835,7 +12835,7 @@
         <v>114</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D472" s="2">
         <v>80</v>
@@ -12861,7 +12861,7 @@
         <v>114</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D473" s="2">
         <v>92</v>
@@ -12887,7 +12887,7 @@
         <v>114</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D474" s="2">
         <v>146</v>
@@ -12913,7 +12913,7 @@
         <v>114</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D475" s="2">
         <v>465</v>
@@ -12939,7 +12939,7 @@
         <v>114</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D476" s="2">
         <v>361</v>
@@ -12965,7 +12965,7 @@
         <v>114</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D477" s="2">
         <v>420</v>
@@ -12991,7 +12991,7 @@
         <v>114</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D478" s="2">
         <v>471</v>
@@ -13017,7 +13017,7 @@
         <v>114</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D479" s="2">
         <v>174</v>
@@ -13043,7 +13043,7 @@
         <v>114</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D480" s="2">
         <v>95</v>
@@ -13069,7 +13069,7 @@
         <v>114</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D481" s="2">
         <v>305</v>
@@ -13095,7 +13095,7 @@
         <v>114</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D482" s="2">
         <v>465</v>
@@ -13121,7 +13121,7 @@
         <v>114</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D483" s="2">
         <v>418</v>
@@ -13147,7 +13147,7 @@
         <v>114</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D484" s="2">
         <v>478</v>
@@ -13173,7 +13173,7 @@
         <v>114</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D485" s="2">
         <v>434</v>
@@ -13199,7 +13199,7 @@
         <v>114</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D486" s="2">
         <v>459</v>
@@ -13225,7 +13225,7 @@
         <v>114</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D487" s="2">
         <v>99</v>
@@ -13251,7 +13251,7 @@
         <v>114</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D488" s="2">
         <v>104</v>
@@ -13277,7 +13277,7 @@
         <v>114</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D489" s="2">
         <v>166</v>
@@ -13303,7 +13303,7 @@
         <v>114</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D490" s="2">
         <v>277</v>
@@ -13329,7 +13329,7 @@
         <v>114</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D491" s="2">
         <v>329</v>
@@ -13355,7 +13355,7 @@
         <v>114</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D492" s="2">
         <v>193</v>
@@ -13381,7 +13381,7 @@
         <v>114</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D493" s="2">
         <v>70</v>
@@ -13407,7 +13407,7 @@
         <v>114</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D494" s="2">
         <v>174</v>
@@ -13433,7 +13433,7 @@
         <v>114</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D495" s="2">
         <v>305</v>
@@ -13459,7 +13459,7 @@
         <v>114</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D496" s="2">
         <v>274</v>
@@ -13485,7 +13485,7 @@
         <v>114</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D497" s="2">
         <v>185</v>
@@ -13511,7 +13511,7 @@
         <v>114</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D498" s="2">
         <v>249</v>
@@ -13537,7 +13537,7 @@
         <v>114</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D499" s="2">
         <v>203</v>
@@ -13563,7 +13563,7 @@
         <v>114</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D500" s="2">
         <v>315</v>
@@ -13589,7 +13589,7 @@
         <v>114</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D501" s="2">
         <v>211</v>
@@ -13615,7 +13615,7 @@
         <v>114</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D502" s="2">
         <v>262</v>
@@ -13641,7 +13641,7 @@
         <v>114</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D503" s="2">
         <v>346</v>
@@ -13667,7 +13667,7 @@
         <v>114</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D504" s="2">
         <v>232</v>
@@ -13693,7 +13693,7 @@
         <v>114</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D505" s="2">
         <v>142</v>
@@ -13719,7 +13719,7 @@
         <v>115</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D506" s="2">
         <v>316</v>
@@ -13745,7 +13745,7 @@
         <v>115</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D507" s="2">
         <v>221</v>
@@ -13771,7 +13771,7 @@
         <v>115</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D508" s="2">
         <v>318</v>
@@ -13797,7 +13797,7 @@
         <v>115</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D509" s="2">
         <v>147</v>
@@ -13823,7 +13823,7 @@
         <v>115</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D510" s="2">
         <v>396</v>
@@ -13849,7 +13849,7 @@
         <v>115</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D511" s="2">
         <v>409</v>
@@ -13875,7 +13875,7 @@
         <v>115</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D512" s="2">
         <v>278</v>
@@ -13901,7 +13901,7 @@
         <v>115</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D513" s="2">
         <v>103</v>
@@ -13927,7 +13927,7 @@
         <v>115</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D514" s="2">
         <v>419</v>
@@ -13953,7 +13953,7 @@
         <v>115</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D515" s="2">
         <v>243</v>
@@ -13979,7 +13979,7 @@
         <v>115</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D516" s="2">
         <v>280</v>
@@ -14005,7 +14005,7 @@
         <v>115</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D517" s="2">
         <v>206</v>
@@ -14031,7 +14031,7 @@
         <v>115</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D518" s="2">
         <v>114</v>
@@ -14057,7 +14057,7 @@
         <v>115</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D519" s="2">
         <v>58</v>
@@ -14083,7 +14083,7 @@
         <v>115</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D520" s="2">
         <v>198</v>
@@ -14109,7 +14109,7 @@
         <v>115</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D521" s="2">
         <v>138</v>
@@ -14135,7 +14135,7 @@
         <v>115</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D522" s="2">
         <v>417</v>
@@ -14161,7 +14161,7 @@
         <v>115</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D523" s="2">
         <v>141</v>
@@ -14187,7 +14187,7 @@
         <v>115</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D524" s="2">
         <v>456</v>
@@ -14213,7 +14213,7 @@
         <v>115</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D525" s="2">
         <v>316</v>
@@ -14239,7 +14239,7 @@
         <v>115</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D526" s="2">
         <v>357</v>
@@ -14265,7 +14265,7 @@
         <v>115</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D527" s="2">
         <v>143</v>
@@ -14291,7 +14291,7 @@
         <v>115</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D528" s="2">
         <v>177</v>
@@ -14317,7 +14317,7 @@
         <v>115</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D529" s="2">
         <v>226</v>
@@ -14343,7 +14343,7 @@
         <v>115</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D530" s="2">
         <v>344</v>
@@ -14369,7 +14369,7 @@
         <v>115</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D531" s="2">
         <v>143</v>
@@ -14395,7 +14395,7 @@
         <v>115</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D532" s="2">
         <v>97</v>
@@ -14421,7 +14421,7 @@
         <v>115</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D533" s="2">
         <v>193</v>
@@ -14447,7 +14447,7 @@
         <v>115</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D534" s="2">
         <v>56</v>
@@ -14473,7 +14473,7 @@
         <v>115</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D535" s="2">
         <v>121</v>
@@ -14499,7 +14499,7 @@
         <v>115</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D536" s="2">
         <v>150</v>
@@ -14525,7 +14525,7 @@
         <v>115</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D537" s="2">
         <v>344</v>
@@ -14551,7 +14551,7 @@
         <v>115</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D538" s="2">
         <v>188</v>
@@ -14577,7 +14577,7 @@
         <v>115</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D539" s="2">
         <v>342</v>
@@ -14603,7 +14603,7 @@
         <v>115</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D540" s="2">
         <v>234</v>
@@ -14629,7 +14629,7 @@
         <v>115</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D541" s="2">
         <v>239</v>
